--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -84293,7 +84293,7 @@
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>2</v>
+        <v>2572386</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>849544</v>
@@ -84305,7 +84305,7 @@
         <v>30275</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>1174907</v>
+        <v>3747291</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,10 +49,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="10">
@@ -277,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -333,26 +329,15 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -84155,7 +84140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M130"/>
+  <dimension ref="A2:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -84489,22 +84474,22 @@
     <row r="20">
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Repo URLs</t>
+          <t>Outputs</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Class A</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Class B</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Class C</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -84758,1227 +84743,941 @@
       <c r="M33" s="37" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>Score distribution by component (scope 940)</t>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>Component / subcomponent</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>GitHub repos (Class A)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>915</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="41" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>GitLab repos (Class A)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Total repos</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>Concentration</t>
         </is>
       </c>
-      <c r="C38" s="42" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="F38" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="G38" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="H38" s="44" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>· bus factor</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>bf_commits_git_5y</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="21" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>· HHI</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>hhi_commits_git_5y</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>3060</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>5556</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>8987</v>
-      </c>
-      <c r="H40" s="21" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="41" t="inlineStr">
-        <is>
-          <t>Complexity</t>
-        </is>
-      </c>
-      <c r="C41" s="42" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>26</v>
-      </c>
-      <c r="F41" s="43" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" s="43" t="n">
-        <v>73</v>
-      </c>
-      <c r="H41" s="44" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>· lines of code</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>loc_eoy</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>365</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>2704</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>21612</v>
-      </c>
-      <c r="H42" s="21" t="n">
-        <v>36990782</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>· cyclomatic max</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>cyclomatic_max</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="H43" s="21" t="n">
-        <v>12556</v>
+      <c r="C43" s="40" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="41" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C44" s="42" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="D44" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E44" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="F44" s="43" t="n">
-        <v>72</v>
-      </c>
-      <c r="G44" s="43" t="n">
-        <v>84</v>
-      </c>
-      <c r="H44" s="44" t="n">
-        <v>100</v>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>· Bus Factor (5 years, git contributors)</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>· OpenSSF score (0–10)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>openssf_score</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E45" s="30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F45" s="30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>9.6</v>
+          <t>· HHI (5 years, git contributors)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>· CVE count 5y</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>cve_count_5y</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>10602</v>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>Workload</t>
-        </is>
-      </c>
-      <c r="C47" s="42" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="D47" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="43" t="n">
-        <v>38</v>
-      </c>
-      <c r="F47" s="43" t="n">
-        <v>56</v>
-      </c>
-      <c r="G47" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H47" s="44" t="n">
-        <v>97</v>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>· Lines of Code (last year snapshot)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>· LOC / contributor</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>loc_per_ac</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>107</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>302</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>804</v>
-      </c>
-      <c r="H48" s="21" t="n">
-        <v>353301</v>
+          <t>· Cyclomatic Complexity (last year snapshot)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>· CVE / contributor</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>cve_per_ac</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>14</v>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>· net-new-issues / contributor</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>nni_per_ac</t>
-        </is>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>-9.93</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G50" s="30" t="n">
+          <t>· OpenSSF Security Score (most recent data)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>· CVE count (5 years)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>Workload</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>· LOCs / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>· CVE / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>· Net new issues / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>Risk Score</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="39" t="inlineStr">
+        <is>
+          <t>Concentration</t>
+        </is>
+      </c>
+      <c r="C60" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="29" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="45" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C51" s="46" t="inlineStr">
-        <is>
-          <t>risk_score</t>
-        </is>
-      </c>
-      <c r="D51" s="47" t="n">
-        <v>11</v>
-      </c>
-      <c r="E51" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="F51" s="47" t="n">
-        <v>54</v>
-      </c>
-      <c r="G51" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="H51" s="48" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>Concentration funnel</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>input top repos</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D56" s="49" t="n">
+      <c r="D60" s="41" t="n">
+        <v>41</v>
+      </c>
+      <c r="E60" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="F60" s="41" t="n">
+        <v>95</v>
+      </c>
+      <c r="G60" s="40" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>· Bus Factor (5 years, git contributors)</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>bus factor / HHI (git 5y) computed</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D57" s="49" t="n">
+      <c r="D61" s="20" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>bus factor / HHI (GitHub) computed</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="n">
-        <v>902</v>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="45" t="inlineStr">
-        <is>
-          <t>Concentration score</t>
-        </is>
-      </c>
-      <c r="C59" s="47" t="n">
-        <v>940</v>
-      </c>
-      <c r="D59" s="50" t="n">
+      <c r="E61" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="F61" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="62">
-      <c r="B62" s="39" t="inlineStr">
-        <is>
-          <t>Complexity funnel</t>
-        </is>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>· HHI (5 years, git contributors)</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D62" s="20" t="n">
+        <v>3060</v>
+      </c>
+      <c r="E62" s="20" t="n">
+        <v>5556</v>
+      </c>
+      <c r="F62" s="20" t="n">
+        <v>8987</v>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="B63" s="39" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="E63" s="41" t="n">
+        <v>49</v>
+      </c>
+      <c r="F63" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="G63" s="40" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>input top repos</t>
+          <t>· Lines of Code (last year snapshot)</t>
         </is>
       </c>
       <c r="C64" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D64" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D64" s="20" t="n">
+        <v>365</v>
+      </c>
+      <c r="E64" s="20" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F64" s="20" t="n">
+        <v>21612</v>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>36990782</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>lines of code (scc)</t>
+          <t>· Cyclomatic Complexity (last year snapshot)</t>
         </is>
       </c>
       <c r="C65" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D65" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D65" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>12556</v>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>cyclomatic max (lizard)</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D66" s="49" t="n">
-        <v>1</v>
+      <c r="B66" s="39" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C66" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D66" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="F66" s="41" t="n">
+        <v>84</v>
+      </c>
+      <c r="G66" s="40" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>cognitive max (lizard)</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D67" s="49" t="n">
-        <v>1</v>
+          <t>· OpenSSF Security Score (most recent data)</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D67" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F67" s="30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G67" s="29" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>churn 5y</t>
+          <t>· CVE count (5 years)</t>
         </is>
       </c>
       <c r="C68" s="20" t="n">
-        <v>882</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="21" t="n">
+        <v>10602</v>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="45" t="inlineStr">
-        <is>
-          <t>Complexity score</t>
-        </is>
-      </c>
-      <c r="C69" s="47" t="n">
+      <c r="B69" s="39" t="inlineStr">
+        <is>
+          <t>Workload</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="E69" s="41" t="n">
+        <v>56</v>
+      </c>
+      <c r="F69" s="41" t="n">
+        <v>70</v>
+      </c>
+      <c r="G69" s="40" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>· LOCs / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="20" t="n">
+        <v>107</v>
+      </c>
+      <c r="E70" s="20" t="n">
+        <v>302</v>
+      </c>
+      <c r="F70" s="20" t="n">
+        <v>804</v>
+      </c>
+      <c r="G70" s="21" t="n">
+        <v>353301</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>· CVE / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="29" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>· Net new issues / active contributors (5 years)</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="n">
+        <v>-9.93</v>
+      </c>
+      <c r="D72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F72" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="29" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>Risk Score</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="E73" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>65</v>
+      </c>
+      <c r="G73" s="28" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="42" t="n"/>
+      <c r="B76" s="43" t="inlineStr">
+        <is>
+          <t>Stage 3: Eligibility</t>
+        </is>
+      </c>
+      <c r="C76" s="42" t="n"/>
+      <c r="D76" s="42" t="n"/>
+      <c r="E76" s="42" t="n"/>
+      <c r="F76" s="42" t="n"/>
+      <c r="G76" s="42" t="n"/>
+      <c r="H76" s="42" t="n"/>
+      <c r="I76" s="42" t="n"/>
+      <c r="J76" s="42" t="n"/>
+      <c r="K76" s="42" t="n"/>
+      <c r="L76" s="42" t="n"/>
+      <c r="M76" s="42" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>GitHub repos (Class A)</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>GitLab repos (Class A)</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>Total repos</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="n">
         <v>940</v>
       </c>
-      <c r="D69" s="50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="39" t="inlineStr">
-        <is>
-          <t>Security funnel</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D73" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>input top repos</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D74" s="49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>OpenSSF score present</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D75" s="49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>CVE count 5y &gt; 0</t>
-        </is>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>208</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>0.221</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>OSS-Fuzz enrolled</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="n">
-        <v>135</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.144</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>CII Best Practices badge</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>0.033</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="45" t="inlineStr">
-        <is>
-          <t>Security score</t>
-        </is>
-      </c>
-      <c r="C79" s="47" t="n">
-        <v>940</v>
-      </c>
-      <c r="D79" s="50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="39" t="inlineStr">
-        <is>
-          <t>Workload funnel</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D83" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>input top repos</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D84" s="49" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="85">
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>issues data present</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D85" s="49" t="n">
-        <v>1</v>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>per-AC ratios (loc/cve/nni) computed</t>
-        </is>
-      </c>
-      <c r="C86" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D86" s="49" t="n">
-        <v>1</v>
+          <t>Open Source</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="n">
+        <v>936</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>issue_close_ratio computed</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>847</v>
-      </c>
-      <c r="D87" s="32" t="n">
-        <v>0.9009999999999999</v>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>918</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>issue_trend_score computed</t>
-        </is>
-      </c>
-      <c r="C88" s="20" t="n">
-        <v>642</v>
-      </c>
-      <c r="D88" s="32" t="n">
-        <v>0.6829999999999999</v>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="C88" s="21" t="n">
+        <v>736</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="45" t="inlineStr">
-        <is>
-          <t>Workload score</t>
-        </is>
-      </c>
-      <c r="C89" s="47" t="n">
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Nonprofit</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="n">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="26" t="inlineStr">
+        <is>
+          <t>Eligibility checked</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="n">
         <v>940</v>
       </c>
-      <c r="D89" s="50" t="n">
+    </row>
+    <row r="93">
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>Solo blocker</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>Open Source</t>
+        </is>
+      </c>
+      <c r="C94" s="45" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="51" t="n"/>
-      <c r="B92" s="52" t="inlineStr">
-        <is>
-          <t>Stage 3: Eligibility</t>
-        </is>
-      </c>
-      <c r="C92" s="51" t="n"/>
-      <c r="D92" s="51" t="n"/>
-      <c r="E92" s="51" t="n"/>
-      <c r="F92" s="51" t="n"/>
-      <c r="G92" s="51" t="n"/>
-      <c r="H92" s="51" t="n"/>
-      <c r="I92" s="51" t="n"/>
-      <c r="J92" s="51" t="n"/>
-      <c r="K92" s="51" t="n"/>
-      <c r="L92" s="51" t="n"/>
-      <c r="M92" s="51" t="n"/>
+      <c r="D94" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="45" t="n">
+        <v>936</v>
+      </c>
+      <c r="F94" s="46" t="n">
+        <v>940</v>
+      </c>
     </row>
     <row r="95">
-      <c r="B95" s="39" t="inlineStr">
-        <is>
-          <t>Licenses (scope 940)</t>
-        </is>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>· License from manual override</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C96" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D96" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>· License from package registry</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="n">
+        <v>893</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>input top repos (incl. archived)</t>
-        </is>
-      </c>
-      <c r="C97" s="20" t="n">
-        <v>940</v>
-      </c>
-      <c r="D97" s="49" t="n">
-        <v>1</v>
+          <t>· License from GitHub repo</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>license resolved</t>
-        </is>
-      </c>
-      <c r="C98" s="20" t="n">
+          <t>· License from GitLab repo</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C99" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D99" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="E99" s="45" t="n">
+        <v>918</v>
+      </c>
+      <c r="F99" s="46" t="n">
         <v>940</v>
-      </c>
-      <c r="D98" s="49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>· from override</t>
-        </is>
-      </c>
-      <c r="C99" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="D99" s="32" t="n">
-        <v>0.024</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>· from registry</t>
-        </is>
-      </c>
-      <c r="C100" s="20" t="n">
-        <v>893</v>
-      </c>
-      <c r="D100" s="32" t="n">
-        <v>0.95</v>
+          <t>· EOL (manual override)</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>· from GitHub</t>
-        </is>
-      </c>
-      <c r="C101" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="D101" s="32" t="n">
-        <v>0.01</v>
+          <t>· Archived (repo)</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>· from GitLab</t>
-        </is>
-      </c>
-      <c r="C102" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D102" s="32" t="n">
-        <v>0.016</v>
+          <t>· Archived but mirror-exempt</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="41" t="inlineStr">
-        <is>
-          <t>oss=True (OSS-approved)</t>
-        </is>
-      </c>
-      <c r="C103" s="43" t="n">
-        <v>936</v>
-      </c>
-      <c r="D103" s="53" t="n">
-        <v>0.996</v>
+      <c r="B103" s="44" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="C103" s="45" t="n">
+        <v>190</v>
+      </c>
+      <c r="D103" s="45" t="n">
+        <v>204</v>
+      </c>
+      <c r="E103" s="45" t="n">
+        <v>736</v>
+      </c>
+      <c r="F103" s="46" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>oss=False (known non-OSS)</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D104" s="32" t="n">
-        <v>0.004</v>
+          <t>· GitHub Sponsors</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="n">
+        <v>376</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="23" t="inlineStr">
-        <is>
-          <t>oss unknown (no signal)</t>
-        </is>
-      </c>
-      <c r="C105" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="54" t="n">
-        <v>0</v>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>· FUNDING.yml</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>· funding.json</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>· npm / PyPI funding field</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="39" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>· Maintainer Sponsors</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="n">
+        <v>551</v>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D109" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>· Open Collective</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n">
+        <v>178</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>eol (override)</t>
-        </is>
-      </c>
-      <c r="C110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="32" t="n">
-        <v>0</v>
+          <t>· Institutional host / owner</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="19" t="inlineStr">
-        <is>
-          <t>archived</t>
-        </is>
-      </c>
-      <c r="C111" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="D111" s="32" t="n">
-        <v>0.026</v>
+      <c r="B111" s="44" t="inlineStr">
+        <is>
+          <t>Nonprofit</t>
+        </is>
+      </c>
+      <c r="C111" s="45" t="n">
+        <v>59</v>
+      </c>
+      <c r="D111" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="E111" s="45" t="n">
+        <v>880</v>
+      </c>
+      <c r="F111" s="46" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>archived but mirror-exempt</t>
-        </is>
-      </c>
-      <c r="C112" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D112" s="32" t="n">
-        <v>0.002</v>
+          <t>· Company-backed</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="45" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C113" s="47" t="n">
-        <v>918</v>
-      </c>
-      <c r="D113" s="55" t="n">
-        <v>0.977</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="39" t="inlineStr">
-        <is>
-          <t>Intent and nonprofit</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C117" s="17" t="inlineStr">
-        <is>
-          <t>Repos</t>
-        </is>
-      </c>
-      <c r="D117" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="19" t="inlineStr">
-        <is>
-          <t>intent — any funding signal</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="n">
-        <v>736</v>
-      </c>
-      <c r="D118" s="32" t="n">
-        <v>0.7829999999999999</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="19" t="inlineStr">
-        <is>
-          <t>intent — no funding signal</t>
-        </is>
-      </c>
-      <c r="C119" s="20" t="n">
-        <v>204</v>
-      </c>
-      <c r="D119" s="32" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="33" t="inlineStr">
-        <is>
-          <t>nonprofit — community / independent</t>
-        </is>
-      </c>
-      <c r="C120" s="34" t="n">
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>· Community / independent</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="n">
         <v>880</v>
       </c>
-      <c r="D120" s="35" t="n">
-        <v>0.9359999999999999</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="23" t="inlineStr">
-        <is>
-          <t>nonprofit — company-backed</t>
-        </is>
-      </c>
-      <c r="C121" s="24" t="n">
-        <v>60</v>
-      </c>
-      <c r="D121" s="54" t="n">
-        <v>0.064</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="39" t="inlineStr">
-        <is>
-          <t>Eligibility rollup</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="C125" s="17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D125" s="17" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E125" s="18" t="inlineStr">
-        <is>
-          <t>sole blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>oss</t>
-        </is>
-      </c>
-      <c r="C126" s="20" t="n">
-        <v>936</v>
-      </c>
-      <c r="D126" s="56" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E126" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="19" t="inlineStr">
-        <is>
-          <t>intent</t>
-        </is>
-      </c>
-      <c r="C127" s="20" t="n">
-        <v>736</v>
-      </c>
-      <c r="D127" s="56" t="n">
-        <v>0.7829999999999999</v>
-      </c>
-      <c r="E127" s="21" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="19" t="inlineStr">
-        <is>
-          <t>nonprofit</t>
-        </is>
-      </c>
-      <c r="C128" s="20" t="n">
-        <v>880</v>
-      </c>
-      <c r="D128" s="56" t="n">
-        <v>0.9359999999999999</v>
-      </c>
-      <c r="E128" s="21" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C129" s="20" t="n">
-        <v>918</v>
-      </c>
-      <c r="D129" s="56" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="E129" s="21" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="26" t="inlineStr">
-        <is>
-          <t>eligible</t>
-        </is>
-      </c>
-      <c r="C130" s="27" t="n">
+    </row>
+    <row r="114">
+      <c r="B114" s="26" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="n"/>
+      <c r="D114" s="27" t="n">
+        <v>275</v>
+      </c>
+      <c r="E114" s="27" t="n">
         <v>665</v>
       </c>
-      <c r="D130" s="57" t="n">
-        <v>0.7070000000000001</v>
-      </c>
-      <c r="E130" s="58" t="n"/>
+      <c r="F114" s="28" t="n">
+        <v>940</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -85556,7 +85556,7 @@
     <row r="104">
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>· GitHub Sponsors</t>
+          <t>· GitHub Sponsors (owner or repo)</t>
         </is>
       </c>
       <c r="F104" s="21" t="n">
@@ -85596,7 +85596,7 @@
     <row r="108">
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>· Maintainer Sponsors</t>
+          <t>· GitHub Sponsors (maintainer)</t>
         </is>
       </c>
       <c r="F108" s="21" t="n">

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -85451,6 +85451,15 @@
           <t>· License from manual override</t>
         </is>
       </c>
+      <c r="C95" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="D95" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="20" t="n">
+        <v>23</v>
+      </c>
       <c r="F95" s="21" t="n">
         <v>23</v>
       </c>
@@ -85461,6 +85470,15 @@
           <t>· License from package registry</t>
         </is>
       </c>
+      <c r="C96" s="20" t="n">
+        <v>889</v>
+      </c>
+      <c r="D96" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" s="20" t="n">
+        <v>889</v>
+      </c>
       <c r="F96" s="21" t="n">
         <v>893</v>
       </c>
@@ -85471,6 +85489,15 @@
           <t>· License from GitHub repo</t>
         </is>
       </c>
+      <c r="C97" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D97" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="20" t="n">
+        <v>9</v>
+      </c>
       <c r="F97" s="21" t="n">
         <v>9</v>
       </c>
@@ -85481,6 +85508,15 @@
           <t>· License from GitLab repo</t>
         </is>
       </c>
+      <c r="C98" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="20" t="n">
+        <v>15</v>
+      </c>
       <c r="F98" s="21" t="n">
         <v>15</v>
       </c>
@@ -85510,6 +85546,15 @@
           <t>· EOL (manual override)</t>
         </is>
       </c>
+      <c r="C100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="F100" s="21" t="n">
         <v>0</v>
       </c>
@@ -85520,6 +85565,15 @@
           <t>· Archived (repo)</t>
         </is>
       </c>
+      <c r="C101" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D101" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="F101" s="21" t="n">
         <v>24</v>
       </c>
@@ -85530,6 +85584,15 @@
           <t>· Archived but mirror-exempt</t>
         </is>
       </c>
+      <c r="C102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="F102" s="21" t="n">
         <v>2</v>
       </c>
@@ -85559,6 +85622,15 @@
           <t>· GitHub Sponsors (owner or repo)</t>
         </is>
       </c>
+      <c r="C104" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>376</v>
+      </c>
       <c r="F104" s="21" t="n">
         <v>376</v>
       </c>
@@ -85569,6 +85641,15 @@
           <t>· FUNDING.yml</t>
         </is>
       </c>
+      <c r="C105" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="D105" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="20" t="n">
+        <v>391</v>
+      </c>
       <c r="F105" s="21" t="n">
         <v>391</v>
       </c>
@@ -85579,6 +85660,15 @@
           <t>· funding.json</t>
         </is>
       </c>
+      <c r="C106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="20" t="n">
+        <v>8</v>
+      </c>
       <c r="F106" s="21" t="n">
         <v>8</v>
       </c>
@@ -85589,6 +85679,15 @@
           <t>· npm / PyPI funding field</t>
         </is>
       </c>
+      <c r="C107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="20" t="n">
+        <v>215</v>
+      </c>
       <c r="F107" s="21" t="n">
         <v>215</v>
       </c>
@@ -85599,6 +85698,15 @@
           <t>· GitHub Sponsors (maintainer)</t>
         </is>
       </c>
+      <c r="C108" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="D108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>551</v>
+      </c>
       <c r="F108" s="21" t="n">
         <v>551</v>
       </c>
@@ -85609,6 +85717,15 @@
           <t>· Open Collective</t>
         </is>
       </c>
+      <c r="C109" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>178</v>
+      </c>
       <c r="F109" s="21" t="n">
         <v>178</v>
       </c>
@@ -85619,6 +85736,15 @@
           <t>· Institutional host / owner</t>
         </is>
       </c>
+      <c r="C110" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="D110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>90</v>
+      </c>
       <c r="F110" s="21" t="n">
         <v>90</v>
       </c>
@@ -85648,6 +85774,15 @@
           <t>· Company-backed</t>
         </is>
       </c>
+      <c r="C112" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="D112" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E112" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="F112" s="21" t="n">
         <v>60</v>
       </c>
@@ -85657,6 +85792,15 @@
         <is>
           <t>· Community / independent</t>
         </is>
+      </c>
+      <c r="C113" s="20" t="n">
+        <v>880</v>
+      </c>
+      <c r="D113" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="20" t="n">
+        <v>880</v>
       </c>
       <c r="F113" s="21" t="n">
         <v>880</v>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -85448,77 +85448,77 @@
     <row r="95">
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>· License from manual override</t>
+          <t>· License from package registry</t>
         </is>
       </c>
       <c r="C95" s="20" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D95" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>23</v>
+        <v>889</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>23</v>
+        <v>893</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>· License from package registry</t>
+          <t>· License from manual override</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="D96" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>889</v>
+        <v>23</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>893</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>· License from GitHub repo</t>
+          <t>· License from GitLab repo</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D97" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>· License from GitLab repo</t>
+          <t>· License from GitHub repo</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D98" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
@@ -85543,45 +85543,45 @@
     <row r="100">
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>· EOL (manual override)</t>
+          <t>· Archived GitHub repo</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D100" s="20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F100" s="21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>· Archived (repo)</t>
+          <t>· Archived GitHub repo but mirror-exempt</t>
         </is>
       </c>
       <c r="C101" s="20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D101" s="20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E101" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="21" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>· Archived but mirror-exempt</t>
+          <t>· EOL (manual override)</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
@@ -85591,10 +85591,10 @@
         <v>0</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F102" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -85619,20 +85619,20 @@
     <row r="104">
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>· GitHub Sponsors (owner or repo)</t>
+          <t>· GitHub Sponsors (maintainer)</t>
         </is>
       </c>
       <c r="C104" s="20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D104" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E104" s="20" t="n">
-        <v>376</v>
+        <v>551</v>
       </c>
       <c r="F104" s="21" t="n">
-        <v>376</v>
+        <v>551</v>
       </c>
     </row>
     <row r="105">
@@ -85642,7 +85642,7 @@
         </is>
       </c>
       <c r="C105" s="20" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D105" s="20" t="n">
         <v>0</v>
@@ -85657,7 +85657,7 @@
     <row r="106">
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>· funding.json</t>
+          <t>· GitHub Sponsors (owner or repo)</t>
         </is>
       </c>
       <c r="C106" s="20" t="n">
@@ -85667,10 +85667,10 @@
         <v>0</v>
       </c>
       <c r="E106" s="20" t="n">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="F106" s="21" t="n">
-        <v>8</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107">
@@ -85695,58 +85695,58 @@
     <row r="108">
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>· GitHub Sponsors (maintainer)</t>
+          <t>· Open Collective</t>
         </is>
       </c>
       <c r="C108" s="20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D108" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E108" s="20" t="n">
-        <v>551</v>
+        <v>178</v>
       </c>
       <c r="F108" s="21" t="n">
-        <v>551</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="19" t="inlineStr">
         <is>
-          <t>· Open Collective</t>
+          <t>· Institutional host / owner</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D109" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="F109" s="21" t="n">
-        <v>178</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>· Institutional host / owner</t>
+          <t>· funding.json</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D110" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E110" s="20" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F110" s="21" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -85771,39 +85771,39 @@
     <row r="112">
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>· Company-backed</t>
+          <t>· Community / independent</t>
         </is>
       </c>
       <c r="C112" s="20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D112" s="20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E112" s="20" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="F112" s="21" t="n">
-        <v>60</v>
+        <v>880</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="19" t="inlineStr">
         <is>
-          <t>· Community / independent</t>
+          <t>· Company-backed</t>
         </is>
       </c>
       <c r="C113" s="20" t="n">
-        <v>880</v>
+        <v>59</v>
       </c>
       <c r="D113" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E113" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="20" t="n">
-        <v>880</v>
-      </c>
       <c r="F113" s="21" t="n">
-        <v>880</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -85597,10 +85597,10 @@
         <v>0</v>
       </c>
       <c r="E107" s="20" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="21" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108">

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>25.59</v>
+        <v>25.65</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>55.14</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>29.44</v>
+        <v>29.68</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>57.51</v>
@@ -4213,7 +4213,7 @@
         <v>100</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>64.13</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>74.22</v>
@@ -4231,7 +4231,7 @@
         <v>73.95999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>68.87</v>
+        <v>68.88</v>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
@@ -5747,12 +5747,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>caolan/async</t>
+          <t>util-linux/util-linux</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5762,46 +5762,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>async</t>
+          <t>util-linux</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>41.24</v>
+        <v>31.85</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>62.24</v>
+        <v>58.79</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>58.59</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>65.5</v>
+        <v>68.36</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>53.95</v>
+        <v>30.77</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>93.12</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>74.67</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>69.22</v>
+        <v>66.34</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>67.33</v>
+        <v>67.34</v>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
@@ -5833,12 +5833,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>util-linux/util-linux</t>
+          <t>caolan/async</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5848,43 +5848,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>util-linux</t>
+          <t>async</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>31.61</v>
+        <v>41.24</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>58.79</v>
+        <v>62.24</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>58.59</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>68.33</v>
+        <v>65.5</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>30.77</v>
+        <v>53.95</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>93.12</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>92.75</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>66.34</v>
+        <v>69.22</v>
       </c>
       <c r="P59" s="3" t="n">
         <v>67.33</v>
@@ -6267,12 +6267,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>curl/curl</t>
+          <t>isaacs/minipass</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6282,46 +6282,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>minipass</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>32.08</v>
+        <v>71.36</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>59.02</v>
+        <v>72.56</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>69.92</v>
+        <v>44.89</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>71.06</v>
+        <v>61.33</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>35.6</v>
+        <v>91.31</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>94.83</v>
+        <v>56.01</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>99.52</v>
+        <v>92.75</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>48.19</v>
+        <v>61.31</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>63.43</v>
+        <v>73.44</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>67.14</v>
+        <v>67.11</v>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>isaacs/minipass</t>
+          <t>postcss/postcss</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6375,41 +6375,41 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>minipass</t>
+          <t>postcss</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>71.36</v>
+        <v>48.48</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>72.56</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>44.89</v>
+        <v>63.48</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>61.33</v>
+        <v>69.38</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>91.31</v>
+        <v>57.71</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>56.01</v>
+        <v>74.08</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>92.75</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>61.31</v>
+        <v>47.98</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>73.44</v>
+        <v>64.72</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>67.11</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
@@ -6443,12 +6443,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>postcss/postcss</t>
+          <t>micromark/micromark</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6463,41 +6463,41 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>postcss</t>
+          <t>micromark-util-symbol</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>48.48</v>
+        <v>63.28</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>64.43000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>63.48</v>
+        <v>48.25</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>69.38</v>
+        <v>62.24</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>57.71</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>74.08</v>
+        <v>69.37</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>85.51000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>47.98</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>64.72</v>
+        <v>72.09</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>67.01000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
@@ -6531,12 +6531,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>micromark/micromark</t>
+          <t>conventional-changelog/conventional-changelog</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6551,41 +6551,41 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>micromark-util-symbol</t>
+          <t>conventional-commits-parser</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>63.28</v>
+        <v>37.47</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>69.59</v>
+        <v>61.06</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>48.25</v>
+        <v>56.7</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>62.24</v>
+        <v>63.87</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>91.20999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>69.37</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>65.14</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>65.54000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>72.09</v>
+        <v>70.22</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>66.98</v>
+        <v>66.97</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S67" s="5" t="inlineStr">
@@ -6609,22 +6609,20 @@
       </c>
       <c r="U67" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V67" s="5" t="n">
-        <v>46</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>conventional-changelog/conventional-changelog</t>
+          <t>petkaantonov/bluebird</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6639,41 +6637,41 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>conventional-commits-parser</t>
+          <t>bluebird</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>37.47</v>
+        <v>25.23</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>61.06</v>
+        <v>56.7</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>56.7</v>
+        <v>55.73</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>63.87</v>
+        <v>61.63</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>63.7</v>
+        <v>39.12</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>76.51000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>70.22</v>
+        <v>72.67</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>66.97</v>
+        <v>66.92</v>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
@@ -6705,7 +6703,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>petkaantonov/bluebird</t>
+          <t>follow-redirects/follow-redirects</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,41 +6723,41 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>bluebird</t>
+          <t>follow-redirects</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>25.23</v>
+        <v>38.39</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>56.7</v>
+        <v>61.35</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>55.73</v>
+        <v>54.16</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>61.63</v>
+        <v>62.47</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>39.12</v>
+        <v>82.91</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>80.7</v>
+        <v>55.24</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>98.83</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>89.36</v>
+        <v>65.67</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>72.67</v>
+        <v>71.66</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>66.92</v>
+        <v>66.91</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
@@ -6768,7 +6766,7 @@
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S69" s="5" t="inlineStr">
@@ -6783,20 +6781,22 @@
       </c>
       <c r="U69" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V69" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V69" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>follow-redirects/follow-redirects</t>
+          <t>curl/curl</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6806,46 +6806,46 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>follow-redirects</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>38.39</v>
+        <v>28.94</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>61.35</v>
+        <v>56.88</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>54.16</v>
+        <v>69.92</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>62.47</v>
+        <v>70.53</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>82.91</v>
+        <v>35.6</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>55.24</v>
+        <v>94.83</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>87.68000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>65.67</v>
+        <v>48.19</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>71.66</v>
+        <v>63.43</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>66.91</v>
+        <v>66.89</v>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="F117" s="3" t="n">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>56.47</v>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>26.9</v>
+        <v>26.96</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>55.93</v>
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="F145" s="3" t="n">
-        <v>28.2</v>
+        <v>28.26</v>
       </c>
       <c r="G145" s="3" t="n">
         <v>56.49</v>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="4" t="n">
-        <v>53.63</v>
+        <v>53.64</v>
       </c>
       <c r="K145" s="3" t="n">
         <v>78.16</v>
@@ -15941,61 +15941,57 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>getsentry/sentry-javascript</t>
+          <t>gnome/libxml2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>@sentry/core</t>
+          <t>libxml2</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
-        <v>51.31</v>
+        <v>29.49</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="H175" s="3" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="I175" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>57.41</v>
+      </c>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
       <c r="J175" s="4" t="n">
-        <v>73.92</v>
+        <v>43.45</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>14.4</v>
+        <v>89.55</v>
       </c>
       <c r="L175" s="3" t="n">
-        <v>88.42</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>85.51000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>71.97</v>
+        <v>79</v>
       </c>
       <c r="O175" s="4" t="n">
-        <v>52.91</v>
+        <v>90.12</v>
       </c>
       <c r="P175" s="3" t="n">
-        <v>62.54</v>
+        <v>62.58</v>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
@@ -16009,7 +16005,7 @@
       </c>
       <c r="S175" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T175" s="5" t="inlineStr">
@@ -16019,65 +16015,71 @@
       </c>
       <c r="U175" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V175" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V175" s="5" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>gnome/libxml2</t>
+          <t>getsentry/sentry-javascript</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>libxml2</t>
+          <t>@sentry/core</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
-        <v>29.25</v>
+        <v>51.31</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
+        <v>65.19</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J176" s="4" t="n">
-        <v>43.33</v>
+        <v>73.92</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>89.55</v>
+        <v>14.4</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>95.29000000000001</v>
+        <v>88.42</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>97.83</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>79</v>
+        <v>71.97</v>
       </c>
       <c r="O176" s="4" t="n">
-        <v>90.12</v>
+        <v>52.91</v>
       </c>
       <c r="P176" s="3" t="n">
-        <v>62.49</v>
+        <v>62.54</v>
       </c>
       <c r="Q176" s="5" t="inlineStr">
         <is>
@@ -16091,7 +16093,7 @@
       </c>
       <c r="S176" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T176" s="5" t="inlineStr">
@@ -16101,12 +16103,10 @@
       </c>
       <c r="U176" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V176" s="5" t="n">
-        <v>117</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="F184" s="3" t="n">
-        <v>29.06</v>
+        <v>29.3</v>
       </c>
       <c r="G184" s="3" t="n">
         <v>57.28</v>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="4" t="n">
-        <v>48.54</v>
+        <v>48.57</v>
       </c>
       <c r="K184" s="3" t="n">
         <v>64.31</v>
@@ -16775,7 +16775,7 @@
         <v>79.09</v>
       </c>
       <c r="P184" s="3" t="n">
-        <v>61.96</v>
+        <v>61.98</v>
       </c>
       <c r="Q184" s="5" t="inlineStr">
         <is>
@@ -18201,61 +18201,57 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>npm/node-semver</t>
+          <t>bzip2/bzip2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>semver</t>
+          <t>bzip2</t>
         </is>
       </c>
       <c r="F201" s="3" t="n">
-        <v>77.94</v>
+        <v>30.72</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="H201" s="3" t="n">
-        <v>57.36</v>
-      </c>
-      <c r="I201" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>58.48</v>
+      </c>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
       <c r="J201" s="4" t="n">
-        <v>69.7</v>
+        <v>44.6</v>
       </c>
       <c r="K201" s="3" t="n">
-        <v>32.11</v>
+        <v>80.69</v>
       </c>
       <c r="L201" s="3" t="n">
-        <v>71.75</v>
+        <v>75.16</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>51.75</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>54.26</v>
+        <v>84.88</v>
       </c>
       <c r="P201" s="3" t="n">
-        <v>61.5</v>
+        <v>61.53</v>
       </c>
       <c r="Q201" s="5" t="inlineStr">
         <is>
@@ -18264,17 +18260,17 @@
       </c>
       <c r="R201" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S201" s="5" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T201" s="5" t="inlineStr">
+        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="T201" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
       <c r="U201" s="6" t="inlineStr">
@@ -18287,12 +18283,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>python-jsonschema/referencing</t>
+          <t>npm/node-semver</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -18302,43 +18298,43 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>referencing</t>
+          <t>semver</t>
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>41.35</v>
+        <v>77.94</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>73.2</v>
+        <v>74.86</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>42.21</v>
+        <v>57.36</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>56.78</v>
+        <v>69.7</v>
       </c>
       <c r="K202" s="3" t="n">
-        <v>98.70999999999999</v>
+        <v>32.11</v>
       </c>
       <c r="L202" s="3" t="n">
-        <v>47.89</v>
+        <v>71.75</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>50</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>83.28</v>
+        <v>51.75</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>66.61</v>
+        <v>54.26</v>
       </c>
       <c r="P202" s="3" t="n">
         <v>61.5</v>
@@ -18355,7 +18351,7 @@
       </c>
       <c r="S202" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T202" s="5" t="inlineStr">
@@ -18365,22 +18361,20 @@
       </c>
       <c r="U202" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V202" s="5" t="n">
-        <v>133</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>tapjs/stack-utils</t>
+          <t>python-jsonschema/referencing</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -18390,46 +18384,46 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>stack-utils</t>
+          <t>referencing</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
-        <v>25.36</v>
+        <v>41.35</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>56.71</v>
+        <v>73.2</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>40.5</v>
+        <v>42.21</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>52.51</v>
+        <v>56.78</v>
       </c>
       <c r="K203" s="3" t="n">
-        <v>80.34</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="L203" s="3" t="n">
-        <v>49.16</v>
+        <v>47.89</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>88.06</v>
+        <v>50</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>77.29000000000001</v>
+        <v>83.28</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>72</v>
+        <v>66.61</v>
       </c>
       <c r="P203" s="3" t="n">
-        <v>61.49</v>
+        <v>61.5</v>
       </c>
       <c r="Q203" s="5" t="inlineStr">
         <is>
@@ -18457,63 +18451,67 @@
         </is>
       </c>
       <c r="V203" s="5" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>bzip2/bzip2</t>
+          <t>tapjs/stack-utils</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>bzip2</t>
+          <t>stack-utils</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
-        <v>30.48</v>
+        <v>25.36</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>58.48</v>
-      </c>
-      <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="n"/>
+        <v>56.71</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J204" s="4" t="n">
-        <v>44.48</v>
+        <v>52.51</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>80.69</v>
+        <v>80.34</v>
       </c>
       <c r="L204" s="3" t="n">
-        <v>75.16</v>
+        <v>49.16</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>92.75</v>
+        <v>88.06</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>92.26000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>84.88</v>
+        <v>72</v>
       </c>
       <c r="P204" s="3" t="n">
-        <v>61.44</v>
+        <v>61.49</v>
       </c>
       <c r="Q204" s="5" t="inlineStr">
         <is>
@@ -18522,7 +18520,7 @@
       </c>
       <c r="R204" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S204" s="5" t="inlineStr">
@@ -18532,15 +18530,17 @@
       </c>
       <c r="T204" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U204" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V204" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V204" s="5" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -22717,59 +22717,57 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>remusao/tldts</t>
+          <t>libidn/libidn2</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>tldts</t>
+          <t>libidn2</t>
         </is>
       </c>
       <c r="F253" s="3" t="n">
-        <v>44.92</v>
+        <v>31.17</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="H253" s="3" t="n">
-        <v>54.15</v>
-      </c>
+        <v>58.62</v>
+      </c>
+      <c r="H253" s="3" t="n"/>
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="4" t="n">
-        <v>54.18</v>
+        <v>44.89</v>
       </c>
       <c r="K253" s="3" t="n">
-        <v>73.8</v>
+        <v>90.77</v>
       </c>
       <c r="L253" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>50</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>81.3</v>
+        <v>82.89</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>66.65000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="P253" s="3" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="Q253" s="5" t="inlineStr">
         <is>
@@ -22801,12 +22799,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>rust-lang/compiler-builtins</t>
+          <t>remusao/tldts</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>rust</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -22816,46 +22814,44 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>crates</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>libm</t>
+          <t>tldts</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
-        <v>35.23</v>
+        <v>44.92</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>71.15000000000001</v>
+        <v>63.59</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>54.15</v>
+      </c>
+      <c r="I254" s="3" t="n"/>
       <c r="J254" s="4" t="n">
-        <v>63.57</v>
+        <v>54.18</v>
       </c>
       <c r="K254" s="3" t="n">
-        <v>57.98</v>
+        <v>73.8</v>
       </c>
       <c r="L254" s="3" t="n">
-        <v>81.17</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="M254" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>44.21</v>
+        <v>81.3</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>56.79</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="P254" s="3" t="n">
-        <v>60.08</v>
+        <v>60.09</v>
       </c>
       <c r="Q254" s="5" t="inlineStr">
         <is>
@@ -22864,7 +22860,7 @@
       </c>
       <c r="R254" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S254" s="5" t="inlineStr">
@@ -22879,22 +22875,20 @@
       </c>
       <c r="U254" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V254" s="5" t="n">
-        <v>164</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V254" s="5" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>blakeembrey/change-case</t>
+          <t>rust-lang/compiler-builtins</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>rust</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -22904,46 +22898,46 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>crates</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>no-case</t>
+          <t>libm</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
-        <v>68.37</v>
+        <v>35.23</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>71.52</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>46.31</v>
+        <v>54.88</v>
       </c>
       <c r="I255" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J255" s="4" t="n">
-        <v>61.77</v>
+        <v>63.57</v>
       </c>
       <c r="K255" s="3" t="n">
-        <v>83.72</v>
+        <v>57.98</v>
       </c>
       <c r="L255" s="3" t="n">
-        <v>48.9</v>
+        <v>81.17</v>
       </c>
       <c r="M255" s="3" t="n">
-        <v>65.14</v>
+        <v>50</v>
       </c>
       <c r="N255" s="3" t="n">
-        <v>43.61</v>
+        <v>44.21</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>58.4</v>
+        <v>56.79</v>
       </c>
       <c r="P255" s="3" t="n">
-        <v>60.06</v>
+        <v>60.08</v>
       </c>
       <c r="Q255" s="5" t="inlineStr">
         <is>
@@ -22971,18 +22965,18 @@
         </is>
       </c>
       <c r="V255" s="5" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>selinuxproject/selinux</t>
+          <t>blakeembrey/change-case</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -22992,41 +22986,43 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>libselinux</t>
+          <t>no-case</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
-        <v>35.68</v>
+        <v>68.37</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>62.28</v>
+        <v>71.52</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="I256" s="3" t="n"/>
+        <v>46.31</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J256" s="4" t="n">
-        <v>58</v>
+        <v>61.77</v>
       </c>
       <c r="K256" s="3" t="n">
-        <v>38.44</v>
+        <v>83.72</v>
       </c>
       <c r="L256" s="3" t="n">
-        <v>93.55</v>
+        <v>48.9</v>
       </c>
       <c r="M256" s="3" t="n">
-        <v>50</v>
+        <v>65.14</v>
       </c>
       <c r="N256" s="3" t="n">
-        <v>83.23</v>
+        <v>43.61</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>62.2</v>
+        <v>58.4</v>
       </c>
       <c r="P256" s="3" t="n">
         <v>60.06</v>
@@ -23038,7 +23034,7 @@
       </c>
       <c r="R256" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S256" s="5" t="inlineStr">
@@ -23053,20 +23049,22 @@
       </c>
       <c r="U256" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V256" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V256" s="5" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>burntsushi/termcolor</t>
+          <t>selinuxproject/selinux</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>rust</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -23076,46 +23074,44 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>crates</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>termcolor</t>
+          <t>libselinux</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>44.44</v>
+        <v>35.68</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>74.39</v>
+        <v>62.28</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="I257" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="I257" s="3" t="n"/>
       <c r="J257" s="4" t="n">
-        <v>61.1</v>
+        <v>58</v>
       </c>
       <c r="K257" s="3" t="n">
-        <v>54.01</v>
+        <v>38.44</v>
       </c>
       <c r="L257" s="3" t="n">
-        <v>50.05</v>
+        <v>93.55</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>84.33</v>
+        <v>50</v>
       </c>
       <c r="N257" s="3" t="n">
-        <v>53.16</v>
+        <v>83.23</v>
       </c>
       <c r="O257" s="4" t="n">
-        <v>59</v>
+        <v>62.2</v>
       </c>
       <c r="P257" s="3" t="n">
-        <v>60.04</v>
+        <v>60.06</v>
       </c>
       <c r="Q257" s="5" t="inlineStr">
         <is>
@@ -23124,7 +23120,7 @@
       </c>
       <c r="R257" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S257" s="5" t="inlineStr">
@@ -23139,17 +23135,15 @@
       </c>
       <c r="U257" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V257" s="5" t="n">
-        <v>166</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V257" s="5" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>burntsushi/jiff</t>
+          <t>burntsushi/termcolor</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -23169,39 +23163,41 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>jiff</t>
+          <t>termcolor</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
-        <v>25.41</v>
+        <v>44.44</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>66.59</v>
+        <v>74.39</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>50.85</v>
-      </c>
-      <c r="I258" s="3" t="n"/>
+        <v>48.7</v>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J258" s="4" t="n">
-        <v>49.64</v>
+        <v>61.1</v>
       </c>
       <c r="K258" s="3" t="n">
-        <v>89.45999999999999</v>
+        <v>54.01</v>
       </c>
       <c r="L258" s="3" t="n">
-        <v>80.05</v>
+        <v>50.05</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>50</v>
+        <v>84.33</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>77.42</v>
+        <v>53.16</v>
       </c>
       <c r="O258" s="4" t="n">
-        <v>72.56</v>
+        <v>59</v>
       </c>
       <c r="P258" s="3" t="n">
-        <v>60.02</v>
+        <v>60.04</v>
       </c>
       <c r="Q258" s="5" t="inlineStr">
         <is>
@@ -23229,18 +23225,18 @@
         </is>
       </c>
       <c r="V258" s="5" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>ethers-io/ethers.js</t>
+          <t>burntsushi/jiff</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>typescript</t>
+          <t>rust</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -23250,41 +23246,41 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>crates</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>@ethersproject/logger</t>
+          <t>jiff</t>
         </is>
       </c>
       <c r="F259" s="3" t="n">
-        <v>29.37</v>
+        <v>25.41</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>58.12</v>
+        <v>66.59</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>39.06</v>
+        <v>50.85</v>
       </c>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="4" t="n">
-        <v>40.23</v>
+        <v>49.64</v>
       </c>
       <c r="K259" s="3" t="n">
-        <v>100</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L259" s="3" t="n">
-        <v>90.39</v>
+        <v>80.05</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="N259" s="3" t="n">
-        <v>91.95999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="O259" s="4" t="n">
-        <v>89.56</v>
+        <v>72.56</v>
       </c>
       <c r="P259" s="3" t="n">
         <v>60.02</v>
@@ -23315,60 +23311,62 @@
         </is>
       </c>
       <c r="V259" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>libidn/libidn2</t>
+          <t>ethers-io/ethers.js</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>typescript</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>libidn2</t>
+          <t>@ethersproject/logger</t>
         </is>
       </c>
       <c r="F260" s="3" t="n">
-        <v>30.93</v>
+        <v>29.37</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>58.62</v>
-      </c>
-      <c r="H260" s="3" t="n"/>
+        <v>58.12</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>39.06</v>
+      </c>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="4" t="n">
-        <v>44.77</v>
+        <v>40.23</v>
       </c>
       <c r="K260" s="3" t="n">
-        <v>90.77</v>
+        <v>100</v>
       </c>
       <c r="L260" s="3" t="n">
-        <v>71.95</v>
+        <v>90.39</v>
       </c>
       <c r="M260" s="3" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>82.89</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="O260" s="4" t="n">
-        <v>80.45999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="P260" s="3" t="n">
         <v>60.02</v>
@@ -23380,7 +23378,7 @@
       </c>
       <c r="R260" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S260" s="5" t="inlineStr">
@@ -23395,10 +23393,12 @@
       </c>
       <c r="U260" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V260" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V260" s="5" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -24793,61 +24793,57 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>acornjs/acorn</t>
+          <t>holmgren/nettle</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>acorn</t>
+          <t>nettle</t>
         </is>
       </c>
       <c r="F277" s="3" t="n">
-        <v>64.48</v>
+        <v>28.77</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="H277" s="3" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I277" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>56.71</v>
+      </c>
+      <c r="H277" s="3" t="n"/>
+      <c r="I277" s="3" t="n"/>
       <c r="J277" s="4" t="n">
-        <v>69.34</v>
+        <v>42.74</v>
       </c>
       <c r="K277" s="3" t="n">
-        <v>36.01</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="L277" s="3" t="n">
-        <v>88.09</v>
+        <v>90.03</v>
       </c>
       <c r="M277" s="3" t="n">
-        <v>50</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="N277" s="3" t="n">
-        <v>43.38</v>
+        <v>71.42</v>
       </c>
       <c r="O277" s="4" t="n">
-        <v>51.22</v>
+        <v>83.13</v>
       </c>
       <c r="P277" s="3" t="n">
-        <v>59.6</v>
+        <v>59.61</v>
       </c>
       <c r="Q277" s="5" t="inlineStr">
         <is>
@@ -24881,7 +24877,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>kriskowal/asap</t>
+          <t>acornjs/acorn</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -24901,38 +24897,38 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>asap</t>
+          <t>acorn</t>
         </is>
       </c>
       <c r="F278" s="3" t="n">
-        <v>29.13</v>
+        <v>64.48</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>58.01</v>
+        <v>70.02</v>
       </c>
       <c r="H278" s="3" t="n">
-        <v>35.93</v>
+        <v>59.82</v>
       </c>
       <c r="I278" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J278" s="4" t="n">
-        <v>50.27</v>
+        <v>69.34</v>
       </c>
       <c r="K278" s="3" t="n">
-        <v>70.70999999999999</v>
+        <v>36.01</v>
       </c>
       <c r="L278" s="3" t="n">
-        <v>46.69</v>
+        <v>88.09</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>88.06</v>
+        <v>50</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>85.79000000000001</v>
+        <v>43.38</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>70.67</v>
+        <v>51.22</v>
       </c>
       <c r="P278" s="3" t="n">
         <v>59.6</v>
@@ -24944,7 +24940,7 @@
       </c>
       <c r="R278" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S278" s="5" t="inlineStr">
@@ -24959,65 +24955,71 @@
       </c>
       <c r="U278" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V278" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V278" s="5" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>holmgren/nettle</t>
+          <t>kriskowal/asap</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>nettle</t>
+          <t>asap</t>
         </is>
       </c>
       <c r="F279" s="3" t="n">
-        <v>28.71</v>
+        <v>29.13</v>
       </c>
       <c r="G279" s="3" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="H279" s="3" t="n"/>
-      <c r="I279" s="3" t="n"/>
+        <v>58.01</v>
+      </c>
+      <c r="H279" s="3" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="I279" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J279" s="4" t="n">
-        <v>42.71</v>
+        <v>50.27</v>
       </c>
       <c r="K279" s="3" t="n">
-        <v>84.70999999999999</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="L279" s="3" t="n">
-        <v>90.03</v>
+        <v>46.69</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>87.68000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>71.42</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>83.13</v>
+        <v>70.67</v>
       </c>
       <c r="P279" s="3" t="n">
-        <v>59.59</v>
+        <v>59.6</v>
       </c>
       <c r="Q279" s="5" t="inlineStr">
         <is>
@@ -25026,7 +25028,7 @@
       </c>
       <c r="R279" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S279" s="5" t="inlineStr">
@@ -25041,12 +25043,10 @@
       </c>
       <c r="U279" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V279" s="5" t="n">
-        <v>180</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V279" s="5" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -27423,7 +27423,7 @@
         </is>
       </c>
       <c r="F307" s="3" t="n">
-        <v>25.87</v>
+        <v>25.93</v>
       </c>
       <c r="G307" s="3" t="n">
         <v>55.36</v>
@@ -27433,7 +27433,7 @@
       </c>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="4" t="n">
-        <v>60.91</v>
+        <v>60.92</v>
       </c>
       <c r="K307" s="3" t="n">
         <v>15.71</v>
@@ -29251,7 +29251,7 @@
         </is>
       </c>
       <c r="F328" s="3" t="n">
-        <v>29.64</v>
+        <v>29.87</v>
       </c>
       <c r="G328" s="3" t="n">
         <v>57.99</v>
@@ -29263,7 +29263,7 @@
         <v>0</v>
       </c>
       <c r="J328" s="4" t="n">
-        <v>42.63</v>
+        <v>42.66</v>
       </c>
       <c r="K328" s="3" t="n">
         <v>65.59999999999999</v>
@@ -29281,7 +29281,7 @@
         <v>80.20999999999999</v>
       </c>
       <c r="P328" s="3" t="n">
-        <v>58.48</v>
+        <v>58.5</v>
       </c>
       <c r="Q328" s="5" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         </is>
       </c>
       <c r="F345" s="3" t="n">
-        <v>25.19</v>
+        <v>25.25</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>54.71</v>
@@ -30745,7 +30745,7 @@
       </c>
       <c r="I345" s="3" t="n"/>
       <c r="J345" s="4" t="n">
-        <v>48.15</v>
+        <v>48.16</v>
       </c>
       <c r="K345" s="3" t="n">
         <v>39.1</v>
@@ -31411,58 +31411,54 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>isaacs/node-lru-cache</t>
+          <t>gnutls/libtasn1</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>lru-cache</t>
+          <t>libtasn1</t>
         </is>
       </c>
       <c r="F353" s="3" t="n">
-        <v>67.47</v>
+        <v>26.07</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="H353" s="3" t="n">
-        <v>54.45</v>
-      </c>
-      <c r="I353" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>55.38</v>
+      </c>
+      <c r="H353" s="3" t="n"/>
+      <c r="I353" s="3" t="n"/>
       <c r="J353" s="4" t="n">
-        <v>66.52</v>
+        <v>40.73</v>
       </c>
       <c r="K353" s="3" t="n">
-        <v>92.18000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="L353" s="3" t="n">
-        <v>58.5</v>
+        <v>81.22</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>50</v>
+        <v>79.53</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>24.04</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>50.46</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="P353" s="3" t="n">
         <v>57.94</v>
@@ -31474,7 +31470,7 @@
       </c>
       <c r="R353" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S353" s="5" t="inlineStr">
@@ -31489,17 +31485,15 @@
       </c>
       <c r="U353" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V353" s="5" t="n">
-        <v>229</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V353" s="5" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>fitzgen/glob-to-regexp</t>
+          <t>isaacs/node-lru-cache</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -31519,41 +31513,41 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>glob-to-regexp</t>
+          <t>lru-cache</t>
         </is>
       </c>
       <c r="F354" s="3" t="n">
-        <v>26.77</v>
+        <v>67.47</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>57.32</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="H354" s="3" t="n">
-        <v>29.38</v>
+        <v>54.45</v>
       </c>
       <c r="I354" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J354" s="4" t="n">
-        <v>46.04</v>
+        <v>66.52</v>
       </c>
       <c r="K354" s="3" t="n">
-        <v>100</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="L354" s="3" t="n">
-        <v>42.04</v>
+        <v>58.5</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>95.73999999999999</v>
+        <v>50</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>70.02</v>
+        <v>24.04</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>72.86</v>
+        <v>50.46</v>
       </c>
       <c r="P354" s="3" t="n">
-        <v>57.92</v>
+        <v>57.94</v>
       </c>
       <c r="Q354" s="5" t="inlineStr">
         <is>
@@ -31562,7 +31556,7 @@
       </c>
       <c r="R354" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S354" s="5" t="inlineStr">
@@ -31572,67 +31566,73 @@
       </c>
       <c r="T354" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U354" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V354" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V354" s="5" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>gnutls/libtasn1</t>
+          <t>fitzgen/glob-to-regexp</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>libtasn1</t>
+          <t>glob-to-regexp</t>
         </is>
       </c>
       <c r="F355" s="3" t="n">
-        <v>26.01</v>
+        <v>26.77</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="H355" s="3" t="n"/>
-      <c r="I355" s="3" t="n"/>
+        <v>57.32</v>
+      </c>
+      <c r="H355" s="3" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="I355" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J355" s="4" t="n">
-        <v>40.7</v>
+        <v>46.04</v>
       </c>
       <c r="K355" s="3" t="n">
-        <v>86.69</v>
+        <v>100</v>
       </c>
       <c r="L355" s="3" t="n">
-        <v>81.22</v>
+        <v>42.04</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>79.53</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>82.45999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>82.43000000000001</v>
+        <v>72.86</v>
       </c>
       <c r="P355" s="3" t="n">
         <v>57.92</v>
@@ -31654,7 +31654,7 @@
       </c>
       <c r="T355" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="U355" s="6" t="inlineStr">
@@ -32825,7 +32825,7 @@
         </is>
       </c>
       <c r="F369" s="3" t="n">
-        <v>25.06</v>
+        <v>25.12</v>
       </c>
       <c r="G369" s="3" t="n">
         <v>54.69</v>
@@ -32835,7 +32835,7 @@
       </c>
       <c r="I369" s="3" t="n"/>
       <c r="J369" s="4" t="n">
-        <v>50.68</v>
+        <v>50.69</v>
       </c>
       <c r="K369" s="3" t="n">
         <v>63.91</v>
@@ -32853,7 +32853,7 @@
         <v>65.09</v>
       </c>
       <c r="P369" s="3" t="n">
-        <v>57.43</v>
+        <v>57.44</v>
       </c>
       <c r="Q369" s="5" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="F372" s="3" t="n">
-        <v>27.22</v>
+        <v>27.28</v>
       </c>
       <c r="G372" s="3" t="n">
         <v>56.08</v>
@@ -33097,7 +33097,7 @@
         <v>0</v>
       </c>
       <c r="J372" s="4" t="n">
-        <v>39.47</v>
+        <v>39.48</v>
       </c>
       <c r="K372" s="3" t="n">
         <v>84.81999999999999</v>
@@ -33115,7 +33115,7 @@
         <v>83.25</v>
       </c>
       <c r="P372" s="3" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="Q372" s="5" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         </is>
       </c>
       <c r="F429" s="3" t="n">
-        <v>28.54</v>
+        <v>28.6</v>
       </c>
       <c r="G429" s="3" t="n">
         <v>56.61</v>
@@ -41253,61 +41253,57 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>watson/ci-info</t>
+          <t>debian/gdbm</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>ci-info</t>
+          <t>gdbm</t>
         </is>
       </c>
       <c r="F466" s="3" t="n">
-        <v>45.1</v>
+        <v>27.76</v>
       </c>
       <c r="G466" s="3" t="n">
-        <v>63.62</v>
-      </c>
-      <c r="H466" s="3" t="n">
-        <v>47.91</v>
-      </c>
-      <c r="I466" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>56.26</v>
+      </c>
+      <c r="H466" s="3" t="n"/>
+      <c r="I466" s="3" t="n"/>
       <c r="J466" s="4" t="n">
-        <v>59.62</v>
+        <v>42.01</v>
       </c>
       <c r="K466" s="3" t="n">
-        <v>57.3</v>
+        <v>83.2</v>
       </c>
       <c r="L466" s="3" t="n">
-        <v>32.9</v>
+        <v>83.98</v>
       </c>
       <c r="M466" s="3" t="n">
-        <v>86.34999999999999</v>
+        <v>59.38</v>
       </c>
       <c r="N466" s="3" t="n">
-        <v>40.93</v>
+        <v>65.25</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>50.81</v>
+        <v>72.13</v>
       </c>
       <c r="P466" s="3" t="n">
-        <v>55.04</v>
+        <v>55.05</v>
       </c>
       <c r="Q466" s="5" t="inlineStr">
         <is>
@@ -41341,57 +41337,61 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>debian/gdbm</t>
+          <t>watson/ci-info</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>gdbm</t>
+          <t>ci-info</t>
         </is>
       </c>
       <c r="F467" s="3" t="n">
-        <v>27.7</v>
+        <v>45.1</v>
       </c>
       <c r="G467" s="3" t="n">
-        <v>56.26</v>
-      </c>
-      <c r="H467" s="3" t="n"/>
-      <c r="I467" s="3" t="n"/>
+        <v>63.62</v>
+      </c>
+      <c r="H467" s="3" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="I467" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J467" s="4" t="n">
-        <v>41.98</v>
+        <v>59.62</v>
       </c>
       <c r="K467" s="3" t="n">
-        <v>83.2</v>
+        <v>57.3</v>
       </c>
       <c r="L467" s="3" t="n">
-        <v>83.98</v>
+        <v>32.9</v>
       </c>
       <c r="M467" s="3" t="n">
-        <v>59.38</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="N467" s="3" t="n">
-        <v>65.25</v>
+        <v>40.93</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>72.13</v>
+        <v>50.81</v>
       </c>
       <c r="P467" s="3" t="n">
-        <v>55.03</v>
+        <v>55.04</v>
       </c>
       <c r="Q467" s="5" t="inlineStr">
         <is>
@@ -41863,61 +41863,57 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>yuzujs/setimmediate</t>
+          <t>xorg/lib/libxext</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>setimmediate</t>
+          <t>libxext</t>
         </is>
       </c>
       <c r="F473" s="3" t="n">
-        <v>25.16</v>
+        <v>31.39</v>
       </c>
       <c r="G473" s="3" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="H473" s="3" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="I473" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>58.63</v>
+      </c>
+      <c r="H473" s="3" t="n"/>
+      <c r="I473" s="3" t="n"/>
       <c r="J473" s="4" t="n">
-        <v>44.87</v>
+        <v>45.01</v>
       </c>
       <c r="K473" s="3" t="n">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="L473" s="3" t="n">
-        <v>29.36</v>
+        <v>61.94</v>
       </c>
       <c r="M473" s="3" t="n">
-        <v>92.75</v>
+        <v>52.35</v>
       </c>
       <c r="N473" s="3" t="n">
-        <v>74.36</v>
+        <v>69.52</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>67.08</v>
+        <v>67.02</v>
       </c>
       <c r="P473" s="3" t="n">
-        <v>54.86</v>
+        <v>54.92</v>
       </c>
       <c r="Q473" s="5" t="inlineStr">
         <is>
@@ -41926,7 +41922,7 @@
       </c>
       <c r="R473" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S473" s="5" t="inlineStr">
@@ -41941,15 +41937,17 @@
       </c>
       <c r="U473" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V473" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V473" s="5" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>alexindigo/asynckit</t>
+          <t>yuzujs/setimmediate</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -41969,41 +41967,41 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>asynckit</t>
+          <t>setimmediate</t>
         </is>
       </c>
       <c r="F474" s="3" t="n">
-        <v>36.12</v>
+        <v>25.16</v>
       </c>
       <c r="G474" s="3" t="n">
-        <v>60.62</v>
+        <v>56.69</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>24.52</v>
+        <v>27.81</v>
       </c>
       <c r="I474" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J474" s="4" t="n">
-        <v>44.39</v>
+        <v>44.87</v>
       </c>
       <c r="K474" s="3" t="n">
-        <v>74.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="L474" s="3" t="n">
-        <v>38.71</v>
+        <v>29.36</v>
       </c>
       <c r="M474" s="3" t="n">
-        <v>97.33</v>
+        <v>92.75</v>
       </c>
       <c r="N474" s="3" t="n">
-        <v>75.12</v>
+        <v>74.36</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>67.77</v>
+        <v>67.08</v>
       </c>
       <c r="P474" s="3" t="n">
-        <v>54.85</v>
+        <v>54.86</v>
       </c>
       <c r="Q474" s="5" t="inlineStr">
         <is>
@@ -42035,54 +42033,58 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>xorg/lib/libxext</t>
+          <t>alexindigo/asynckit</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>libxext</t>
+          <t>asynckit</t>
         </is>
       </c>
       <c r="F475" s="3" t="n">
-        <v>31.16</v>
+        <v>36.12</v>
       </c>
       <c r="G475" s="3" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="H475" s="3" t="n"/>
-      <c r="I475" s="3" t="n"/>
+        <v>60.62</v>
+      </c>
+      <c r="H475" s="3" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="I475" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J475" s="4" t="n">
-        <v>44.89</v>
+        <v>44.39</v>
       </c>
       <c r="K475" s="3" t="n">
-        <v>89.5</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="L475" s="3" t="n">
-        <v>61.94</v>
+        <v>38.71</v>
       </c>
       <c r="M475" s="3" t="n">
-        <v>52.35</v>
+        <v>97.33</v>
       </c>
       <c r="N475" s="3" t="n">
-        <v>69.52</v>
+        <v>75.12</v>
       </c>
       <c r="O475" s="4" t="n">
-        <v>67.02</v>
+        <v>67.77</v>
       </c>
       <c r="P475" s="3" t="n">
         <v>54.85</v>
@@ -42094,7 +42096,7 @@
       </c>
       <c r="R475" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S475" s="5" t="inlineStr">
@@ -42109,12 +42111,10 @@
       </c>
       <c r="U475" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V475" s="5" t="n">
-        <v>310</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V475" s="5" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -42557,12 +42557,12 @@
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>jprichardson/node-fs-extra</t>
+          <t>libuv/libuv</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -42572,46 +42572,46 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>fs-extra</t>
+          <t>libuv</t>
         </is>
       </c>
       <c r="F481" s="3" t="n">
-        <v>46.84</v>
+        <v>29.12</v>
       </c>
       <c r="G481" s="3" t="n">
-        <v>63.99</v>
+        <v>56.97</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>52.87</v>
+        <v>61.73</v>
       </c>
       <c r="I481" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J481" s="4" t="n">
-        <v>62.81</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="K481" s="3" t="n">
-        <v>65.66</v>
+        <v>15.8</v>
       </c>
       <c r="L481" s="3" t="n">
-        <v>51.68</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="M481" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N481" s="3" t="n">
-        <v>30.58</v>
+        <v>62.72</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>47.73</v>
+        <v>45.68</v>
       </c>
       <c r="P481" s="3" t="n">
-        <v>54.75</v>
+        <v>54.76</v>
       </c>
       <c r="Q481" s="5" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
       </c>
       <c r="R481" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S481" s="5" t="inlineStr">
@@ -42635,15 +42635,17 @@
       </c>
       <c r="U481" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V481" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V481" s="5" t="n">
+        <v>315</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>jshttp/negotiator</t>
+          <t>jprichardson/node-fs-extra</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -42663,38 +42665,38 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>negotiator</t>
+          <t>fs-extra</t>
         </is>
       </c>
       <c r="F482" s="3" t="n">
-        <v>36.91</v>
+        <v>46.84</v>
       </c>
       <c r="G482" s="3" t="n">
-        <v>60.88</v>
+        <v>63.99</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>44.58</v>
+        <v>52.87</v>
       </c>
       <c r="I482" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J482" s="4" t="n">
-        <v>56.53</v>
+        <v>62.81</v>
       </c>
       <c r="K482" s="3" t="n">
-        <v>64.55</v>
+        <v>65.66</v>
       </c>
       <c r="L482" s="3" t="n">
-        <v>42.65</v>
+        <v>51.68</v>
       </c>
       <c r="M482" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N482" s="3" t="n">
-        <v>57.46</v>
+        <v>30.58</v>
       </c>
       <c r="O482" s="4" t="n">
-        <v>53.03</v>
+        <v>47.73</v>
       </c>
       <c r="P482" s="3" t="n">
         <v>54.75</v>
@@ -42706,7 +42708,7 @@
       </c>
       <c r="R482" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S482" s="5" t="inlineStr">
@@ -42721,22 +42723,20 @@
       </c>
       <c r="U482" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V482" s="5" t="n">
-        <v>315</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V482" s="5" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>libuv/libuv</t>
+          <t>jshttp/negotiator</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -42746,43 +42746,43 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>libuv</t>
+          <t>negotiator</t>
         </is>
       </c>
       <c r="F483" s="3" t="n">
-        <v>28.88</v>
+        <v>36.91</v>
       </c>
       <c r="G483" s="3" t="n">
-        <v>56.97</v>
+        <v>60.88</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>61.73</v>
+        <v>44.58</v>
       </c>
       <c r="I483" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>65.62</v>
+        <v>56.53</v>
       </c>
       <c r="K483" s="3" t="n">
-        <v>15.8</v>
+        <v>64.55</v>
       </c>
       <c r="L483" s="3" t="n">
-        <v>87.84999999999999</v>
+        <v>42.65</v>
       </c>
       <c r="M483" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N483" s="3" t="n">
-        <v>62.72</v>
+        <v>57.46</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>45.68</v>
+        <v>53.03</v>
       </c>
       <c r="P483" s="3" t="n">
         <v>54.75</v>
@@ -45121,7 +45121,7 @@
         </is>
       </c>
       <c r="F510" s="3" t="n">
-        <v>28.37</v>
+        <v>28.43</v>
       </c>
       <c r="G510" s="3" t="n">
         <v>56.52</v>
@@ -45131,7 +45131,7 @@
       </c>
       <c r="I510" s="3" t="n"/>
       <c r="J510" s="4" t="n">
-        <v>50.27</v>
+        <v>50.28</v>
       </c>
       <c r="K510" s="3" t="n">
         <v>21.76</v>
@@ -48937,12 +48937,12 @@
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>sindresorhus/p-limit</t>
+          <t>freedesktop-unofficial-mirror/cairo</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -48952,46 +48952,44 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>p-limit</t>
+          <t>cairo-graphics-library</t>
         </is>
       </c>
       <c r="F554" s="3" t="n">
-        <v>71.72</v>
+        <v>31.62</v>
       </c>
       <c r="G554" s="3" t="n">
-        <v>72.62</v>
+        <v>58.68</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I554" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>27.16</v>
+      </c>
+      <c r="I554" s="3" t="n"/>
       <c r="J554" s="4" t="n">
-        <v>61.64</v>
+        <v>31.66</v>
       </c>
       <c r="K554" s="3" t="n">
-        <v>71.34</v>
+        <v>100</v>
       </c>
       <c r="L554" s="3" t="n">
-        <v>23.55</v>
+        <v>92.78</v>
       </c>
       <c r="M554" s="3" t="n">
-        <v>50</v>
+        <v>98.08</v>
       </c>
       <c r="N554" s="3" t="n">
-        <v>49.55</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="O554" s="4" t="n">
-        <v>45.17</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="P554" s="3" t="n">
-        <v>52.77</v>
+        <v>52.79</v>
       </c>
       <c r="Q554" s="5" t="inlineStr">
         <is>
@@ -49025,12 +49023,12 @@
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>freedesktop-unofficial-mirror/cairo</t>
+          <t>sindresorhus/p-limit</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -49040,44 +49038,46 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>cairo-graphics-library</t>
+          <t>p-limit</t>
         </is>
       </c>
       <c r="F555" s="3" t="n">
-        <v>31.38</v>
+        <v>71.72</v>
       </c>
       <c r="G555" s="3" t="n">
-        <v>58.68</v>
+        <v>72.62</v>
       </c>
       <c r="H555" s="3" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="I555" s="3" t="n"/>
+        <v>45.34</v>
+      </c>
+      <c r="I555" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J555" s="4" t="n">
-        <v>31.63</v>
+        <v>61.64</v>
       </c>
       <c r="K555" s="3" t="n">
-        <v>100</v>
+        <v>71.34</v>
       </c>
       <c r="L555" s="3" t="n">
-        <v>92.78</v>
+        <v>23.55</v>
       </c>
       <c r="M555" s="3" t="n">
-        <v>98.08</v>
+        <v>50</v>
       </c>
       <c r="N555" s="3" t="n">
-        <v>65.93000000000001</v>
+        <v>49.55</v>
       </c>
       <c r="O555" s="4" t="n">
-        <v>88.01000000000001</v>
+        <v>45.17</v>
       </c>
       <c r="P555" s="3" t="n">
-        <v>52.76</v>
+        <v>52.77</v>
       </c>
       <c r="Q555" s="5" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         </is>
       </c>
       <c r="F558" s="3" t="n">
-        <v>30.71</v>
+        <v>30.95</v>
       </c>
       <c r="G558" s="3" t="n">
         <v>58.54</v>
@@ -49321,7 +49321,7 @@
         <v>0</v>
       </c>
       <c r="J558" s="4" t="n">
-        <v>40.46</v>
+        <v>40.48</v>
       </c>
       <c r="K558" s="3" t="n">
         <v>80.59</v>
@@ -49339,7 +49339,7 @@
         <v>68.61</v>
       </c>
       <c r="P558" s="3" t="n">
-        <v>52.69</v>
+        <v>52.7</v>
       </c>
       <c r="Q558" s="5" t="inlineStr">
         <is>
@@ -50507,12 +50507,12 @@
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>realpython/pytest-mypy</t>
+          <t>autotools-mirror/libtool</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -50522,41 +50522,41 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>pytest-mypy</t>
+          <t>libtool</t>
         </is>
       </c>
       <c r="F572" s="3" t="n">
-        <v>43.73</v>
+        <v>26.81</v>
       </c>
       <c r="G572" s="3" t="n">
-        <v>74.45</v>
+        <v>55.93</v>
       </c>
       <c r="H572" s="3" t="n">
-        <v>43.41</v>
+        <v>47.21</v>
       </c>
       <c r="I572" s="3" t="n"/>
       <c r="J572" s="4" t="n">
-        <v>47.33</v>
+        <v>45.75</v>
       </c>
       <c r="K572" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>53.99</v>
       </c>
       <c r="L572" s="3" t="n">
-        <v>42.39</v>
+        <v>69.61</v>
       </c>
       <c r="M572" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N572" s="3" t="n">
-        <v>35.73</v>
+        <v>42.43</v>
       </c>
       <c r="O572" s="4" t="n">
-        <v>58.2</v>
+        <v>60.19</v>
       </c>
       <c r="P572" s="3" t="n">
         <v>52.48</v>
@@ -50568,7 +50568,7 @@
       </c>
       <c r="R572" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S572" s="5" t="inlineStr">
@@ -50583,20 +50583,22 @@
       </c>
       <c r="U572" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V572" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V572" s="5" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>autotools-mirror/libtool</t>
+          <t>realpython/pytest-mypy</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -50606,44 +50608,44 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>libtool</t>
+          <t>pytest-mypy</t>
         </is>
       </c>
       <c r="F573" s="3" t="n">
-        <v>26.75</v>
+        <v>43.73</v>
       </c>
       <c r="G573" s="3" t="n">
-        <v>55.93</v>
+        <v>74.45</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>47.21</v>
+        <v>43.41</v>
       </c>
       <c r="I573" s="3" t="n"/>
       <c r="J573" s="4" t="n">
-        <v>45.74</v>
+        <v>47.33</v>
       </c>
       <c r="K573" s="3" t="n">
-        <v>53.99</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L573" s="3" t="n">
-        <v>69.61</v>
+        <v>42.39</v>
       </c>
       <c r="M573" s="3" t="n">
-        <v>82.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N573" s="3" t="n">
-        <v>42.43</v>
+        <v>35.73</v>
       </c>
       <c r="O573" s="4" t="n">
-        <v>60.19</v>
+        <v>58.2</v>
       </c>
       <c r="P573" s="3" t="n">
-        <v>52.47</v>
+        <v>52.48</v>
       </c>
       <c r="Q573" s="5" t="inlineStr">
         <is>
@@ -50652,7 +50654,7 @@
       </c>
       <c r="R573" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S573" s="5" t="inlineStr">
@@ -50667,12 +50669,10 @@
       </c>
       <c r="U573" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V573" s="5" t="n">
-        <v>384</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V573" s="5" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -53287,61 +53287,57 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>burntsushi/quickcheck</t>
+          <t>debian/giflib</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>rust</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>crates</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>quickcheck</t>
+          <t>giflib</t>
         </is>
       </c>
       <c r="F604" s="3" t="n">
-        <v>57.52</v>
+        <v>27.12</v>
       </c>
       <c r="G604" s="3" t="n">
-        <v>77.59</v>
-      </c>
-      <c r="H604" s="3" t="n">
-        <v>49.21</v>
-      </c>
-      <c r="I604" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>56.01</v>
+      </c>
+      <c r="H604" s="3" t="n"/>
+      <c r="I604" s="3" t="n"/>
       <c r="J604" s="4" t="n">
-        <v>63.04</v>
+        <v>41.57</v>
       </c>
       <c r="K604" s="3" t="n">
-        <v>29.42</v>
+        <v>35.54</v>
       </c>
       <c r="L604" s="3" t="n">
-        <v>33.9</v>
+        <v>76.53</v>
       </c>
       <c r="M604" s="3" t="n">
-        <v>50</v>
+        <v>92.03</v>
       </c>
       <c r="N604" s="3" t="n">
-        <v>64.45</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="O604" s="4" t="n">
-        <v>42.34</v>
+        <v>64.23</v>
       </c>
       <c r="P604" s="3" t="n">
-        <v>51.66</v>
+        <v>51.67</v>
       </c>
       <c r="Q604" s="5" t="inlineStr">
         <is>
@@ -53375,12 +53371,12 @@
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>jonschlinkert/has-values</t>
+          <t>burntsushi/quickcheck</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>rust</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -53390,43 +53386,43 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>crates</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>has-values</t>
+          <t>quickcheck</t>
         </is>
       </c>
       <c r="F605" s="3" t="n">
-        <v>33.41</v>
+        <v>57.52</v>
       </c>
       <c r="G605" s="3" t="n">
-        <v>59.56</v>
+        <v>77.59</v>
       </c>
       <c r="H605" s="3" t="n">
-        <v>22.27</v>
+        <v>49.21</v>
       </c>
       <c r="I605" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J605" s="4" t="n">
-        <v>42.66</v>
+        <v>63.04</v>
       </c>
       <c r="K605" s="3" t="n">
-        <v>100</v>
+        <v>29.42</v>
       </c>
       <c r="L605" s="3" t="n">
-        <v>28.28</v>
+        <v>33.9</v>
       </c>
       <c r="M605" s="3" t="n">
-        <v>92.75</v>
+        <v>50</v>
       </c>
       <c r="N605" s="3" t="n">
-        <v>58.37</v>
+        <v>64.45</v>
       </c>
       <c r="O605" s="4" t="n">
-        <v>62.55</v>
+        <v>42.34</v>
       </c>
       <c r="P605" s="3" t="n">
         <v>51.66</v>
@@ -53463,57 +53459,61 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>debian/giflib</t>
+          <t>jonschlinkert/has-values</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>giflib</t>
+          <t>has-values</t>
         </is>
       </c>
       <c r="F606" s="3" t="n">
-        <v>27.06</v>
+        <v>33.41</v>
       </c>
       <c r="G606" s="3" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="H606" s="3" t="n"/>
-      <c r="I606" s="3" t="n"/>
+        <v>59.56</v>
+      </c>
+      <c r="H606" s="3" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="I606" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J606" s="4" t="n">
-        <v>41.54</v>
+        <v>42.66</v>
       </c>
       <c r="K606" s="3" t="n">
-        <v>35.54</v>
+        <v>100</v>
       </c>
       <c r="L606" s="3" t="n">
-        <v>76.53</v>
+        <v>28.28</v>
       </c>
       <c r="M606" s="3" t="n">
-        <v>92.03</v>
+        <v>92.75</v>
       </c>
       <c r="N606" s="3" t="n">
-        <v>68.01000000000001</v>
+        <v>58.37</v>
       </c>
       <c r="O606" s="4" t="n">
-        <v>64.23</v>
+        <v>62.55</v>
       </c>
       <c r="P606" s="3" t="n">
-        <v>51.65</v>
+        <v>51.66</v>
       </c>
       <c r="Q606" s="5" t="inlineStr">
         <is>
@@ -55025,64 +55025,60 @@
         </is>
       </c>
       <c r="V623" s="5" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>tox-dev/platformdirs</t>
+          <t>pixman/pixman</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>platformdirs</t>
+          <t>pixman</t>
         </is>
       </c>
       <c r="F624" s="3" t="n">
-        <v>45.05</v>
+        <v>25.51</v>
       </c>
       <c r="G624" s="3" t="n">
-        <v>74.54000000000001</v>
-      </c>
-      <c r="H624" s="3" t="n">
-        <v>54.26</v>
-      </c>
-      <c r="I624" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>54.76</v>
+      </c>
+      <c r="H624" s="3" t="n"/>
+      <c r="I624" s="3" t="n"/>
       <c r="J624" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>40.14</v>
       </c>
       <c r="K624" s="3" t="n">
-        <v>31.42</v>
+        <v>28.99</v>
       </c>
       <c r="L624" s="3" t="n">
-        <v>43.71</v>
+        <v>85.12</v>
       </c>
       <c r="M624" s="3" t="n">
-        <v>50</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="N624" s="3" t="n">
-        <v>38.6</v>
+        <v>81.73</v>
       </c>
       <c r="O624" s="4" t="n">
-        <v>40.35</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="P624" s="3" t="n">
         <v>51.02</v>
@@ -55119,12 +55115,12 @@
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>react/metro</t>
+          <t>tox-dev/platformdirs</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -55134,44 +55130,46 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>metro-source-map</t>
+          <t>platformdirs</t>
         </is>
       </c>
       <c r="F625" s="3" t="n">
-        <v>30.16</v>
+        <v>45.05</v>
       </c>
       <c r="G625" s="3" t="n">
-        <v>58.38</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="H625" s="3" t="n">
-        <v>52.62</v>
-      </c>
-      <c r="I625" s="3" t="n"/>
+        <v>54.26</v>
+      </c>
+      <c r="I625" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J625" s="4" t="n">
-        <v>50.53</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="K625" s="3" t="n">
-        <v>21.1</v>
+        <v>31.42</v>
       </c>
       <c r="L625" s="3" t="n">
-        <v>86.48</v>
+        <v>43.71</v>
       </c>
       <c r="M625" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N625" s="3" t="n">
-        <v>77.04000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="O625" s="4" t="n">
-        <v>51.49</v>
+        <v>40.35</v>
       </c>
       <c r="P625" s="3" t="n">
-        <v>51.01</v>
+        <v>51.02</v>
       </c>
       <c r="Q625" s="5" t="inlineStr">
         <is>
@@ -55185,7 +55183,7 @@
       </c>
       <c r="S625" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T625" s="5" t="inlineStr">
@@ -55195,65 +55193,69 @@
       </c>
       <c r="U625" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V625" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V625" s="5" t="n">
+        <v>421</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>pixman/pixman</t>
+          <t>react/metro</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>pixman</t>
+          <t>metro-source-map</t>
         </is>
       </c>
       <c r="F626" s="3" t="n">
-        <v>25.45</v>
+        <v>30.16</v>
       </c>
       <c r="G626" s="3" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="H626" s="3" t="n"/>
+        <v>58.38</v>
+      </c>
+      <c r="H626" s="3" t="n">
+        <v>52.62</v>
+      </c>
       <c r="I626" s="3" t="n"/>
       <c r="J626" s="4" t="n">
-        <v>40.11</v>
+        <v>50.53</v>
       </c>
       <c r="K626" s="3" t="n">
-        <v>28.99</v>
+        <v>21.1</v>
       </c>
       <c r="L626" s="3" t="n">
-        <v>85.12</v>
+        <v>86.48</v>
       </c>
       <c r="M626" s="3" t="n">
-        <v>87.68000000000001</v>
+        <v>50</v>
       </c>
       <c r="N626" s="3" t="n">
-        <v>81.73</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="O626" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>51.49</v>
       </c>
       <c r="P626" s="3" t="n">
-        <v>51</v>
+        <v>51.01</v>
       </c>
       <c r="Q626" s="5" t="inlineStr">
         <is>
@@ -55267,7 +55269,7 @@
       </c>
       <c r="S626" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T626" s="5" t="inlineStr">
@@ -55277,12 +55279,10 @@
       </c>
       <c r="U626" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V626" s="5" t="n">
-        <v>422</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V626" s="5" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -56855,61 +56855,57 @@
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
         <is>
-          <t>zesterer/spin-rs</t>
+          <t>gnome/gdk-pixbuf</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>rust</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>crates</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>spin</t>
+          <t>gdk-pixbuf</t>
         </is>
       </c>
       <c r="F645" s="3" t="n">
-        <v>29.57</v>
+        <v>25.38</v>
       </c>
       <c r="G645" s="3" t="n">
-        <v>68.55</v>
-      </c>
-      <c r="H645" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I645" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>54.76</v>
+      </c>
+      <c r="H645" s="3" t="n"/>
+      <c r="I645" s="3" t="n"/>
       <c r="J645" s="4" t="n">
-        <v>53.81</v>
+        <v>40.07</v>
       </c>
       <c r="K645" s="3" t="n">
-        <v>28.84</v>
+        <v>31.73</v>
       </c>
       <c r="L645" s="3" t="n">
-        <v>41.53</v>
+        <v>81.98</v>
       </c>
       <c r="M645" s="3" t="n">
-        <v>82.37</v>
+        <v>92.75</v>
       </c>
       <c r="N645" s="3" t="n">
-        <v>50.78</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="O645" s="4" t="n">
-        <v>47.31</v>
+        <v>63.57</v>
       </c>
       <c r="P645" s="3" t="n">
-        <v>50.46</v>
+        <v>50.47</v>
       </c>
       <c r="Q645" s="5" t="inlineStr">
         <is>
@@ -56943,57 +56939,61 @@
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
         <is>
-          <t>gnome/gdk-pixbuf</t>
+          <t>zesterer/spin-rs</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>rust</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>crates</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>gdk-pixbuf</t>
+          <t>spin</t>
         </is>
       </c>
       <c r="F646" s="3" t="n">
-        <v>25.32</v>
+        <v>29.57</v>
       </c>
       <c r="G646" s="3" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="H646" s="3" t="n"/>
-      <c r="I646" s="3" t="n"/>
+        <v>68.55</v>
+      </c>
+      <c r="H646" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I646" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J646" s="4" t="n">
-        <v>40.04</v>
+        <v>53.81</v>
       </c>
       <c r="K646" s="3" t="n">
-        <v>31.73</v>
+        <v>28.84</v>
       </c>
       <c r="L646" s="3" t="n">
-        <v>81.98</v>
+        <v>41.53</v>
       </c>
       <c r="M646" s="3" t="n">
-        <v>92.75</v>
+        <v>82.37</v>
       </c>
       <c r="N646" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>50.78</v>
       </c>
       <c r="O646" s="4" t="n">
-        <v>63.57</v>
+        <v>47.31</v>
       </c>
       <c r="P646" s="3" t="n">
-        <v>50.45</v>
+        <v>50.46</v>
       </c>
       <c r="Q646" s="5" t="inlineStr">
         <is>
@@ -57551,61 +57551,57 @@
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
         <is>
-          <t>jshttp/fresh</t>
+          <t>cpython-team/python3-defaults</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>python3-defaults</t>
         </is>
       </c>
       <c r="F653" s="3" t="n">
-        <v>27.69</v>
+        <v>30.5</v>
       </c>
       <c r="G653" s="3" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="H653" s="3" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="I653" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>58.45</v>
+      </c>
+      <c r="H653" s="3" t="n"/>
+      <c r="I653" s="3" t="n"/>
       <c r="J653" s="4" t="n">
-        <v>53.83</v>
+        <v>44.48</v>
       </c>
       <c r="K653" s="3" t="n">
-        <v>80.86</v>
+        <v>66.23</v>
       </c>
       <c r="L653" s="3" t="n">
-        <v>35.23</v>
+        <v>47.91</v>
       </c>
       <c r="M653" s="3" t="n">
-        <v>50</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N653" s="3" t="n">
-        <v>34.47</v>
+        <v>42.99</v>
       </c>
       <c r="O653" s="4" t="n">
-        <v>47.07</v>
+        <v>57</v>
       </c>
       <c r="P653" s="3" t="n">
-        <v>50.34</v>
+        <v>50.35</v>
       </c>
       <c r="Q653" s="5" t="inlineStr">
         <is>
@@ -57639,12 +57635,12 @@
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
         <is>
-          <t>pytest-dev/iniconfig</t>
+          <t>jshttp/fresh</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -57654,46 +57650,46 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>iniconfig</t>
+          <t>fresh</t>
         </is>
       </c>
       <c r="F654" s="3" t="n">
-        <v>40.82</v>
+        <v>27.69</v>
       </c>
       <c r="G654" s="3" t="n">
-        <v>72.95</v>
+        <v>57.63</v>
       </c>
       <c r="H654" s="3" t="n">
-        <v>46.76</v>
+        <v>42.16</v>
       </c>
       <c r="I654" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J654" s="4" t="n">
-        <v>59.43</v>
+        <v>53.83</v>
       </c>
       <c r="K654" s="3" t="n">
-        <v>67.17</v>
+        <v>80.86</v>
       </c>
       <c r="L654" s="3" t="n">
-        <v>40.29</v>
+        <v>35.23</v>
       </c>
       <c r="M654" s="3" t="n">
-        <v>52.35</v>
+        <v>50</v>
       </c>
       <c r="N654" s="3" t="n">
-        <v>23.17</v>
+        <v>34.47</v>
       </c>
       <c r="O654" s="4" t="n">
-        <v>42.57</v>
+        <v>47.07</v>
       </c>
       <c r="P654" s="3" t="n">
-        <v>50.3</v>
+        <v>50.34</v>
       </c>
       <c r="Q654" s="5" t="inlineStr">
         <is>
@@ -57727,7 +57723,7 @@
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
         <is>
-          <t>cpython-team/python3-defaults</t>
+          <t>pytest-dev/iniconfig</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -57737,47 +57733,51 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>python3-defaults</t>
+          <t>iniconfig</t>
         </is>
       </c>
       <c r="F655" s="3" t="n">
-        <v>30.26</v>
+        <v>40.82</v>
       </c>
       <c r="G655" s="3" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="H655" s="3" t="n"/>
-      <c r="I655" s="3" t="n"/>
+        <v>72.95</v>
+      </c>
+      <c r="H655" s="3" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="I655" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J655" s="4" t="n">
-        <v>44.36</v>
+        <v>59.43</v>
       </c>
       <c r="K655" s="3" t="n">
-        <v>66.23</v>
+        <v>67.17</v>
       </c>
       <c r="L655" s="3" t="n">
-        <v>47.91</v>
+        <v>40.29</v>
       </c>
       <c r="M655" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>52.35</v>
       </c>
       <c r="N655" s="3" t="n">
-        <v>42.99</v>
+        <v>23.17</v>
       </c>
       <c r="O655" s="4" t="n">
-        <v>57</v>
+        <v>42.57</v>
       </c>
       <c r="P655" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
       </c>
       <c r="Q655" s="5" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         </is>
       </c>
       <c r="F658" s="3" t="n">
-        <v>26.16</v>
+        <v>26.22</v>
       </c>
       <c r="G658" s="3" t="n">
         <v>55.39</v>
@@ -58021,7 +58021,7 @@
       </c>
       <c r="I658" s="3" t="n"/>
       <c r="J658" s="4" t="n">
-        <v>49.93</v>
+        <v>49.94</v>
       </c>
       <c r="K658" s="3" t="n">
         <v>16.82</v>
@@ -58039,7 +58039,7 @@
         <v>50.34</v>
       </c>
       <c r="P658" s="3" t="n">
-        <v>50.13</v>
+        <v>50.14</v>
       </c>
       <c r="Q658" s="5" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         </is>
       </c>
       <c r="F682" s="3" t="n">
-        <v>27.86</v>
+        <v>27.92</v>
       </c>
       <c r="G682" s="3" t="n">
         <v>56.45</v>
@@ -60111,7 +60111,7 @@
       </c>
       <c r="I682" s="3" t="n"/>
       <c r="J682" s="4" t="n">
-        <v>44.94</v>
+        <v>44.95</v>
       </c>
       <c r="K682" s="3" t="n">
         <v>63.83</v>
@@ -60129,7 +60129,7 @@
         <v>54.24</v>
       </c>
       <c r="P682" s="3" t="n">
-        <v>49.37</v>
+        <v>49.38</v>
       </c>
       <c r="Q682" s="5" t="inlineStr">
         <is>
@@ -63043,61 +63043,57 @@
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
         <is>
-          <t>python-jsonschema/jsonschema-specifications</t>
+          <t>xorg/lib/libxrender</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>jsonschema-specifications</t>
+          <t>libxrender</t>
         </is>
       </c>
       <c r="F716" s="3" t="n">
-        <v>30.14</v>
+        <v>25.79</v>
       </c>
       <c r="G716" s="3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="H716" s="3" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="I716" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>55.31</v>
+      </c>
+      <c r="H716" s="3" t="n"/>
+      <c r="I716" s="3" t="n"/>
       <c r="J716" s="4" t="n">
-        <v>51.16</v>
+        <v>40.55</v>
       </c>
       <c r="K716" s="3" t="n">
-        <v>95.81</v>
+        <v>61.58</v>
       </c>
       <c r="L716" s="3" t="n">
-        <v>24.52</v>
+        <v>60.47</v>
       </c>
       <c r="M716" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N716" s="3" t="n">
-        <v>37.09</v>
+        <v>59.43</v>
       </c>
       <c r="O716" s="4" t="n">
-        <v>45.69</v>
+        <v>57.68</v>
       </c>
       <c r="P716" s="3" t="n">
-        <v>48.35</v>
+        <v>48.36</v>
       </c>
       <c r="Q716" s="5" t="inlineStr">
         <is>
@@ -63131,57 +63127,61 @@
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
         <is>
-          <t>xorg/lib/libxrender</t>
+          <t>python-jsonschema/jsonschema-specifications</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>libxrender</t>
+          <t>jsonschema-specifications</t>
         </is>
       </c>
       <c r="F717" s="3" t="n">
-        <v>25.73</v>
+        <v>30.14</v>
       </c>
       <c r="G717" s="3" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="H717" s="3" t="n"/>
-      <c r="I717" s="3" t="n"/>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="H717" s="3" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="I717" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J717" s="4" t="n">
-        <v>40.52</v>
+        <v>51.16</v>
       </c>
       <c r="K717" s="3" t="n">
-        <v>61.58</v>
+        <v>95.81</v>
       </c>
       <c r="L717" s="3" t="n">
-        <v>60.47</v>
+        <v>24.52</v>
       </c>
       <c r="M717" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N717" s="3" t="n">
-        <v>59.43</v>
+        <v>37.09</v>
       </c>
       <c r="O717" s="4" t="n">
-        <v>57.68</v>
+        <v>45.69</v>
       </c>
       <c r="P717" s="3" t="n">
-        <v>48.34</v>
+        <v>48.35</v>
       </c>
       <c r="Q717" s="5" t="inlineStr">
         <is>
@@ -71269,7 +71269,7 @@
         </is>
       </c>
       <c r="F810" s="3" t="n">
-        <v>26.3</v>
+        <v>26.36</v>
       </c>
       <c r="G810" s="3" t="n">
         <v>55.44</v>
@@ -71277,7 +71277,7 @@
       <c r="H810" s="3" t="n"/>
       <c r="I810" s="3" t="n"/>
       <c r="J810" s="4" t="n">
-        <v>40.87</v>
+        <v>40.9</v>
       </c>
       <c r="K810" s="3" t="n">
         <v>9.19</v>
@@ -71295,7 +71295,7 @@
         <v>49.26</v>
       </c>
       <c r="P810" s="3" t="n">
-        <v>44.87</v>
+        <v>44.89</v>
       </c>
       <c r="Q810" s="5" t="inlineStr">
         <is>
@@ -75877,61 +75877,59 @@
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
         <is>
-          <t>certifi/python-certifi</t>
+          <t>fontconfig/fontconfig</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>gitlab</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>cpp</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>certifi</t>
+          <t>fontconfig</t>
         </is>
       </c>
       <c r="F863" s="3" t="n">
-        <v>69.70999999999999</v>
+        <v>32.08</v>
       </c>
       <c r="G863" s="3" t="n">
-        <v>82.94</v>
-      </c>
-      <c r="H863" s="3" t="n">
-        <v>54.33</v>
-      </c>
+        <v>58.99</v>
+      </c>
+      <c r="H863" s="3" t="n"/>
       <c r="I863" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J863" s="4" t="n">
-        <v>67.86</v>
+        <v>22.77</v>
       </c>
       <c r="K863" s="3" t="n">
-        <v>30.46</v>
+        <v>64.23</v>
       </c>
       <c r="L863" s="3" t="n">
-        <v>10.48</v>
+        <v>88</v>
       </c>
       <c r="M863" s="3" t="n">
-        <v>85.51000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="N863" s="3" t="n">
-        <v>13.29</v>
+        <v>77.83</v>
       </c>
       <c r="O863" s="4" t="n">
-        <v>24.54</v>
+        <v>73.17</v>
       </c>
       <c r="P863" s="3" t="n">
-        <v>40.81</v>
+        <v>40.82</v>
       </c>
       <c r="Q863" s="5" t="inlineStr">
         <is>
@@ -75940,7 +75938,7 @@
       </c>
       <c r="R863" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S863" s="5" t="inlineStr">
@@ -75955,20 +75953,22 @@
       </c>
       <c r="U863" s="6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V863" s="5" t="n"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V863" s="5" t="n">
+        <v>611</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
         <is>
-          <t>jshttp/methods</t>
+          <t>certifi/python-certifi</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -75978,46 +75978,46 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>methods</t>
+          <t>certifi</t>
         </is>
       </c>
       <c r="F864" s="3" t="n">
-        <v>25.83</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="G864" s="3" t="n">
-        <v>56.86</v>
+        <v>82.94</v>
       </c>
       <c r="H864" s="3" t="n">
-        <v>37.2</v>
+        <v>54.33</v>
       </c>
       <c r="I864" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J864" s="4" t="n">
-        <v>50.59</v>
+        <v>67.86</v>
       </c>
       <c r="K864" s="3" t="n">
-        <v>70.70999999999999</v>
+        <v>30.46</v>
       </c>
       <c r="L864" s="3" t="n">
-        <v>13.41</v>
+        <v>10.48</v>
       </c>
       <c r="M864" s="3" t="n">
-        <v>50</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="N864" s="3" t="n">
-        <v>24.61</v>
+        <v>13.29</v>
       </c>
       <c r="O864" s="4" t="n">
-        <v>32.87</v>
+        <v>24.54</v>
       </c>
       <c r="P864" s="3" t="n">
-        <v>40.78</v>
+        <v>40.81</v>
       </c>
       <c r="Q864" s="5" t="inlineStr">
         <is>
@@ -76026,7 +76026,7 @@
       </c>
       <c r="R864" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="S864" s="5" t="inlineStr">
@@ -76041,69 +76041,69 @@
       </c>
       <c r="U864" s="6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V864" s="5" t="n">
-        <v>611</v>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V864" s="5" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
         <is>
-          <t>fontconfig/fontconfig</t>
+          <t>jshttp/methods</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>gitlab</t>
+          <t>github</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>cpp</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>fontconfig</t>
+          <t>methods</t>
         </is>
       </c>
       <c r="F865" s="3" t="n">
-        <v>31.84</v>
+        <v>25.83</v>
       </c>
       <c r="G865" s="3" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="H865" s="3" t="n"/>
+        <v>56.86</v>
+      </c>
+      <c r="H865" s="3" t="n">
+        <v>37.2</v>
+      </c>
       <c r="I865" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J865" s="4" t="n">
-        <v>22.71</v>
+        <v>50.59</v>
       </c>
       <c r="K865" s="3" t="n">
-        <v>64.23</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="L865" s="3" t="n">
-        <v>88</v>
+        <v>13.41</v>
       </c>
       <c r="M865" s="3" t="n">
-        <v>65.14</v>
+        <v>50</v>
       </c>
       <c r="N865" s="3" t="n">
-        <v>77.83</v>
+        <v>24.61</v>
       </c>
       <c r="O865" s="4" t="n">
-        <v>73.17</v>
+        <v>32.87</v>
       </c>
       <c r="P865" s="3" t="n">
-        <v>40.76</v>
+        <v>40.78</v>
       </c>
       <c r="Q865" s="5" t="inlineStr">
         <is>
@@ -84236,10 +84236,10 @@
         <v>3559</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>11572</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="14">
@@ -84340,13 +84340,13 @@
         <v>912</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="E21" s="20" t="n">
         <v>6928</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>10616</v>
+        <v>10617</v>
       </c>
       <c r="G21" s="32" t="n">
         <v>0.917</v>
@@ -84406,13 +84406,13 @@
         <v>946</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>7501</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>11465</v>
+        <v>11466</v>
       </c>
       <c r="G24" s="35" t="n">
         <v>0.991</v>
@@ -84516,13 +84516,13 @@
         <v>86</v>
       </c>
       <c r="D29" s="20" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E29" s="20" t="n">
         <v>846</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="G29" s="32" t="n">
         <v>0.127</v>
@@ -84538,13 +84538,13 @@
         <v>946</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="E30" s="27" t="n">
         <v>7586</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>11572</v>
+        <v>11573</v>
       </c>
       <c r="G30" s="36" t="n">
         <v>1</v>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -84345,10 +84345,10 @@
         <v>2771</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>6928</v>
+        <v>6927</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>10611</v>
+        <v>10610</v>
       </c>
       <c r="G21" s="32" t="n">
         <v>0.917</v>
@@ -84367,10 +84367,10 @@
         <v>225</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="G22" s="32" t="n">
         <v>0.073</v>
@@ -84389,10 +84389,10 @@
         <v>41</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G23" s="32" t="n">
         <v>0.01</v>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -83848,7 +83848,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Maintenance burden per maintainer: LOC per active contributor, CVEs per active contributor, and net-new issues per active contributor (GitHub Issues Search, per-year opened − closed) — each percentile-ranked, combined by geometric mean. The divisor is the same 5-year active-contributor count concentration uses (AC = 0 scored as AC = 1).</t>
+          <t>Maintenance burden per maintainer: LOC per active contributor, CVEs per active contributor, and net-new issues per active contributor (GitHub Issues Search + GitLab issues API, merged by repo_id, per-year opened − closed) — each percentile-ranked, combined by geometric mean. The divisor is the same 5-year active-contributor count concentration uses (AC = 0 scored as AC = 1).</t>
         </is>
       </c>
     </row>
@@ -83872,7 +83872,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="62" customHeight="1">
+    <row r="20" ht="76" customHeight="1">
       <c r="B20" s="9" t="inlineStr">
         <is>
           <t>oss</t>
@@ -83880,7 +83880,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>One SPDX license resolved per repo — manual override → registry license of the repo's packages → GitHub Licensee → GitLab API — then checked against the OSI-approved set (SPDX isOsiApproved ∪ curated extras). Expression-aware: 'mit OR apache-2.0' counts if any component is approved. Ternary: True / False / blank (unknown ≠ known-non-OSS).</t>
+          <t>One SPDX license resolved per repo — manual override → registry license of the repo's packages → GitHub Licensee → GitLab API — then checked against the approved set: SPDX isOsiApproved ∪ (isFsfLibre − content licenses) ∪ curated extras, so an FSF-libre software licence the OSI never formally reviewed still counts, while font/doc licences do not. Expression-aware: 'mit OR apache-2.0' counts if any component is approved. Ternary: True / False / blank (unknown ≠ known-non-OSS).</t>
         </is>
       </c>
     </row>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -80082,7 +80082,7 @@
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>2574779</v>
+        <v>2592690</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>849544</v>
@@ -80094,7 +80094,7 @@
         <v>30293</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>3749702</v>
+        <v>3767613</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -12,7 +12,7 @@
     <sheet name="pipeline" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'repos'!$A$1:$U$947</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'repos'!$A$1:$V$947</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U947"/>
+  <dimension ref="A1:V947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,7 @@
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,6 +850,11 @@
           <t>priority</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>eco_priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -930,6 +936,7 @@
         </is>
       </c>
       <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1011,6 +1018,7 @@
         </is>
       </c>
       <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1094,6 +1102,9 @@
       <c r="U4" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="V4" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1177,6 +1188,9 @@
       <c r="U5" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="V5" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1256,6 +1270,7 @@
         </is>
       </c>
       <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1337,6 +1352,7 @@
         </is>
       </c>
       <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1420,6 +1436,9 @@
       <c r="U8" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="V8" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1503,6 +1522,9 @@
       <c r="U9" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="V9" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1586,6 +1608,9 @@
       <c r="U10" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="V10" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1669,6 +1694,9 @@
       <c r="U11" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="V11" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1750,6 +1778,7 @@
         </is>
       </c>
       <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1831,6 +1860,7 @@
         </is>
       </c>
       <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1914,6 +1944,9 @@
       <c r="U14" s="5" t="n">
         <v>7</v>
       </c>
+      <c r="V14" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1997,6 +2030,9 @@
       <c r="U15" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="V15" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2080,6 +2116,9 @@
       <c r="U16" s="5" t="n">
         <v>9</v>
       </c>
+      <c r="V16" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2159,6 +2198,7 @@
         </is>
       </c>
       <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2242,6 +2282,9 @@
       <c r="U18" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="V18" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2325,6 +2368,9 @@
       <c r="U19" s="5" t="n">
         <v>11</v>
       </c>
+      <c r="V19" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2408,6 +2454,9 @@
       <c r="U20" s="5" t="n">
         <v>12</v>
       </c>
+      <c r="V20" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2491,6 +2540,9 @@
       <c r="U21" s="5" t="n">
         <v>13</v>
       </c>
+      <c r="V21" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2574,6 +2626,9 @@
       <c r="U22" s="5" t="n">
         <v>14</v>
       </c>
+      <c r="V22" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2657,6 +2712,9 @@
       <c r="U23" s="5" t="n">
         <v>15</v>
       </c>
+      <c r="V23" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2740,6 +2798,9 @@
       <c r="U24" s="5" t="n">
         <v>16</v>
       </c>
+      <c r="V24" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2823,6 +2884,9 @@
       <c r="U25" s="5" t="n">
         <v>17</v>
       </c>
+      <c r="V25" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2904,6 +2968,7 @@
         </is>
       </c>
       <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2987,6 +3052,9 @@
       <c r="U27" s="5" t="n">
         <v>18</v>
       </c>
+      <c r="V27" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3070,6 +3138,9 @@
       <c r="U28" s="5" t="n">
         <v>19</v>
       </c>
+      <c r="V28" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3153,6 +3224,9 @@
       <c r="U29" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="V29" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3236,6 +3310,9 @@
       <c r="U30" s="5" t="n">
         <v>21</v>
       </c>
+      <c r="V30" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3319,6 +3396,9 @@
       <c r="U31" s="5" t="n">
         <v>22</v>
       </c>
+      <c r="V31" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3402,6 +3482,9 @@
       <c r="U32" s="5" t="n">
         <v>23</v>
       </c>
+      <c r="V32" s="5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3485,6 +3568,9 @@
       <c r="U33" s="5" t="n">
         <v>24</v>
       </c>
+      <c r="V33" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3568,6 +3654,9 @@
       <c r="U34" s="5" t="n">
         <v>25</v>
       </c>
+      <c r="V34" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3649,6 +3738,7 @@
         </is>
       </c>
       <c r="U35" s="5" t="n"/>
+      <c r="V35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3730,6 +3820,7 @@
         </is>
       </c>
       <c r="U36" s="5" t="n"/>
+      <c r="V36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3813,6 +3904,9 @@
       <c r="U37" s="5" t="n">
         <v>26</v>
       </c>
+      <c r="V37" s="5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3894,6 +3988,7 @@
         </is>
       </c>
       <c r="U38" s="5" t="n"/>
+      <c r="V38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3975,6 +4070,7 @@
         </is>
       </c>
       <c r="U39" s="5" t="n"/>
+      <c r="V39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4058,6 +4154,9 @@
       <c r="U40" s="5" t="n">
         <v>27</v>
       </c>
+      <c r="V40" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4141,6 +4240,9 @@
       <c r="U41" s="5" t="n">
         <v>28</v>
       </c>
+      <c r="V41" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4224,6 +4326,9 @@
       <c r="U42" s="5" t="n">
         <v>29</v>
       </c>
+      <c r="V42" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4307,6 +4412,9 @@
       <c r="U43" s="5" t="n">
         <v>30</v>
       </c>
+      <c r="V43" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4389,6 +4497,9 @@
       </c>
       <c r="U44" s="5" t="n">
         <v>31</v>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -4471,6 +4582,9 @@
       <c r="U45" s="5" t="n">
         <v>32</v>
       </c>
+      <c r="V45" s="5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4552,6 +4666,9 @@
       <c r="U46" s="5" t="n">
         <v>33</v>
       </c>
+      <c r="V46" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4635,6 +4752,9 @@
       <c r="U47" s="5" t="n">
         <v>34</v>
       </c>
+      <c r="V47" s="5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4718,6 +4838,9 @@
       <c r="U48" s="5" t="n">
         <v>35</v>
       </c>
+      <c r="V48" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4799,6 +4922,7 @@
         </is>
       </c>
       <c r="U49" s="5" t="n"/>
+      <c r="V49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4882,6 +5006,9 @@
       <c r="U50" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="V50" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4963,6 +5090,7 @@
         </is>
       </c>
       <c r="U51" s="5" t="n"/>
+      <c r="V51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5044,6 +5172,7 @@
         </is>
       </c>
       <c r="U52" s="5" t="n"/>
+      <c r="V52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5125,6 +5254,7 @@
         </is>
       </c>
       <c r="U53" s="5" t="n"/>
+      <c r="V53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5208,6 +5338,9 @@
       <c r="U54" s="5" t="n">
         <v>37</v>
       </c>
+      <c r="V54" s="5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5291,6 +5424,9 @@
       <c r="U55" s="5" t="n">
         <v>38</v>
       </c>
+      <c r="V55" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5374,6 +5510,9 @@
       <c r="U56" s="5" t="n">
         <v>39</v>
       </c>
+      <c r="V56" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5457,6 +5596,9 @@
       <c r="U57" s="5" t="n">
         <v>40</v>
       </c>
+      <c r="V57" s="5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5538,6 +5680,7 @@
         </is>
       </c>
       <c r="U58" s="5" t="n"/>
+      <c r="V58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5619,6 +5762,7 @@
         </is>
       </c>
       <c r="U59" s="5" t="n"/>
+      <c r="V59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5700,6 +5844,7 @@
         </is>
       </c>
       <c r="U60" s="5" t="n"/>
+      <c r="V60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5781,6 +5926,7 @@
         </is>
       </c>
       <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5862,6 +6008,7 @@
         </is>
       </c>
       <c r="U62" s="5" t="n"/>
+      <c r="V62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5945,6 +6092,9 @@
       <c r="U63" s="5" t="n">
         <v>41</v>
       </c>
+      <c r="V63" s="5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6028,6 +6178,9 @@
       <c r="U64" s="5" t="n">
         <v>42</v>
       </c>
+      <c r="V64" s="5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6111,6 +6264,9 @@
       <c r="U65" s="5" t="n">
         <v>43</v>
       </c>
+      <c r="V65" s="5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6194,6 +6350,9 @@
       <c r="U66" s="5" t="n">
         <v>44</v>
       </c>
+      <c r="V66" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6275,6 +6434,7 @@
         </is>
       </c>
       <c r="U67" s="5" t="n"/>
+      <c r="V67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6356,6 +6516,7 @@
         </is>
       </c>
       <c r="U68" s="5" t="n"/>
+      <c r="V68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6439,6 +6600,9 @@
       <c r="U69" s="5" t="n">
         <v>45</v>
       </c>
+      <c r="V69" s="5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6522,6 +6686,9 @@
       <c r="U70" s="5" t="n">
         <v>46</v>
       </c>
+      <c r="V70" s="5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6605,6 +6772,9 @@
       <c r="U71" s="5" t="n">
         <v>47</v>
       </c>
+      <c r="V71" s="5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6688,6 +6858,9 @@
       <c r="U72" s="5" t="n">
         <v>48</v>
       </c>
+      <c r="V72" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6771,6 +6944,9 @@
       <c r="U73" s="5" t="n">
         <v>49</v>
       </c>
+      <c r="V73" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6852,6 +7028,7 @@
         </is>
       </c>
       <c r="U74" s="5" t="n"/>
+      <c r="V74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6935,6 +7112,9 @@
       <c r="U75" s="5" t="n">
         <v>50</v>
       </c>
+      <c r="V75" s="5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7018,6 +7198,9 @@
       <c r="U76" s="5" t="n">
         <v>51</v>
       </c>
+      <c r="V76" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7099,6 +7282,7 @@
         </is>
       </c>
       <c r="U77" s="5" t="n"/>
+      <c r="V77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7182,6 +7366,9 @@
       <c r="U78" s="5" t="n">
         <v>52</v>
       </c>
+      <c r="V78" s="5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7263,6 +7450,7 @@
         </is>
       </c>
       <c r="U79" s="5" t="n"/>
+      <c r="V79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7344,6 +7532,9 @@
       <c r="U80" s="5" t="n">
         <v>53</v>
       </c>
+      <c r="V80" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -7427,6 +7618,9 @@
       <c r="U81" s="5" t="n">
         <v>54</v>
       </c>
+      <c r="V81" s="5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7510,6 +7704,9 @@
       <c r="U82" s="5" t="n">
         <v>55</v>
       </c>
+      <c r="V82" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7591,6 +7788,7 @@
         </is>
       </c>
       <c r="U83" s="5" t="n"/>
+      <c r="V83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7672,6 +7870,7 @@
         </is>
       </c>
       <c r="U84" s="5" t="n"/>
+      <c r="V84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7753,6 +7952,7 @@
         </is>
       </c>
       <c r="U85" s="5" t="n"/>
+      <c r="V85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7836,6 +8036,9 @@
       <c r="U86" s="5" t="n">
         <v>56</v>
       </c>
+      <c r="V86" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7917,6 +8120,7 @@
         </is>
       </c>
       <c r="U87" s="5" t="n"/>
+      <c r="V87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7998,6 +8202,7 @@
         </is>
       </c>
       <c r="U88" s="5" t="n"/>
+      <c r="V88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -8079,6 +8284,7 @@
         </is>
       </c>
       <c r="U89" s="5" t="n"/>
+      <c r="V89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -8162,6 +8368,9 @@
       <c r="U90" s="5" t="n">
         <v>57</v>
       </c>
+      <c r="V90" s="5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -8245,6 +8454,9 @@
       <c r="U91" s="5" t="n">
         <v>58</v>
       </c>
+      <c r="V91" s="5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -8328,6 +8540,9 @@
       <c r="U92" s="5" t="n">
         <v>59</v>
       </c>
+      <c r="V92" s="5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8411,6 +8626,9 @@
       <c r="U93" s="5" t="n">
         <v>60</v>
       </c>
+      <c r="V93" s="5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -8492,6 +8710,7 @@
         </is>
       </c>
       <c r="U94" s="5" t="n"/>
+      <c r="V94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -8573,6 +8792,7 @@
         </is>
       </c>
       <c r="U95" s="5" t="n"/>
+      <c r="V95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -8654,6 +8874,7 @@
         </is>
       </c>
       <c r="U96" s="5" t="n"/>
+      <c r="V96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -8733,6 +8954,9 @@
       <c r="U97" s="5" t="n">
         <v>61</v>
       </c>
+      <c r="V97" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -8816,6 +9040,9 @@
       <c r="U98" s="5" t="n">
         <v>62</v>
       </c>
+      <c r="V98" s="5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -8897,6 +9124,7 @@
         </is>
       </c>
       <c r="U99" s="5" t="n"/>
+      <c r="V99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8978,6 +9206,7 @@
         </is>
       </c>
       <c r="U100" s="5" t="n"/>
+      <c r="V100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -9061,6 +9290,9 @@
       <c r="U101" s="5" t="n">
         <v>63</v>
       </c>
+      <c r="V101" s="5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9144,6 +9376,9 @@
       <c r="U102" s="5" t="n">
         <v>64</v>
       </c>
+      <c r="V102" s="5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9227,6 +9462,9 @@
       <c r="U103" s="5" t="n">
         <v>65</v>
       </c>
+      <c r="V103" s="5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9308,6 +9546,7 @@
         </is>
       </c>
       <c r="U104" s="5" t="n"/>
+      <c r="V104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -9389,6 +9628,7 @@
         </is>
       </c>
       <c r="U105" s="5" t="n"/>
+      <c r="V105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9470,6 +9710,7 @@
         </is>
       </c>
       <c r="U106" s="5" t="n"/>
+      <c r="V106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9553,6 +9794,9 @@
       <c r="U107" s="5" t="n">
         <v>66</v>
       </c>
+      <c r="V107" s="5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9634,6 +9878,7 @@
         </is>
       </c>
       <c r="U108" s="5" t="n"/>
+      <c r="V108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -9717,6 +9962,9 @@
       <c r="U109" s="5" t="n">
         <v>67</v>
       </c>
+      <c r="V109" s="5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -9800,6 +10048,9 @@
       <c r="U110" s="5" t="n">
         <v>69</v>
       </c>
+      <c r="V110" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -9883,6 +10134,9 @@
       <c r="U111" s="5" t="n">
         <v>68</v>
       </c>
+      <c r="V111" s="5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9964,6 +10218,7 @@
         </is>
       </c>
       <c r="U112" s="5" t="n"/>
+      <c r="V112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -10045,6 +10300,7 @@
         </is>
       </c>
       <c r="U113" s="5" t="n"/>
+      <c r="V113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -10128,6 +10384,9 @@
       <c r="U114" s="5" t="n">
         <v>71</v>
       </c>
+      <c r="V114" s="5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -10211,6 +10470,9 @@
       <c r="U115" s="5" t="n">
         <v>70</v>
       </c>
+      <c r="V115" s="5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10293,6 +10555,9 @@
       </c>
       <c r="U116" s="5" t="n">
         <v>72</v>
+      </c>
+      <c r="V116" s="5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="117">
@@ -10373,6 +10638,7 @@
         </is>
       </c>
       <c r="U117" s="5" t="n"/>
+      <c r="V117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -10454,6 +10720,9 @@
       <c r="U118" s="5" t="n">
         <v>74</v>
       </c>
+      <c r="V118" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10537,6 +10806,9 @@
       <c r="U119" s="5" t="n">
         <v>73</v>
       </c>
+      <c r="V119" s="5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10619,6 +10891,9 @@
       </c>
       <c r="U120" s="5" t="n">
         <v>75</v>
+      </c>
+      <c r="V120" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="121">
@@ -10699,6 +10974,9 @@
       <c r="U121" s="5" t="n">
         <v>76</v>
       </c>
+      <c r="V121" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -10782,6 +11060,9 @@
       <c r="U122" s="5" t="n">
         <v>77</v>
       </c>
+      <c r="V122" s="5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10865,6 +11146,9 @@
       <c r="U123" s="5" t="n">
         <v>78</v>
       </c>
+      <c r="V123" s="5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -10948,6 +11232,9 @@
       <c r="U124" s="5" t="n">
         <v>79</v>
       </c>
+      <c r="V124" s="5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -11030,6 +11317,9 @@
       </c>
       <c r="U125" s="5" t="n">
         <v>80</v>
+      </c>
+      <c r="V125" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="126">
@@ -11112,6 +11402,9 @@
       <c r="U126" s="5" t="n">
         <v>81</v>
       </c>
+      <c r="V126" s="5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -11195,6 +11488,9 @@
       <c r="U127" s="5" t="n">
         <v>82</v>
       </c>
+      <c r="V127" s="5" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -11278,6 +11574,9 @@
       <c r="U128" s="5" t="n">
         <v>83</v>
       </c>
+      <c r="V128" s="5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -11361,6 +11660,9 @@
       <c r="U129" s="5" t="n">
         <v>85</v>
       </c>
+      <c r="V129" s="5" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -11444,6 +11746,9 @@
       <c r="U130" s="5" t="n">
         <v>84</v>
       </c>
+      <c r="V130" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -11525,6 +11830,7 @@
         </is>
       </c>
       <c r="U131" s="5" t="n"/>
+      <c r="V131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -11607,6 +11913,9 @@
       </c>
       <c r="U132" s="5" t="n">
         <v>86</v>
+      </c>
+      <c r="V132" s="5" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="133">
@@ -11689,6 +11998,9 @@
       <c r="U133" s="5" t="n">
         <v>87</v>
       </c>
+      <c r="V133" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -11772,6 +12084,9 @@
       <c r="U134" s="5" t="n">
         <v>88</v>
       </c>
+      <c r="V134" s="5" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -11855,6 +12170,9 @@
       <c r="U135" s="5" t="n">
         <v>89</v>
       </c>
+      <c r="V135" s="5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -11936,6 +12254,7 @@
         </is>
       </c>
       <c r="U136" s="5" t="n"/>
+      <c r="V136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -12019,6 +12338,9 @@
       <c r="U137" s="5" t="n">
         <v>90</v>
       </c>
+      <c r="V137" s="5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -12101,6 +12423,9 @@
       </c>
       <c r="U138" s="5" t="n">
         <v>91</v>
+      </c>
+      <c r="V138" s="5" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="139">
@@ -12183,6 +12508,9 @@
       <c r="U139" s="5" t="n">
         <v>92</v>
       </c>
+      <c r="V139" s="5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -12264,6 +12592,9 @@
       <c r="U140" s="5" t="n">
         <v>93</v>
       </c>
+      <c r="V140" s="5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -12347,6 +12678,9 @@
       <c r="U141" s="5" t="n">
         <v>94</v>
       </c>
+      <c r="V141" s="5" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -12430,6 +12764,9 @@
       <c r="U142" s="5" t="n">
         <v>95</v>
       </c>
+      <c r="V142" s="5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -12513,6 +12850,9 @@
       <c r="U143" s="5" t="n">
         <v>96</v>
       </c>
+      <c r="V143" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -12596,6 +12936,9 @@
       <c r="U144" s="5" t="n">
         <v>97</v>
       </c>
+      <c r="V144" s="5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -12679,6 +13022,9 @@
       <c r="U145" s="5" t="n">
         <v>98</v>
       </c>
+      <c r="V145" s="5" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -12762,6 +13108,9 @@
       <c r="U146" s="5" t="n">
         <v>99</v>
       </c>
+      <c r="V146" s="5" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -12845,6 +13194,9 @@
       <c r="U147" s="5" t="n">
         <v>100</v>
       </c>
+      <c r="V147" s="5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -12928,6 +13280,9 @@
       <c r="U148" s="5" t="n">
         <v>101</v>
       </c>
+      <c r="V148" s="5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -13011,6 +13366,9 @@
       <c r="U149" s="5" t="n">
         <v>102</v>
       </c>
+      <c r="V149" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -13092,6 +13450,7 @@
         </is>
       </c>
       <c r="U150" s="5" t="n"/>
+      <c r="V150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -13173,6 +13532,7 @@
         </is>
       </c>
       <c r="U151" s="5" t="n"/>
+      <c r="V151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -13254,6 +13614,7 @@
         </is>
       </c>
       <c r="U152" s="5" t="n"/>
+      <c r="V152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -13337,6 +13698,9 @@
       <c r="U153" s="5" t="n">
         <v>103</v>
       </c>
+      <c r="V153" s="5" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -13418,6 +13782,7 @@
         </is>
       </c>
       <c r="U154" s="5" t="n"/>
+      <c r="V154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -13501,6 +13866,9 @@
       <c r="U155" s="5" t="n">
         <v>104</v>
       </c>
+      <c r="V155" s="5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -13584,6 +13952,9 @@
       <c r="U156" s="5" t="n">
         <v>105</v>
       </c>
+      <c r="V156" s="5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -13667,6 +14038,9 @@
       <c r="U157" s="5" t="n">
         <v>106</v>
       </c>
+      <c r="V157" s="5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -13748,6 +14122,7 @@
         </is>
       </c>
       <c r="U158" s="5" t="n"/>
+      <c r="V158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -13831,6 +14206,9 @@
       <c r="U159" s="5" t="n">
         <v>107</v>
       </c>
+      <c r="V159" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -13914,6 +14292,9 @@
       <c r="U160" s="5" t="n">
         <v>108</v>
       </c>
+      <c r="V160" s="5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -13995,6 +14376,7 @@
         </is>
       </c>
       <c r="U161" s="5" t="n"/>
+      <c r="V161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -14076,6 +14458,7 @@
         </is>
       </c>
       <c r="U162" s="5" t="n"/>
+      <c r="V162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -14159,6 +14542,9 @@
       <c r="U163" s="5" t="n">
         <v>109</v>
       </c>
+      <c r="V163" s="5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -14242,6 +14628,9 @@
       <c r="U164" s="5" t="n">
         <v>110</v>
       </c>
+      <c r="V164" s="5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -14325,6 +14714,9 @@
       <c r="U165" s="5" t="n">
         <v>111</v>
       </c>
+      <c r="V165" s="5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -14408,6 +14800,9 @@
       <c r="U166" s="5" t="n">
         <v>112</v>
       </c>
+      <c r="V166" s="5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -14491,6 +14886,9 @@
       <c r="U167" s="5" t="n">
         <v>113</v>
       </c>
+      <c r="V167" s="5" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -14574,6 +14972,9 @@
       <c r="U168" s="5" t="n">
         <v>114</v>
       </c>
+      <c r="V168" s="5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -14656,6 +15057,9 @@
       </c>
       <c r="U169" s="5" t="n">
         <v>115</v>
+      </c>
+      <c r="V169" s="5" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="170">
@@ -14736,6 +15140,7 @@
         </is>
       </c>
       <c r="U170" s="5" t="n"/>
+      <c r="V170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -14817,6 +15222,7 @@
         </is>
       </c>
       <c r="U171" s="5" t="n"/>
+      <c r="V171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -14900,6 +15306,9 @@
       <c r="U172" s="5" t="n">
         <v>116</v>
       </c>
+      <c r="V172" s="5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -14981,6 +15390,7 @@
         </is>
       </c>
       <c r="U173" s="5" t="n"/>
+      <c r="V173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -15064,6 +15474,9 @@
       <c r="U174" s="5" t="n">
         <v>117</v>
       </c>
+      <c r="V174" s="5" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -15145,6 +15558,7 @@
         </is>
       </c>
       <c r="U175" s="5" t="n"/>
+      <c r="V175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -15228,6 +15642,9 @@
       <c r="U176" s="5" t="n">
         <v>118</v>
       </c>
+      <c r="V176" s="5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -15311,6 +15728,9 @@
       <c r="U177" s="5" t="n">
         <v>119</v>
       </c>
+      <c r="V177" s="5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -15392,6 +15812,7 @@
         </is>
       </c>
       <c r="U178" s="5" t="n"/>
+      <c r="V178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -15471,6 +15892,9 @@
       <c r="U179" s="5" t="n">
         <v>120</v>
       </c>
+      <c r="V179" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -15552,6 +15976,7 @@
         </is>
       </c>
       <c r="U180" s="5" t="n"/>
+      <c r="V180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -15635,6 +16060,9 @@
       <c r="U181" s="5" t="n">
         <v>121</v>
       </c>
+      <c r="V181" s="5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -15716,6 +16144,9 @@
       <c r="U182" s="5" t="n">
         <v>122</v>
       </c>
+      <c r="V182" s="5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -15799,6 +16230,9 @@
       <c r="U183" s="5" t="n">
         <v>123</v>
       </c>
+      <c r="V183" s="5" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -15881,6 +16315,9 @@
       </c>
       <c r="U184" s="5" t="n">
         <v>124</v>
+      </c>
+      <c r="V184" s="5" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="185">
@@ -15963,6 +16400,9 @@
       <c r="U185" s="5" t="n">
         <v>125</v>
       </c>
+      <c r="V185" s="5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -15986,7 +16426,7 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>37.31</v>
+        <v>37.32</v>
       </c>
       <c r="F186" s="3" t="n">
         <v>63.56</v>
@@ -16042,6 +16482,7 @@
         </is>
       </c>
       <c r="U186" s="5" t="n"/>
+      <c r="V186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -16123,6 +16564,7 @@
         </is>
       </c>
       <c r="U187" s="5" t="n"/>
+      <c r="V187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -16206,6 +16648,9 @@
       <c r="U188" s="5" t="n">
         <v>126</v>
       </c>
+      <c r="V188" s="5" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -16288,6 +16733,9 @@
       </c>
       <c r="U189" s="5" t="n">
         <v>127</v>
+      </c>
+      <c r="V189" s="5" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="190">
@@ -16368,6 +16816,7 @@
         </is>
       </c>
       <c r="U190" s="5" t="n"/>
+      <c r="V190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -16451,6 +16900,9 @@
       <c r="U191" s="5" t="n">
         <v>128</v>
       </c>
+      <c r="V191" s="5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -16532,6 +16984,7 @@
         </is>
       </c>
       <c r="U192" s="5" t="n"/>
+      <c r="V192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -16615,6 +17068,9 @@
       <c r="U193" s="5" t="n">
         <v>129</v>
       </c>
+      <c r="V193" s="5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -16698,6 +17154,9 @@
       <c r="U194" s="5" t="n">
         <v>130</v>
       </c>
+      <c r="V194" s="5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -16781,6 +17240,9 @@
       <c r="U195" s="5" t="n">
         <v>132</v>
       </c>
+      <c r="V195" s="5" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -16864,6 +17326,9 @@
       <c r="U196" s="5" t="n">
         <v>131</v>
       </c>
+      <c r="V196" s="5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -16945,6 +17410,7 @@
         </is>
       </c>
       <c r="U197" s="5" t="n"/>
+      <c r="V197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -17028,6 +17494,9 @@
       <c r="U198" s="5" t="n">
         <v>133</v>
       </c>
+      <c r="V198" s="5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -17109,6 +17578,7 @@
         </is>
       </c>
       <c r="U199" s="5" t="n"/>
+      <c r="V199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -17190,6 +17660,7 @@
         </is>
       </c>
       <c r="U200" s="5" t="n"/>
+      <c r="V200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -17273,6 +17744,9 @@
       <c r="U201" s="5" t="n">
         <v>134</v>
       </c>
+      <c r="V201" s="5" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -17354,6 +17828,7 @@
         </is>
       </c>
       <c r="U202" s="5" t="n"/>
+      <c r="V202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -17437,6 +17912,9 @@
       <c r="U203" s="5" t="n">
         <v>135</v>
       </c>
+      <c r="V203" s="5" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -17520,6 +17998,9 @@
       <c r="U204" s="5" t="n">
         <v>136</v>
       </c>
+      <c r="V204" s="5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -17603,6 +18084,9 @@
       <c r="U205" s="5" t="n">
         <v>137</v>
       </c>
+      <c r="V205" s="5" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -17684,6 +18168,7 @@
         </is>
       </c>
       <c r="U206" s="5" t="n"/>
+      <c r="V206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -17767,6 +18252,9 @@
       <c r="U207" s="5" t="n">
         <v>138</v>
       </c>
+      <c r="V207" s="5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -17848,6 +18336,7 @@
         </is>
       </c>
       <c r="U208" s="5" t="n"/>
+      <c r="V208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -17929,6 +18418,7 @@
         </is>
       </c>
       <c r="U209" s="5" t="n"/>
+      <c r="V209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -18012,6 +18502,9 @@
       <c r="U210" s="5" t="n">
         <v>139</v>
       </c>
+      <c r="V210" s="5" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -18093,6 +18586,7 @@
         </is>
       </c>
       <c r="U211" s="5" t="n"/>
+      <c r="V211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -18174,6 +18668,9 @@
       <c r="U212" s="5" t="n">
         <v>140</v>
       </c>
+      <c r="V212" s="5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -18257,6 +18754,9 @@
       <c r="U213" s="5" t="n">
         <v>141</v>
       </c>
+      <c r="V213" s="5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -18340,6 +18840,9 @@
       <c r="U214" s="5" t="n">
         <v>142</v>
       </c>
+      <c r="V214" s="5" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -18423,6 +18926,9 @@
       <c r="U215" s="5" t="n">
         <v>143</v>
       </c>
+      <c r="V215" s="5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -18506,6 +19012,9 @@
       <c r="U216" s="5" t="n">
         <v>144</v>
       </c>
+      <c r="V216" s="5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -18589,6 +19098,9 @@
       <c r="U217" s="5" t="n">
         <v>145</v>
       </c>
+      <c r="V217" s="5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -18670,6 +19182,7 @@
         </is>
       </c>
       <c r="U218" s="5" t="n"/>
+      <c r="V218" s="5" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -18751,6 +19264,7 @@
         </is>
       </c>
       <c r="U219" s="5" t="n"/>
+      <c r="V219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -18832,6 +19346,7 @@
         </is>
       </c>
       <c r="U220" s="5" t="n"/>
+      <c r="V220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -18913,6 +19428,7 @@
         </is>
       </c>
       <c r="U221" s="5" t="n"/>
+      <c r="V221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -18996,6 +19512,9 @@
       <c r="U222" s="5" t="n">
         <v>146</v>
       </c>
+      <c r="V222" s="5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -19077,6 +19596,7 @@
         </is>
       </c>
       <c r="U223" s="5" t="n"/>
+      <c r="V223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -19158,6 +19678,7 @@
         </is>
       </c>
       <c r="U224" s="5" t="n"/>
+      <c r="V224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -19241,6 +19762,9 @@
       <c r="U225" s="5" t="n">
         <v>147</v>
       </c>
+      <c r="V225" s="5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -19323,6 +19847,9 @@
       </c>
       <c r="U226" s="5" t="n">
         <v>148</v>
+      </c>
+      <c r="V226" s="5" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="227">
@@ -19403,6 +19930,9 @@
       <c r="U227" s="5" t="n">
         <v>149</v>
       </c>
+      <c r="V227" s="5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -19486,6 +20016,9 @@
       <c r="U228" s="5" t="n">
         <v>150</v>
       </c>
+      <c r="V228" s="5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -19569,6 +20102,9 @@
       <c r="U229" s="5" t="n">
         <v>151</v>
       </c>
+      <c r="V229" s="5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -19652,6 +20188,9 @@
       <c r="U230" s="5" t="n">
         <v>152</v>
       </c>
+      <c r="V230" s="5" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -19735,6 +20274,9 @@
       <c r="U231" s="5" t="n">
         <v>153</v>
       </c>
+      <c r="V231" s="5" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -19816,6 +20358,7 @@
         </is>
       </c>
       <c r="U232" s="5" t="n"/>
+      <c r="V232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -19895,6 +20438,7 @@
         </is>
       </c>
       <c r="U233" s="5" t="n"/>
+      <c r="V233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -19974,6 +20518,7 @@
         </is>
       </c>
       <c r="U234" s="5" t="n"/>
+      <c r="V234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -20055,6 +20600,7 @@
         </is>
       </c>
       <c r="U235" s="5" t="n"/>
+      <c r="V235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -20138,6 +20684,9 @@
       <c r="U236" s="5" t="n">
         <v>154</v>
       </c>
+      <c r="V236" s="5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -20219,6 +20768,7 @@
         </is>
       </c>
       <c r="U237" s="5" t="n"/>
+      <c r="V237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -20302,6 +20852,9 @@
       <c r="U238" s="5" t="n">
         <v>156</v>
       </c>
+      <c r="V238" s="5" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -20385,6 +20938,9 @@
       <c r="U239" s="5" t="n">
         <v>157</v>
       </c>
+      <c r="V239" s="5" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -20468,6 +21024,9 @@
       <c r="U240" s="5" t="n">
         <v>155</v>
       </c>
+      <c r="V240" s="5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -20549,6 +21108,7 @@
         </is>
       </c>
       <c r="U241" s="5" t="n"/>
+      <c r="V241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -20632,6 +21192,9 @@
       <c r="U242" s="5" t="n">
         <v>158</v>
       </c>
+      <c r="V242" s="5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -20715,6 +21278,9 @@
       <c r="U243" s="5" t="n">
         <v>159</v>
       </c>
+      <c r="V243" s="5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -20796,6 +21362,7 @@
         </is>
       </c>
       <c r="U244" s="5" t="n"/>
+      <c r="V244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -20877,6 +21444,7 @@
         </is>
       </c>
       <c r="U245" s="5" t="n"/>
+      <c r="V245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -20958,6 +21526,7 @@
         </is>
       </c>
       <c r="U246" s="5" t="n"/>
+      <c r="V246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -21041,6 +21610,9 @@
       <c r="U247" s="5" t="n">
         <v>160</v>
       </c>
+      <c r="V247" s="5" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -21122,6 +21694,7 @@
         </is>
       </c>
       <c r="U248" s="5" t="n"/>
+      <c r="V248" s="5" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -21205,6 +21778,9 @@
       <c r="U249" s="5" t="n">
         <v>161</v>
       </c>
+      <c r="V249" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -21288,6 +21864,9 @@
       <c r="U250" s="5" t="n">
         <v>163</v>
       </c>
+      <c r="V250" s="5" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -21370,6 +21949,9 @@
       </c>
       <c r="U251" s="5" t="n">
         <v>162</v>
+      </c>
+      <c r="V251" s="5" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="252">
@@ -21448,6 +22030,7 @@
         </is>
       </c>
       <c r="U252" s="5" t="n"/>
+      <c r="V252" s="5" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -21531,6 +22114,9 @@
       <c r="U253" s="5" t="n">
         <v>164</v>
       </c>
+      <c r="V253" s="5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -21614,6 +22200,9 @@
       <c r="U254" s="5" t="n">
         <v>165</v>
       </c>
+      <c r="V254" s="5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -21697,6 +22286,9 @@
       <c r="U255" s="5" t="n">
         <v>166</v>
       </c>
+      <c r="V255" s="5" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -21779,6 +22371,9 @@
       </c>
       <c r="U256" s="5" t="n">
         <v>167</v>
+      </c>
+      <c r="V256" s="5" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="257">
@@ -21859,6 +22454,7 @@
         </is>
       </c>
       <c r="U257" s="5" t="n"/>
+      <c r="V257" s="5" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -21942,6 +22538,9 @@
       <c r="U258" s="5" t="n">
         <v>168</v>
       </c>
+      <c r="V258" s="5" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -21965,7 +22564,7 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>35.66</v>
+        <v>35.67</v>
       </c>
       <c r="F259" s="3" t="n">
         <v>62.28</v>
@@ -22021,6 +22620,7 @@
         </is>
       </c>
       <c r="U259" s="5" t="n"/>
+      <c r="V259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -22102,6 +22702,9 @@
       <c r="U260" s="5" t="n">
         <v>169</v>
       </c>
+      <c r="V260" s="5" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -22184,6 +22787,9 @@
       </c>
       <c r="U261" s="5" t="n">
         <v>170</v>
+      </c>
+      <c r="V261" s="5" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="262">
@@ -22266,6 +22872,9 @@
       <c r="U262" s="5" t="n">
         <v>171</v>
       </c>
+      <c r="V262" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -22349,6 +22958,9 @@
       <c r="U263" s="5" t="n">
         <v>172</v>
       </c>
+      <c r="V263" s="5" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -22431,6 +23043,9 @@
       </c>
       <c r="U264" s="5" t="n">
         <v>173</v>
+      </c>
+      <c r="V264" s="5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="265">
@@ -22513,6 +23128,9 @@
       <c r="U265" s="5" t="n">
         <v>174</v>
       </c>
+      <c r="V265" s="5" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -22594,6 +23212,7 @@
         </is>
       </c>
       <c r="U266" s="5" t="n"/>
+      <c r="V266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -22677,6 +23296,9 @@
       <c r="U267" s="5" t="n">
         <v>175</v>
       </c>
+      <c r="V267" s="5" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -22758,6 +23380,7 @@
         </is>
       </c>
       <c r="U268" s="5" t="n"/>
+      <c r="V268" s="5" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -22840,6 +23463,9 @@
       </c>
       <c r="U269" s="5" t="n">
         <v>176</v>
+      </c>
+      <c r="V269" s="5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="270">
@@ -22920,6 +23546,7 @@
         </is>
       </c>
       <c r="U270" s="5" t="n"/>
+      <c r="V270" s="5" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -23002,6 +23629,9 @@
       </c>
       <c r="U271" s="5" t="n">
         <v>177</v>
+      </c>
+      <c r="V271" s="5" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="272">
@@ -23082,6 +23712,7 @@
         </is>
       </c>
       <c r="U272" s="5" t="n"/>
+      <c r="V272" s="5" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -23163,6 +23794,9 @@
       <c r="U273" s="5" t="n">
         <v>178</v>
       </c>
+      <c r="V273" s="5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -23246,6 +23880,9 @@
       <c r="U274" s="5" t="n">
         <v>179</v>
       </c>
+      <c r="V274" s="5" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -23329,6 +23966,9 @@
       <c r="U275" s="5" t="n">
         <v>180</v>
       </c>
+      <c r="V275" s="5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -23412,6 +24052,9 @@
       <c r="U276" s="5" t="n">
         <v>181</v>
       </c>
+      <c r="V276" s="5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -23495,6 +24138,9 @@
       <c r="U277" s="5" t="n">
         <v>182</v>
       </c>
+      <c r="V277" s="5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -23576,6 +24222,7 @@
         </is>
       </c>
       <c r="U278" s="5" t="n"/>
+      <c r="V278" s="5" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -23657,6 +24304,7 @@
         </is>
       </c>
       <c r="U279" s="5" t="n"/>
+      <c r="V279" s="5" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -23738,6 +24386,7 @@
         </is>
       </c>
       <c r="U280" s="5" t="n"/>
+      <c r="V280" s="5" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -23821,6 +24470,9 @@
       <c r="U281" s="5" t="n">
         <v>183</v>
       </c>
+      <c r="V281" s="5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -23904,6 +24556,9 @@
       <c r="U282" s="5" t="n">
         <v>185</v>
       </c>
+      <c r="V282" s="5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -23987,6 +24642,9 @@
       <c r="U283" s="5" t="n">
         <v>184</v>
       </c>
+      <c r="V283" s="5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -24069,6 +24727,9 @@
       </c>
       <c r="U284" s="5" t="n">
         <v>186</v>
+      </c>
+      <c r="V284" s="5" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="285">
@@ -24149,6 +24810,9 @@
       <c r="U285" s="5" t="n">
         <v>187</v>
       </c>
+      <c r="V285" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -24232,6 +24896,9 @@
       <c r="U286" s="5" t="n">
         <v>188</v>
       </c>
+      <c r="V286" s="5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -24313,6 +24980,7 @@
         </is>
       </c>
       <c r="U287" s="5" t="n"/>
+      <c r="V287" s="5" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -24396,6 +25064,9 @@
       <c r="U288" s="5" t="n">
         <v>189</v>
       </c>
+      <c r="V288" s="5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -24477,6 +25148,7 @@
         </is>
       </c>
       <c r="U289" s="5" t="n"/>
+      <c r="V289" s="5" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -24558,6 +25230,7 @@
         </is>
       </c>
       <c r="U290" s="5" t="n"/>
+      <c r="V290" s="5" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -24641,6 +25314,9 @@
       <c r="U291" s="5" t="n">
         <v>190</v>
       </c>
+      <c r="V291" s="5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -24724,6 +25400,9 @@
       <c r="U292" s="5" t="n">
         <v>191</v>
       </c>
+      <c r="V292" s="5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -24807,6 +25486,9 @@
       <c r="U293" s="5" t="n">
         <v>192</v>
       </c>
+      <c r="V293" s="5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -24890,6 +25572,9 @@
       <c r="U294" s="5" t="n">
         <v>193</v>
       </c>
+      <c r="V294" s="5" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -24971,6 +25656,7 @@
         </is>
       </c>
       <c r="U295" s="5" t="n"/>
+      <c r="V295" s="5" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -25054,6 +25740,9 @@
       <c r="U296" s="5" t="n">
         <v>194</v>
       </c>
+      <c r="V296" s="5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -25137,6 +25826,9 @@
       <c r="U297" s="5" t="n">
         <v>195</v>
       </c>
+      <c r="V297" s="5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -25218,6 +25910,7 @@
         </is>
       </c>
       <c r="U298" s="5" t="n"/>
+      <c r="V298" s="5" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -25299,6 +25992,7 @@
         </is>
       </c>
       <c r="U299" s="5" t="n"/>
+      <c r="V299" s="5" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -25382,6 +26076,9 @@
       <c r="U300" s="5" t="n">
         <v>196</v>
       </c>
+      <c r="V300" s="5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -25463,6 +26160,7 @@
         </is>
       </c>
       <c r="U301" s="5" t="n"/>
+      <c r="V301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -25544,6 +26242,7 @@
         </is>
       </c>
       <c r="U302" s="5" t="n"/>
+      <c r="V302" s="5" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -25626,6 +26325,9 @@
       </c>
       <c r="U303" s="5" t="n">
         <v>197</v>
+      </c>
+      <c r="V303" s="5" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="304">
@@ -25706,6 +26408,7 @@
         </is>
       </c>
       <c r="U304" s="5" t="n"/>
+      <c r="V304" s="5" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -25787,6 +26490,7 @@
         </is>
       </c>
       <c r="U305" s="5" t="n"/>
+      <c r="V305" s="5" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -25870,6 +26574,9 @@
       <c r="U306" s="5" t="n">
         <v>198</v>
       </c>
+      <c r="V306" s="5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -25951,6 +26658,7 @@
         </is>
       </c>
       <c r="U307" s="5" t="n"/>
+      <c r="V307" s="5" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -26034,6 +26742,9 @@
       <c r="U308" s="5" t="n">
         <v>199</v>
       </c>
+      <c r="V308" s="5" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -26117,6 +26828,9 @@
       <c r="U309" s="5" t="n">
         <v>200</v>
       </c>
+      <c r="V309" s="5" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -26198,6 +26912,7 @@
         </is>
       </c>
       <c r="U310" s="5" t="n"/>
+      <c r="V310" s="5" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -26281,6 +26996,9 @@
       <c r="U311" s="5" t="n">
         <v>202</v>
       </c>
+      <c r="V311" s="5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -26364,6 +27082,9 @@
       <c r="U312" s="5" t="n">
         <v>201</v>
       </c>
+      <c r="V312" s="5" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -26447,6 +27168,9 @@
       <c r="U313" s="5" t="n">
         <v>203</v>
       </c>
+      <c r="V313" s="5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -26530,6 +27254,9 @@
       <c r="U314" s="5" t="n">
         <v>204</v>
       </c>
+      <c r="V314" s="5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -26613,6 +27340,9 @@
       <c r="U315" s="5" t="n">
         <v>205</v>
       </c>
+      <c r="V315" s="5" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -26695,6 +27425,9 @@
       </c>
       <c r="U316" s="5" t="n">
         <v>206</v>
+      </c>
+      <c r="V316" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="317">
@@ -26777,6 +27510,9 @@
       <c r="U317" s="5" t="n">
         <v>207</v>
       </c>
+      <c r="V317" s="5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -26860,6 +27596,9 @@
       <c r="U318" s="5" t="n">
         <v>208</v>
       </c>
+      <c r="V318" s="5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -26941,6 +27680,7 @@
         </is>
       </c>
       <c r="U319" s="5" t="n"/>
+      <c r="V319" s="5" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -27024,6 +27764,9 @@
       <c r="U320" s="5" t="n">
         <v>209</v>
       </c>
+      <c r="V320" s="5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -27105,6 +27848,7 @@
         </is>
       </c>
       <c r="U321" s="5" t="n"/>
+      <c r="V321" s="5" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -27186,6 +27930,7 @@
         </is>
       </c>
       <c r="U322" s="5" t="n"/>
+      <c r="V322" s="5" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -27269,6 +28014,9 @@
       <c r="U323" s="5" t="n">
         <v>210</v>
       </c>
+      <c r="V323" s="5" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -27350,6 +28098,7 @@
         </is>
       </c>
       <c r="U324" s="5" t="n"/>
+      <c r="V324" s="5" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -27431,6 +28180,7 @@
         </is>
       </c>
       <c r="U325" s="5" t="n"/>
+      <c r="V325" s="5" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -27512,6 +28262,7 @@
         </is>
       </c>
       <c r="U326" s="5" t="n"/>
+      <c r="V326" s="5" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -27595,6 +28346,9 @@
       <c r="U327" s="5" t="n">
         <v>211</v>
       </c>
+      <c r="V327" s="5" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -27676,6 +28430,7 @@
         </is>
       </c>
       <c r="U328" s="5" t="n"/>
+      <c r="V328" s="5" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -27757,6 +28512,7 @@
         </is>
       </c>
       <c r="U329" s="5" t="n"/>
+      <c r="V329" s="5" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -27840,6 +28596,9 @@
       <c r="U330" s="5" t="n">
         <v>212</v>
       </c>
+      <c r="V330" s="5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -27923,6 +28682,9 @@
       <c r="U331" s="5" t="n">
         <v>213</v>
       </c>
+      <c r="V331" s="5" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -28004,6 +28766,7 @@
         </is>
       </c>
       <c r="U332" s="5" t="n"/>
+      <c r="V332" s="5" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -28085,6 +28848,9 @@
       <c r="U333" s="5" t="n">
         <v>214</v>
       </c>
+      <c r="V333" s="5" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -28168,6 +28934,9 @@
       <c r="U334" s="5" t="n">
         <v>215</v>
       </c>
+      <c r="V334" s="5" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -28251,6 +29020,9 @@
       <c r="U335" s="5" t="n">
         <v>216</v>
       </c>
+      <c r="V335" s="5" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -28334,6 +29106,9 @@
       <c r="U336" s="5" t="n">
         <v>217</v>
       </c>
+      <c r="V336" s="5" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -28417,6 +29192,9 @@
       <c r="U337" s="5" t="n">
         <v>218</v>
       </c>
+      <c r="V337" s="5" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -28500,6 +29278,9 @@
       <c r="U338" s="5" t="n">
         <v>219</v>
       </c>
+      <c r="V338" s="5" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -28581,6 +29362,7 @@
         </is>
       </c>
       <c r="U339" s="5" t="n"/>
+      <c r="V339" s="5" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -28664,6 +29446,9 @@
       <c r="U340" s="5" t="n">
         <v>220</v>
       </c>
+      <c r="V340" s="5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -28747,6 +29532,9 @@
       <c r="U341" s="5" t="n">
         <v>221</v>
       </c>
+      <c r="V341" s="5" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -28829,6 +29617,9 @@
       </c>
       <c r="U342" s="5" t="n">
         <v>222</v>
+      </c>
+      <c r="V342" s="5" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="343">
@@ -28909,6 +29700,7 @@
         </is>
       </c>
       <c r="U343" s="5" t="n"/>
+      <c r="V343" s="5" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -28992,6 +29784,9 @@
       <c r="U344" s="5" t="n">
         <v>223</v>
       </c>
+      <c r="V344" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -29075,6 +29870,9 @@
       <c r="U345" s="5" t="n">
         <v>224</v>
       </c>
+      <c r="V345" s="5" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -29157,6 +29955,9 @@
       </c>
       <c r="U346" s="5" t="n">
         <v>225</v>
+      </c>
+      <c r="V346" s="5" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="347">
@@ -29237,6 +30038,7 @@
         </is>
       </c>
       <c r="U347" s="5" t="n"/>
+      <c r="V347" s="5" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -29320,6 +30122,9 @@
       <c r="U348" s="5" t="n">
         <v>226</v>
       </c>
+      <c r="V348" s="5" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -29403,6 +30208,9 @@
       <c r="U349" s="5" t="n">
         <v>227</v>
       </c>
+      <c r="V349" s="5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -29486,6 +30294,9 @@
       <c r="U350" s="5" t="n">
         <v>228</v>
       </c>
+      <c r="V350" s="5" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -29569,6 +30380,9 @@
       <c r="U351" s="5" t="n">
         <v>229</v>
       </c>
+      <c r="V351" s="5" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -29652,6 +30466,9 @@
       <c r="U352" s="5" t="n">
         <v>231</v>
       </c>
+      <c r="V352" s="5" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -29735,6 +30552,9 @@
       <c r="U353" s="5" t="n">
         <v>230</v>
       </c>
+      <c r="V353" s="5" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -29817,6 +30637,9 @@
       </c>
       <c r="U354" s="5" t="n">
         <v>232</v>
+      </c>
+      <c r="V354" s="5" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="355">
@@ -29895,6 +30718,7 @@
         </is>
       </c>
       <c r="U355" s="5" t="n"/>
+      <c r="V355" s="5" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -29978,6 +30802,9 @@
       <c r="U356" s="5" t="n">
         <v>234</v>
       </c>
+      <c r="V356" s="5" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -30061,6 +30888,9 @@
       <c r="U357" s="5" t="n">
         <v>233</v>
       </c>
+      <c r="V357" s="5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -30142,6 +30972,7 @@
         </is>
       </c>
       <c r="U358" s="5" t="n"/>
+      <c r="V358" s="5" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -30223,6 +31054,9 @@
       <c r="U359" s="5" t="n">
         <v>235</v>
       </c>
+      <c r="V359" s="5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -30306,6 +31140,9 @@
       <c r="U360" s="5" t="n">
         <v>236</v>
       </c>
+      <c r="V360" s="5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -30387,6 +31224,7 @@
         </is>
       </c>
       <c r="U361" s="5" t="n"/>
+      <c r="V361" s="5" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -30470,6 +31308,9 @@
       <c r="U362" s="5" t="n">
         <v>237</v>
       </c>
+      <c r="V362" s="5" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -30553,6 +31394,9 @@
       <c r="U363" s="5" t="n">
         <v>238</v>
       </c>
+      <c r="V363" s="5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -30636,6 +31480,9 @@
       <c r="U364" s="5" t="n">
         <v>239</v>
       </c>
+      <c r="V364" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -30717,6 +31564,7 @@
         </is>
       </c>
       <c r="U365" s="5" t="n"/>
+      <c r="V365" s="5" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -30800,6 +31648,9 @@
       <c r="U366" s="5" t="n">
         <v>240</v>
       </c>
+      <c r="V366" s="5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -30882,6 +31733,9 @@
       </c>
       <c r="U367" s="5" t="n">
         <v>241</v>
+      </c>
+      <c r="V367" s="5" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="368">
@@ -30962,6 +31816,7 @@
         </is>
       </c>
       <c r="U368" s="5" t="n"/>
+      <c r="V368" s="5" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -31045,6 +31900,9 @@
       <c r="U369" s="5" t="n">
         <v>242</v>
       </c>
+      <c r="V369" s="5" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -31126,6 +31984,7 @@
         </is>
       </c>
       <c r="U370" s="5" t="n"/>
+      <c r="V370" s="5" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -31209,6 +32068,9 @@
       <c r="U371" s="5" t="n">
         <v>243</v>
       </c>
+      <c r="V371" s="5" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -31292,6 +32154,9 @@
       <c r="U372" s="5" t="n">
         <v>244</v>
       </c>
+      <c r="V372" s="5" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -31375,6 +32240,9 @@
       <c r="U373" s="5" t="n">
         <v>245</v>
       </c>
+      <c r="V373" s="5" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -31456,6 +32324,7 @@
         </is>
       </c>
       <c r="U374" s="5" t="n"/>
+      <c r="V374" s="5" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -31539,6 +32408,9 @@
       <c r="U375" s="5" t="n">
         <v>246</v>
       </c>
+      <c r="V375" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -31620,6 +32492,7 @@
         </is>
       </c>
       <c r="U376" s="5" t="n"/>
+      <c r="V376" s="5" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -31701,6 +32574,7 @@
         </is>
       </c>
       <c r="U377" s="5" t="n"/>
+      <c r="V377" s="5" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -31782,6 +32656,7 @@
         </is>
       </c>
       <c r="U378" s="5" t="n"/>
+      <c r="V378" s="5" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -31865,6 +32740,9 @@
       <c r="U379" s="5" t="n">
         <v>247</v>
       </c>
+      <c r="V379" s="5" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -31948,6 +32826,9 @@
       <c r="U380" s="5" t="n">
         <v>248</v>
       </c>
+      <c r="V380" s="5" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -32031,6 +32912,9 @@
       <c r="U381" s="5" t="n">
         <v>249</v>
       </c>
+      <c r="V381" s="5" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -32113,6 +32997,9 @@
       </c>
       <c r="U382" s="5" t="n">
         <v>250</v>
+      </c>
+      <c r="V382" s="5" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="383">
@@ -32193,6 +33080,9 @@
       <c r="U383" s="5" t="n">
         <v>251</v>
       </c>
+      <c r="V383" s="5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -32274,6 +33164,7 @@
         </is>
       </c>
       <c r="U384" s="5" t="n"/>
+      <c r="V384" s="5" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -32355,6 +33246,7 @@
         </is>
       </c>
       <c r="U385" s="5" t="n"/>
+      <c r="V385" s="5" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -32438,6 +33330,9 @@
       <c r="U386" s="5" t="n">
         <v>252</v>
       </c>
+      <c r="V386" s="5" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -32519,6 +33414,7 @@
         </is>
       </c>
       <c r="U387" s="5" t="n"/>
+      <c r="V387" s="5" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -32598,6 +33494,7 @@
         </is>
       </c>
       <c r="U388" s="5" t="n"/>
+      <c r="V388" s="5" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -32679,6 +33576,7 @@
         </is>
       </c>
       <c r="U389" s="5" t="n"/>
+      <c r="V389" s="5" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -32762,6 +33660,9 @@
       <c r="U390" s="5" t="n">
         <v>253</v>
       </c>
+      <c r="V390" s="5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -32843,6 +33744,7 @@
         </is>
       </c>
       <c r="U391" s="5" t="n"/>
+      <c r="V391" s="5" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -32925,6 +33827,9 @@
       </c>
       <c r="U392" s="5" t="n">
         <v>254</v>
+      </c>
+      <c r="V392" s="5" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="393">
@@ -33005,6 +33910,7 @@
         </is>
       </c>
       <c r="U393" s="5" t="n"/>
+      <c r="V393" s="5" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -33086,6 +33992,9 @@
       <c r="U394" s="5" t="n">
         <v>255</v>
       </c>
+      <c r="V394" s="5" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -33165,6 +34074,7 @@
         </is>
       </c>
       <c r="U395" s="5" t="n"/>
+      <c r="V395" s="5" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -33248,6 +34158,9 @@
       <c r="U396" s="5" t="n">
         <v>256</v>
       </c>
+      <c r="V396" s="5" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -33331,6 +34244,9 @@
       <c r="U397" s="5" t="n">
         <v>257</v>
       </c>
+      <c r="V397" s="5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -33413,6 +34329,9 @@
       </c>
       <c r="U398" s="5" t="n">
         <v>258</v>
+      </c>
+      <c r="V398" s="5" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="399">
@@ -33493,6 +34412,7 @@
         </is>
       </c>
       <c r="U399" s="5" t="n"/>
+      <c r="V399" s="5" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -33574,6 +34494,7 @@
         </is>
       </c>
       <c r="U400" s="5" t="n"/>
+      <c r="V400" s="5" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -33657,6 +34578,9 @@
       <c r="U401" s="5" t="n">
         <v>259</v>
       </c>
+      <c r="V401" s="5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -33738,6 +34662,7 @@
         </is>
       </c>
       <c r="U402" s="5" t="n"/>
+      <c r="V402" s="5" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -33819,6 +34744,9 @@
       <c r="U403" s="5" t="n">
         <v>260</v>
       </c>
+      <c r="V403" s="5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -33900,6 +34828,9 @@
       <c r="U404" s="5" t="n">
         <v>262</v>
       </c>
+      <c r="V404" s="5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -33983,6 +34914,9 @@
       <c r="U405" s="5" t="n">
         <v>261</v>
       </c>
+      <c r="V405" s="5" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -34066,6 +35000,9 @@
       <c r="U406" s="5" t="n">
         <v>263</v>
       </c>
+      <c r="V406" s="5" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -34149,6 +35086,9 @@
       <c r="U407" s="5" t="n">
         <v>264</v>
       </c>
+      <c r="V407" s="5" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -34232,6 +35172,9 @@
       <c r="U408" s="5" t="n">
         <v>265</v>
       </c>
+      <c r="V408" s="5" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -34313,6 +35256,7 @@
         </is>
       </c>
       <c r="U409" s="5" t="n"/>
+      <c r="V409" s="5" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -34394,6 +35338,7 @@
         </is>
       </c>
       <c r="U410" s="5" t="n"/>
+      <c r="V410" s="5" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -34477,6 +35422,9 @@
       <c r="U411" s="5" t="n">
         <v>267</v>
       </c>
+      <c r="V411" s="5" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -34560,6 +35508,9 @@
       <c r="U412" s="5" t="n">
         <v>266</v>
       </c>
+      <c r="V412" s="5" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -34642,6 +35593,9 @@
       </c>
       <c r="U413" s="5" t="n">
         <v>268</v>
+      </c>
+      <c r="V413" s="5" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="414">
@@ -34724,6 +35678,9 @@
       <c r="U414" s="5" t="n">
         <v>269</v>
       </c>
+      <c r="V414" s="5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -34805,6 +35762,7 @@
         </is>
       </c>
       <c r="U415" s="5" t="n"/>
+      <c r="V415" s="5" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -34886,6 +35844,7 @@
         </is>
       </c>
       <c r="U416" s="5" t="n"/>
+      <c r="V416" s="5" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -34969,6 +35928,9 @@
       <c r="U417" s="5" t="n">
         <v>271</v>
       </c>
+      <c r="V417" s="5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -35052,6 +36014,9 @@
       <c r="U418" s="5" t="n">
         <v>270</v>
       </c>
+      <c r="V418" s="5" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -35135,6 +36100,9 @@
       <c r="U419" s="5" t="n">
         <v>272</v>
       </c>
+      <c r="V419" s="5" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -35218,6 +36186,9 @@
       <c r="U420" s="5" t="n">
         <v>273</v>
       </c>
+      <c r="V420" s="5" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -35301,6 +36272,9 @@
       <c r="U421" s="5" t="n">
         <v>274</v>
       </c>
+      <c r="V421" s="5" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -35384,6 +36358,9 @@
       <c r="U422" s="5" t="n">
         <v>275</v>
       </c>
+      <c r="V422" s="5" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -35465,6 +36442,7 @@
         </is>
       </c>
       <c r="U423" s="5" t="n"/>
+      <c r="V423" s="5" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -35548,6 +36526,9 @@
       <c r="U424" s="5" t="n">
         <v>276</v>
       </c>
+      <c r="V424" s="5" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -35631,6 +36612,9 @@
       <c r="U425" s="5" t="n">
         <v>277</v>
       </c>
+      <c r="V425" s="5" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -35712,6 +36696,7 @@
         </is>
       </c>
       <c r="U426" s="5" t="n"/>
+      <c r="V426" s="5" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -35793,6 +36778,7 @@
         </is>
       </c>
       <c r="U427" s="5" t="n"/>
+      <c r="V427" s="5" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -35874,6 +36860,7 @@
         </is>
       </c>
       <c r="U428" s="5" t="n"/>
+      <c r="V428" s="5" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -35957,6 +36944,9 @@
       <c r="U429" s="5" t="n">
         <v>278</v>
       </c>
+      <c r="V429" s="5" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -36040,6 +37030,9 @@
       <c r="U430" s="5" t="n">
         <v>279</v>
       </c>
+      <c r="V430" s="5" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -36123,6 +37116,9 @@
       <c r="U431" s="5" t="n">
         <v>280</v>
       </c>
+      <c r="V431" s="5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -36206,6 +37202,9 @@
       <c r="U432" s="5" t="n">
         <v>281</v>
       </c>
+      <c r="V432" s="5" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -36287,6 +37286,7 @@
         </is>
       </c>
       <c r="U433" s="5" t="n"/>
+      <c r="V433" s="5" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -36370,6 +37370,9 @@
       <c r="U434" s="5" t="n">
         <v>282</v>
       </c>
+      <c r="V434" s="5" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -36453,6 +37456,9 @@
       <c r="U435" s="5" t="n">
         <v>283</v>
       </c>
+      <c r="V435" s="5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -36536,6 +37542,9 @@
       <c r="U436" s="5" t="n">
         <v>284</v>
       </c>
+      <c r="V436" s="5" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -36619,6 +37628,9 @@
       <c r="U437" s="5" t="n">
         <v>286</v>
       </c>
+      <c r="V437" s="5" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -36702,6 +37714,9 @@
       <c r="U438" s="5" t="n">
         <v>285</v>
       </c>
+      <c r="V438" s="5" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -36783,6 +37798,7 @@
         </is>
       </c>
       <c r="U439" s="5" t="n"/>
+      <c r="V439" s="5" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -36866,6 +37882,9 @@
       <c r="U440" s="5" t="n">
         <v>287</v>
       </c>
+      <c r="V440" s="5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -36949,6 +37968,9 @@
       <c r="U441" s="5" t="n">
         <v>288</v>
       </c>
+      <c r="V441" s="5" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -37032,6 +38054,9 @@
       <c r="U442" s="5" t="n">
         <v>289</v>
       </c>
+      <c r="V442" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -37115,6 +38140,9 @@
       <c r="U443" s="5" t="n">
         <v>290</v>
       </c>
+      <c r="V443" s="5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -37198,6 +38226,9 @@
       <c r="U444" s="5" t="n">
         <v>291</v>
       </c>
+      <c r="V444" s="5" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -37281,6 +38312,9 @@
       <c r="U445" s="5" t="n">
         <v>292</v>
       </c>
+      <c r="V445" s="5" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -37364,6 +38398,9 @@
       <c r="U446" s="5" t="n">
         <v>293</v>
       </c>
+      <c r="V446" s="5" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -37447,6 +38484,9 @@
       <c r="U447" s="5" t="n">
         <v>294</v>
       </c>
+      <c r="V447" s="5" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -37530,6 +38570,9 @@
       <c r="U448" s="5" t="n">
         <v>295</v>
       </c>
+      <c r="V448" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -37611,6 +38654,7 @@
         </is>
       </c>
       <c r="U449" s="5" t="n"/>
+      <c r="V449" s="5" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -37694,6 +38738,9 @@
       <c r="U450" s="5" t="n">
         <v>296</v>
       </c>
+      <c r="V450" s="5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -37775,6 +38822,7 @@
         </is>
       </c>
       <c r="U451" s="5" t="n"/>
+      <c r="V451" s="5" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -37858,6 +38906,9 @@
       <c r="U452" s="5" t="n">
         <v>297</v>
       </c>
+      <c r="V452" s="5" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -37941,6 +38992,9 @@
       <c r="U453" s="5" t="n">
         <v>298</v>
       </c>
+      <c r="V453" s="5" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -38022,6 +39076,7 @@
         </is>
       </c>
       <c r="U454" s="5" t="n"/>
+      <c r="V454" s="5" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -38105,6 +39160,9 @@
       <c r="U455" s="5" t="n">
         <v>299</v>
       </c>
+      <c r="V455" s="5" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -38188,6 +39246,9 @@
       <c r="U456" s="5" t="n">
         <v>300</v>
       </c>
+      <c r="V456" s="5" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -38271,6 +39332,9 @@
       <c r="U457" s="5" t="n">
         <v>301</v>
       </c>
+      <c r="V457" s="5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -38354,6 +39418,9 @@
       <c r="U458" s="5" t="n">
         <v>302</v>
       </c>
+      <c r="V458" s="5" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -38436,6 +39503,9 @@
       </c>
       <c r="U459" s="5" t="n">
         <v>303</v>
+      </c>
+      <c r="V459" s="5" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="460">
@@ -38516,6 +39586,7 @@
         </is>
       </c>
       <c r="U460" s="5" t="n"/>
+      <c r="V460" s="5" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -38599,6 +39670,9 @@
       <c r="U461" s="5" t="n">
         <v>304</v>
       </c>
+      <c r="V461" s="5" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -38680,6 +39754,7 @@
         </is>
       </c>
       <c r="U462" s="5" t="n"/>
+      <c r="V462" s="5" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -38763,6 +39838,9 @@
       <c r="U463" s="5" t="n">
         <v>305</v>
       </c>
+      <c r="V463" s="5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -38844,6 +39922,7 @@
         </is>
       </c>
       <c r="U464" s="5" t="n"/>
+      <c r="V464" s="5" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -38927,6 +40006,9 @@
       <c r="U465" s="5" t="n">
         <v>306</v>
       </c>
+      <c r="V465" s="5" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -39008,6 +40090,7 @@
         </is>
       </c>
       <c r="U466" s="5" t="n"/>
+      <c r="V466" s="5" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -39089,6 +40172,7 @@
         </is>
       </c>
       <c r="U467" s="5" t="n"/>
+      <c r="V467" s="5" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -39172,6 +40256,9 @@
       <c r="U468" s="5" t="n">
         <v>307</v>
       </c>
+      <c r="V468" s="5" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -39255,6 +40342,9 @@
       <c r="U469" s="5" t="n">
         <v>308</v>
       </c>
+      <c r="V469" s="5" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -39338,6 +40428,9 @@
       <c r="U470" s="5" t="n">
         <v>309</v>
       </c>
+      <c r="V470" s="5" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -39420,6 +40513,9 @@
       </c>
       <c r="U471" s="5" t="n">
         <v>310</v>
+      </c>
+      <c r="V471" s="5" t="n">
+        <v>164</v>
       </c>
     </row>
     <row r="472">
@@ -39502,6 +40598,9 @@
       <c r="U472" s="5" t="n">
         <v>311</v>
       </c>
+      <c r="V472" s="5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -39585,6 +40684,9 @@
       <c r="U473" s="5" t="n">
         <v>312</v>
       </c>
+      <c r="V473" s="5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -39666,6 +40768,7 @@
         </is>
       </c>
       <c r="U474" s="5" t="n"/>
+      <c r="V474" s="5" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -39749,6 +40852,9 @@
       <c r="U475" s="5" t="n">
         <v>313</v>
       </c>
+      <c r="V475" s="5" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -39831,6 +40937,9 @@
       </c>
       <c r="U476" s="5" t="n">
         <v>314</v>
+      </c>
+      <c r="V476" s="5" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="477">
@@ -39911,6 +41020,9 @@
       <c r="U477" s="5" t="n">
         <v>315</v>
       </c>
+      <c r="V477" s="5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -39992,6 +41104,7 @@
         </is>
       </c>
       <c r="U478" s="5" t="n"/>
+      <c r="V478" s="5" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -40075,6 +41188,9 @@
       <c r="U479" s="5" t="n">
         <v>316</v>
       </c>
+      <c r="V479" s="5" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -40156,6 +41272,7 @@
         </is>
       </c>
       <c r="U480" s="5" t="n"/>
+      <c r="V480" s="5" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -40237,6 +41354,7 @@
         </is>
       </c>
       <c r="U481" s="5" t="n"/>
+      <c r="V481" s="5" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -40320,6 +41438,9 @@
       <c r="U482" s="5" t="n">
         <v>317</v>
       </c>
+      <c r="V482" s="5" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -40403,6 +41524,9 @@
       <c r="U483" s="5" t="n">
         <v>318</v>
       </c>
+      <c r="V483" s="5" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -40484,6 +41608,7 @@
         </is>
       </c>
       <c r="U484" s="5" t="n"/>
+      <c r="V484" s="5" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -40567,6 +41692,9 @@
       <c r="U485" s="5" t="n">
         <v>319</v>
       </c>
+      <c r="V485" s="5" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -40649,6 +41777,9 @@
       </c>
       <c r="U486" s="5" t="n">
         <v>320</v>
+      </c>
+      <c r="V486" s="5" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="487">
@@ -40729,6 +41860,9 @@
       <c r="U487" s="5" t="n">
         <v>321</v>
       </c>
+      <c r="V487" s="5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -40812,6 +41946,9 @@
       <c r="U488" s="5" t="n">
         <v>322</v>
       </c>
+      <c r="V488" s="5" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -40895,6 +42032,9 @@
       <c r="U489" s="5" t="n">
         <v>323</v>
       </c>
+      <c r="V489" s="5" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -40978,6 +42118,9 @@
       <c r="U490" s="5" t="n">
         <v>324</v>
       </c>
+      <c r="V490" s="5" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -41061,6 +42204,9 @@
       <c r="U491" s="5" t="n">
         <v>325</v>
       </c>
+      <c r="V491" s="5" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -41144,6 +42290,9 @@
       <c r="U492" s="5" t="n">
         <v>326</v>
       </c>
+      <c r="V492" s="5" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -41227,6 +42376,9 @@
       <c r="U493" s="5" t="n">
         <v>327</v>
       </c>
+      <c r="V493" s="5" t="n">
+        <v>173</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -41310,6 +42462,9 @@
       <c r="U494" s="5" t="n">
         <v>329</v>
       </c>
+      <c r="V494" s="5" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -41393,6 +42548,9 @@
       <c r="U495" s="5" t="n">
         <v>328</v>
       </c>
+      <c r="V495" s="5" t="n">
+        <v>174</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -41474,6 +42632,7 @@
         </is>
       </c>
       <c r="U496" s="5" t="n"/>
+      <c r="V496" s="5" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -41557,6 +42716,9 @@
       <c r="U497" s="5" t="n">
         <v>330</v>
       </c>
+      <c r="V497" s="5" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -41638,6 +42800,7 @@
         </is>
       </c>
       <c r="U498" s="5" t="n"/>
+      <c r="V498" s="5" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -41721,6 +42884,9 @@
       <c r="U499" s="5" t="n">
         <v>331</v>
       </c>
+      <c r="V499" s="5" t="n">
+        <v>177</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -41804,6 +42970,9 @@
       <c r="U500" s="5" t="n">
         <v>332</v>
       </c>
+      <c r="V500" s="5" t="n">
+        <v>178</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -41887,6 +43056,9 @@
       <c r="U501" s="5" t="n">
         <v>333</v>
       </c>
+      <c r="V501" s="5" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -41970,6 +43142,9 @@
       <c r="U502" s="5" t="n">
         <v>334</v>
       </c>
+      <c r="V502" s="5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -42051,6 +43226,7 @@
         </is>
       </c>
       <c r="U503" s="5" t="n"/>
+      <c r="V503" s="5" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -42134,6 +43310,9 @@
       <c r="U504" s="5" t="n">
         <v>335</v>
       </c>
+      <c r="V504" s="5" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -42217,6 +43396,9 @@
       <c r="U505" s="5" t="n">
         <v>336</v>
       </c>
+      <c r="V505" s="5" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -42300,6 +43482,9 @@
       <c r="U506" s="5" t="n">
         <v>337</v>
       </c>
+      <c r="V506" s="5" t="n">
+        <v>181</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -42383,6 +43568,9 @@
       <c r="U507" s="5" t="n">
         <v>338</v>
       </c>
+      <c r="V507" s="5" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -42466,6 +43654,9 @@
       <c r="U508" s="5" t="n">
         <v>339</v>
       </c>
+      <c r="V508" s="5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -42549,6 +43740,9 @@
       <c r="U509" s="5" t="n">
         <v>340</v>
       </c>
+      <c r="V509" s="5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -42630,6 +43824,7 @@
         </is>
       </c>
       <c r="U510" s="5" t="n"/>
+      <c r="V510" s="5" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -42713,6 +43908,9 @@
       <c r="U511" s="5" t="n">
         <v>341</v>
       </c>
+      <c r="V511" s="5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -42794,6 +43992,7 @@
         </is>
       </c>
       <c r="U512" s="5" t="n"/>
+      <c r="V512" s="5" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -42877,6 +44076,9 @@
       <c r="U513" s="5" t="n">
         <v>342</v>
       </c>
+      <c r="V513" s="5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -42959,6 +44161,9 @@
       </c>
       <c r="U514" s="5" t="n">
         <v>343</v>
+      </c>
+      <c r="V514" s="5" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="515">
@@ -43039,6 +44244,7 @@
         </is>
       </c>
       <c r="U515" s="5" t="n"/>
+      <c r="V515" s="5" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -43120,6 +44326,7 @@
         </is>
       </c>
       <c r="U516" s="5" t="n"/>
+      <c r="V516" s="5" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -43203,6 +44410,9 @@
       <c r="U517" s="5" t="n">
         <v>344</v>
       </c>
+      <c r="V517" s="5" t="n">
+        <v>183</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -43286,6 +44496,9 @@
       <c r="U518" s="5" t="n">
         <v>345</v>
       </c>
+      <c r="V518" s="5" t="n">
+        <v>184</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -43369,6 +44582,9 @@
       <c r="U519" s="5" t="n">
         <v>346</v>
       </c>
+      <c r="V519" s="5" t="n">
+        <v>185</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -43452,6 +44668,9 @@
       <c r="U520" s="5" t="n">
         <v>347</v>
       </c>
+      <c r="V520" s="5" t="n">
+        <v>186</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -43535,6 +44754,9 @@
       <c r="U521" s="5" t="n">
         <v>348</v>
       </c>
+      <c r="V521" s="5" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -43618,6 +44840,9 @@
       <c r="U522" s="5" t="n">
         <v>349</v>
       </c>
+      <c r="V522" s="5" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -43701,6 +44926,9 @@
       <c r="U523" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="V523" s="5" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -43784,6 +45012,9 @@
       <c r="U524" s="5" t="n">
         <v>352</v>
       </c>
+      <c r="V524" s="5" t="n">
+        <v>189</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -43867,6 +45098,9 @@
       <c r="U525" s="5" t="n">
         <v>351</v>
       </c>
+      <c r="V525" s="5" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -43950,6 +45184,9 @@
       <c r="U526" s="5" t="n">
         <v>353</v>
       </c>
+      <c r="V526" s="5" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -44033,6 +45270,9 @@
       <c r="U527" s="5" t="n">
         <v>354</v>
       </c>
+      <c r="V527" s="5" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -44116,6 +45356,9 @@
       <c r="U528" s="5" t="n">
         <v>355</v>
       </c>
+      <c r="V528" s="5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -44199,6 +45442,9 @@
       <c r="U529" s="5" t="n">
         <v>356</v>
       </c>
+      <c r="V529" s="5" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -44282,6 +45528,9 @@
       <c r="U530" s="5" t="n">
         <v>357</v>
       </c>
+      <c r="V530" s="5" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -44363,6 +45612,7 @@
         </is>
       </c>
       <c r="U531" s="5" t="n"/>
+      <c r="V531" s="5" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -44444,6 +45694,7 @@
         </is>
       </c>
       <c r="U532" s="5" t="n"/>
+      <c r="V532" s="5" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -44526,6 +45777,9 @@
       </c>
       <c r="U533" s="5" t="n">
         <v>358</v>
+      </c>
+      <c r="V533" s="5" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="534">
@@ -44606,6 +45860,7 @@
         </is>
       </c>
       <c r="U534" s="5" t="n"/>
+      <c r="V534" s="5" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -44689,6 +45944,9 @@
       <c r="U535" s="5" t="n">
         <v>359</v>
       </c>
+      <c r="V535" s="5" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -44772,6 +46030,9 @@
       <c r="U536" s="5" t="n">
         <v>360</v>
       </c>
+      <c r="V536" s="5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -44855,6 +46116,9 @@
       <c r="U537" s="5" t="n">
         <v>361</v>
       </c>
+      <c r="V537" s="5" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -44938,6 +46202,9 @@
       <c r="U538" s="5" t="n">
         <v>362</v>
       </c>
+      <c r="V538" s="5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -45020,6 +46287,9 @@
       </c>
       <c r="U539" s="5" t="n">
         <v>363</v>
+      </c>
+      <c r="V539" s="5" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="540">
@@ -45102,6 +46372,9 @@
       <c r="U540" s="5" t="n">
         <v>364</v>
       </c>
+      <c r="V540" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -45185,6 +46458,9 @@
       <c r="U541" s="5" t="n">
         <v>365</v>
       </c>
+      <c r="V541" s="5" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -45266,6 +46542,7 @@
         </is>
       </c>
       <c r="U542" s="5" t="n"/>
+      <c r="V542" s="5" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -45349,6 +46626,9 @@
       <c r="U543" s="5" t="n">
         <v>366</v>
       </c>
+      <c r="V543" s="5" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -45431,6 +46711,9 @@
       </c>
       <c r="U544" s="5" t="n">
         <v>367</v>
+      </c>
+      <c r="V544" s="5" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="545">
@@ -45511,6 +46794,7 @@
         </is>
       </c>
       <c r="U545" s="5" t="n"/>
+      <c r="V545" s="5" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -45594,6 +46878,9 @@
       <c r="U546" s="5" t="n">
         <v>368</v>
       </c>
+      <c r="V546" s="5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -45676,6 +46963,9 @@
       </c>
       <c r="U547" s="5" t="n">
         <v>369</v>
+      </c>
+      <c r="V547" s="5" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="548">
@@ -45758,6 +47048,9 @@
       <c r="U548" s="5" t="n">
         <v>370</v>
       </c>
+      <c r="V548" s="5" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -45841,6 +47134,9 @@
       <c r="U549" s="5" t="n">
         <v>371</v>
       </c>
+      <c r="V549" s="5" t="n">
+        <v>201</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -45924,6 +47220,9 @@
       <c r="U550" s="5" t="n">
         <v>372</v>
       </c>
+      <c r="V550" s="5" t="n">
+        <v>202</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -46005,6 +47304,7 @@
         </is>
       </c>
       <c r="U551" s="5" t="n"/>
+      <c r="V551" s="5" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -46087,6 +47387,9 @@
       </c>
       <c r="U552" s="5" t="n">
         <v>373</v>
+      </c>
+      <c r="V552" s="5" t="n">
+        <v>203</v>
       </c>
     </row>
     <row r="553">
@@ -46167,6 +47470,7 @@
         </is>
       </c>
       <c r="U553" s="5" t="n"/>
+      <c r="V553" s="5" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -46248,6 +47552,7 @@
         </is>
       </c>
       <c r="U554" s="5" t="n"/>
+      <c r="V554" s="5" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -46331,6 +47636,9 @@
       <c r="U555" s="5" t="n">
         <v>374</v>
       </c>
+      <c r="V555" s="5" t="n">
+        <v>204</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -46412,6 +47720,7 @@
         </is>
       </c>
       <c r="U556" s="5" t="n"/>
+      <c r="V556" s="5" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -46493,6 +47802,9 @@
       <c r="U557" s="5" t="n">
         <v>376</v>
       </c>
+      <c r="V557" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -46576,6 +47888,9 @@
       <c r="U558" s="5" t="n">
         <v>375</v>
       </c>
+      <c r="V558" s="5" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -46657,6 +47972,7 @@
         </is>
       </c>
       <c r="U559" s="5" t="n"/>
+      <c r="V559" s="5" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -46740,6 +48056,9 @@
       <c r="U560" s="5" t="n">
         <v>377</v>
       </c>
+      <c r="V560" s="5" t="n">
+        <v>206</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -46823,6 +48142,9 @@
       <c r="U561" s="5" t="n">
         <v>378</v>
       </c>
+      <c r="V561" s="5" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -46906,6 +48228,9 @@
       <c r="U562" s="5" t="n">
         <v>379</v>
       </c>
+      <c r="V562" s="5" t="n">
+        <v>208</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -46987,6 +48312,7 @@
         </is>
       </c>
       <c r="U563" s="5" t="n"/>
+      <c r="V563" s="5" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -47070,6 +48396,9 @@
       <c r="U564" s="5" t="n">
         <v>380</v>
       </c>
+      <c r="V564" s="5" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -47153,6 +48482,9 @@
       <c r="U565" s="5" t="n">
         <v>381</v>
       </c>
+      <c r="V565" s="5" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -47234,6 +48566,7 @@
         </is>
       </c>
       <c r="U566" s="5" t="n"/>
+      <c r="V566" s="5" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -47317,6 +48650,9 @@
       <c r="U567" s="5" t="n">
         <v>382</v>
       </c>
+      <c r="V567" s="5" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -47400,6 +48736,9 @@
       <c r="U568" s="5" t="n">
         <v>383</v>
       </c>
+      <c r="V568" s="5" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -47481,6 +48820,7 @@
         </is>
       </c>
       <c r="U569" s="5" t="n"/>
+      <c r="V569" s="5" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -47562,6 +48902,7 @@
         </is>
       </c>
       <c r="U570" s="5" t="n"/>
+      <c r="V570" s="5" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -47643,6 +48984,9 @@
       <c r="U571" s="5" t="n">
         <v>384</v>
       </c>
+      <c r="V571" s="5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -47722,6 +49066,7 @@
         </is>
       </c>
       <c r="U572" s="5" t="n"/>
+      <c r="V572" s="5" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -47805,6 +49150,9 @@
       <c r="U573" s="5" t="n">
         <v>385</v>
       </c>
+      <c r="V573" s="5" t="n">
+        <v>213</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -47886,6 +49234,7 @@
         </is>
       </c>
       <c r="U574" s="5" t="n"/>
+      <c r="V574" s="5" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -47969,6 +49318,9 @@
       <c r="U575" s="5" t="n">
         <v>386</v>
       </c>
+      <c r="V575" s="5" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -48052,6 +49404,9 @@
       <c r="U576" s="5" t="n">
         <v>387</v>
       </c>
+      <c r="V576" s="5" t="n">
+        <v>214</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -48135,6 +49490,9 @@
       <c r="U577" s="5" t="n">
         <v>388</v>
       </c>
+      <c r="V577" s="5" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -48218,6 +49576,9 @@
       <c r="U578" s="5" t="n">
         <v>389</v>
       </c>
+      <c r="V578" s="5" t="n">
+        <v>216</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -48299,6 +49660,7 @@
         </is>
       </c>
       <c r="U579" s="5" t="n"/>
+      <c r="V579" s="5" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -48382,6 +49744,9 @@
       <c r="U580" s="5" t="n">
         <v>390</v>
       </c>
+      <c r="V580" s="5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -48465,6 +49830,9 @@
       <c r="U581" s="5" t="n">
         <v>391</v>
       </c>
+      <c r="V581" s="5" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -48547,6 +49915,9 @@
       </c>
       <c r="U582" s="5" t="n">
         <v>392</v>
+      </c>
+      <c r="V582" s="5" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="583">
@@ -48627,6 +49998,7 @@
         </is>
       </c>
       <c r="U583" s="5" t="n"/>
+      <c r="V583" s="5" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -48710,6 +50082,9 @@
       <c r="U584" s="5" t="n">
         <v>393</v>
       </c>
+      <c r="V584" s="5" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -48793,6 +50168,9 @@
       <c r="U585" s="5" t="n">
         <v>394</v>
       </c>
+      <c r="V585" s="5" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -48876,6 +50254,9 @@
       <c r="U586" s="5" t="n">
         <v>395</v>
       </c>
+      <c r="V586" s="5" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -48957,6 +50338,7 @@
         </is>
       </c>
       <c r="U587" s="5" t="n"/>
+      <c r="V587" s="5" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -49040,6 +50422,9 @@
       <c r="U588" s="5" t="n">
         <v>396</v>
       </c>
+      <c r="V588" s="5" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -49122,6 +50507,9 @@
       </c>
       <c r="U589" s="5" t="n">
         <v>397</v>
+      </c>
+      <c r="V589" s="5" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="590">
@@ -49202,6 +50590,7 @@
         </is>
       </c>
       <c r="U590" s="5" t="n"/>
+      <c r="V590" s="5" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -49283,6 +50672,7 @@
         </is>
       </c>
       <c r="U591" s="5" t="n"/>
+      <c r="V591" s="5" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -49365,6 +50755,9 @@
       </c>
       <c r="U592" s="5" t="n">
         <v>398</v>
+      </c>
+      <c r="V592" s="5" t="n">
+        <v>222</v>
       </c>
     </row>
     <row r="593">
@@ -49445,6 +50838,7 @@
         </is>
       </c>
       <c r="U593" s="5" t="n"/>
+      <c r="V593" s="5" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -49528,6 +50922,9 @@
       <c r="U594" s="5" t="n">
         <v>399</v>
       </c>
+      <c r="V594" s="5" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -49609,6 +51006,7 @@
         </is>
       </c>
       <c r="U595" s="5" t="n"/>
+      <c r="V595" s="5" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -49688,6 +51086,9 @@
       <c r="U596" s="5" t="n">
         <v>400</v>
       </c>
+      <c r="V596" s="5" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -49771,6 +51172,9 @@
       <c r="U597" s="5" t="n">
         <v>401</v>
       </c>
+      <c r="V597" s="5" t="n">
+        <v>223</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -49854,6 +51258,9 @@
       <c r="U598" s="5" t="n">
         <v>402</v>
       </c>
+      <c r="V598" s="5" t="n">
+        <v>224</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -49880,7 +51287,7 @@
         <v>26.34</v>
       </c>
       <c r="F599" s="3" t="n">
-        <v>57.11</v>
+        <v>57.1</v>
       </c>
       <c r="G599" s="3" t="n">
         <v>45.62</v>
@@ -49937,6 +51344,9 @@
       <c r="U599" s="5" t="n">
         <v>403</v>
       </c>
+      <c r="V599" s="5" t="n">
+        <v>225</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -50020,6 +51430,9 @@
       <c r="U600" s="5" t="n">
         <v>405</v>
       </c>
+      <c r="V600" s="5" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -50101,6 +51514,7 @@
         </is>
       </c>
       <c r="U601" s="5" t="n"/>
+      <c r="V601" s="5" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -50180,6 +51594,7 @@
         </is>
       </c>
       <c r="U602" s="5" t="n"/>
+      <c r="V602" s="5" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
@@ -50263,6 +51678,9 @@
       <c r="U603" s="5" t="n">
         <v>404</v>
       </c>
+      <c r="V603" s="5" t="n">
+        <v>226</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -50344,6 +51762,7 @@
         </is>
       </c>
       <c r="U604" s="5" t="n"/>
+      <c r="V604" s="5" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -50426,6 +51845,9 @@
       </c>
       <c r="U605" s="5" t="n">
         <v>406</v>
+      </c>
+      <c r="V605" s="5" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="606">
@@ -50506,6 +51928,9 @@
       <c r="U606" s="5" t="n">
         <v>407</v>
       </c>
+      <c r="V606" s="5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -50589,6 +52014,9 @@
       <c r="U607" s="5" t="n">
         <v>408</v>
       </c>
+      <c r="V607" s="5" t="n">
+        <v>228</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -50670,6 +52098,7 @@
         </is>
       </c>
       <c r="U608" s="5" t="n"/>
+      <c r="V608" s="5" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -50753,6 +52182,9 @@
       <c r="U609" s="5" t="n">
         <v>409</v>
       </c>
+      <c r="V609" s="5" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -50836,6 +52268,9 @@
       <c r="U610" s="5" t="n">
         <v>410</v>
       </c>
+      <c r="V610" s="5" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
@@ -50919,6 +52354,9 @@
       <c r="U611" s="5" t="n">
         <v>411</v>
       </c>
+      <c r="V611" s="5" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -51002,6 +52440,9 @@
       <c r="U612" s="5" t="n">
         <v>412</v>
       </c>
+      <c r="V612" s="5" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -51085,6 +52526,9 @@
       <c r="U613" s="5" t="n">
         <v>413</v>
       </c>
+      <c r="V613" s="5" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
@@ -51168,6 +52612,9 @@
       <c r="U614" s="5" t="n">
         <v>414</v>
       </c>
+      <c r="V614" s="5" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -51251,6 +52698,9 @@
       <c r="U615" s="5" t="n">
         <v>415</v>
       </c>
+      <c r="V615" s="5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -51334,6 +52784,9 @@
       <c r="U616" s="5" t="n">
         <v>416</v>
       </c>
+      <c r="V616" s="5" t="n">
+        <v>232</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -51415,6 +52868,7 @@
         </is>
       </c>
       <c r="U617" s="5" t="n"/>
+      <c r="V617" s="5" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -51498,6 +52952,9 @@
       <c r="U618" s="5" t="n">
         <v>417</v>
       </c>
+      <c r="V618" s="5" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -51579,6 +53036,7 @@
         </is>
       </c>
       <c r="U619" s="5" t="n"/>
+      <c r="V619" s="5" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -51662,6 +53120,9 @@
       <c r="U620" s="5" t="n">
         <v>418</v>
       </c>
+      <c r="V620" s="5" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -51743,6 +53204,7 @@
         </is>
       </c>
       <c r="U621" s="5" t="n"/>
+      <c r="V621" s="5" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -51826,6 +53288,9 @@
       <c r="U622" s="5" t="n">
         <v>419</v>
       </c>
+      <c r="V622" s="5" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -51909,6 +53374,9 @@
       <c r="U623" s="5" t="n">
         <v>420</v>
       </c>
+      <c r="V623" s="5" t="n">
+        <v>234</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -51992,6 +53460,9 @@
       <c r="U624" s="5" t="n">
         <v>421</v>
       </c>
+      <c r="V624" s="5" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -52075,6 +53546,9 @@
       <c r="U625" s="5" t="n">
         <v>422</v>
       </c>
+      <c r="V625" s="5" t="n">
+        <v>235</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -52158,6 +53632,9 @@
       <c r="U626" s="5" t="n">
         <v>423</v>
       </c>
+      <c r="V626" s="5" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -52240,6 +53717,9 @@
       </c>
       <c r="U627" s="5" t="n">
         <v>424</v>
+      </c>
+      <c r="V627" s="5" t="n">
+        <v>237</v>
       </c>
     </row>
     <row r="628">
@@ -52320,6 +53800,7 @@
         </is>
       </c>
       <c r="U628" s="5" t="n"/>
+      <c r="V628" s="5" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -52403,6 +53884,9 @@
       <c r="U629" s="5" t="n">
         <v>425</v>
       </c>
+      <c r="V629" s="5" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -52486,6 +53970,9 @@
       <c r="U630" s="5" t="n">
         <v>426</v>
       </c>
+      <c r="V630" s="5" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -52567,6 +54054,7 @@
         </is>
       </c>
       <c r="U631" s="5" t="n"/>
+      <c r="V631" s="5" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -52646,6 +54134,9 @@
       <c r="U632" s="5" t="n">
         <v>427</v>
       </c>
+      <c r="V632" s="5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
@@ -52727,6 +54218,7 @@
         </is>
       </c>
       <c r="U633" s="5" t="n"/>
+      <c r="V633" s="5" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -52810,6 +54302,9 @@
       <c r="U634" s="5" t="n">
         <v>428</v>
       </c>
+      <c r="V634" s="5" t="n">
+        <v>239</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -52892,6 +54387,9 @@
       </c>
       <c r="U635" s="5" t="n">
         <v>429</v>
+      </c>
+      <c r="V635" s="5" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="636">
@@ -52972,6 +54470,7 @@
         </is>
       </c>
       <c r="U636" s="5" t="n"/>
+      <c r="V636" s="5" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
@@ -53055,6 +54554,9 @@
       <c r="U637" s="5" t="n">
         <v>430</v>
       </c>
+      <c r="V637" s="5" t="n">
+        <v>241</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -53138,6 +54640,9 @@
       <c r="U638" s="5" t="n">
         <v>432</v>
       </c>
+      <c r="V638" s="5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -53221,6 +54726,9 @@
       <c r="U639" s="5" t="n">
         <v>431</v>
       </c>
+      <c r="V639" s="5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -53304,6 +54812,9 @@
       <c r="U640" s="5" t="n">
         <v>433</v>
       </c>
+      <c r="V640" s="5" t="n">
+        <v>242</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -53387,6 +54898,9 @@
       <c r="U641" s="5" t="n">
         <v>434</v>
       </c>
+      <c r="V641" s="5" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -53468,6 +54982,7 @@
         </is>
       </c>
       <c r="U642" s="5" t="n"/>
+      <c r="V642" s="5" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -53549,6 +55064,9 @@
       <c r="U643" s="5" t="n">
         <v>435</v>
       </c>
+      <c r="V643" s="5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -53630,6 +55148,7 @@
         </is>
       </c>
       <c r="U644" s="5" t="n"/>
+      <c r="V644" s="5" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -53709,6 +55228,7 @@
         </is>
       </c>
       <c r="U645" s="5" t="n"/>
+      <c r="V645" s="5" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -53792,6 +55312,9 @@
       <c r="U646" s="5" t="n">
         <v>436</v>
       </c>
+      <c r="V646" s="5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -53873,6 +55396,7 @@
         </is>
       </c>
       <c r="U647" s="5" t="n"/>
+      <c r="V647" s="5" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -53956,6 +55480,9 @@
       <c r="U648" s="5" t="n">
         <v>437</v>
       </c>
+      <c r="V648" s="5" t="n">
+        <v>244</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -54039,6 +55566,9 @@
       <c r="U649" s="5" t="n">
         <v>438</v>
       </c>
+      <c r="V649" s="5" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -54120,6 +55650,7 @@
         </is>
       </c>
       <c r="U650" s="5" t="n"/>
+      <c r="V650" s="5" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -54200,6 +55731,9 @@
       </c>
       <c r="U651" s="5" t="n">
         <v>439</v>
+      </c>
+      <c r="V651" s="5" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="652">
@@ -54280,6 +55814,9 @@
       <c r="U652" s="5" t="n">
         <v>440</v>
       </c>
+      <c r="V652" s="5" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -54363,6 +55900,9 @@
       <c r="U653" s="5" t="n">
         <v>441</v>
       </c>
+      <c r="V653" s="5" t="n">
+        <v>245</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -54446,6 +55986,9 @@
       <c r="U654" s="5" t="n">
         <v>442</v>
       </c>
+      <c r="V654" s="5" t="n">
+        <v>246</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -54529,6 +56072,9 @@
       <c r="U655" s="5" t="n">
         <v>443</v>
       </c>
+      <c r="V655" s="5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -54610,6 +56156,7 @@
         </is>
       </c>
       <c r="U656" s="5" t="n"/>
+      <c r="V656" s="5" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -54693,6 +56240,9 @@
       <c r="U657" s="5" t="n">
         <v>444</v>
       </c>
+      <c r="V657" s="5" t="n">
+        <v>247</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -54776,6 +56326,9 @@
       <c r="U658" s="5" t="n">
         <v>445</v>
       </c>
+      <c r="V658" s="5" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -54857,6 +56410,7 @@
         </is>
       </c>
       <c r="U659" s="5" t="n"/>
+      <c r="V659" s="5" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -54939,6 +56493,9 @@
       </c>
       <c r="U660" s="5" t="n">
         <v>446</v>
+      </c>
+      <c r="V660" s="5" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="661">
@@ -55019,6 +56576,9 @@
       <c r="U661" s="5" t="n">
         <v>447</v>
       </c>
+      <c r="V661" s="5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -55102,6 +56662,9 @@
       <c r="U662" s="5" t="n">
         <v>448</v>
       </c>
+      <c r="V662" s="5" t="n">
+        <v>248</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -55185,6 +56748,9 @@
       <c r="U663" s="5" t="n">
         <v>449</v>
       </c>
+      <c r="V663" s="5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -55266,6 +56832,7 @@
         </is>
       </c>
       <c r="U664" s="5" t="n"/>
+      <c r="V664" s="5" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -55345,6 +56912,7 @@
         </is>
       </c>
       <c r="U665" s="5" t="n"/>
+      <c r="V665" s="5" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -55428,6 +56996,9 @@
       <c r="U666" s="5" t="n">
         <v>450</v>
       </c>
+      <c r="V666" s="5" t="n">
+        <v>249</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -55511,6 +57082,9 @@
       <c r="U667" s="5" t="n">
         <v>451</v>
       </c>
+      <c r="V667" s="5" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
@@ -55593,6 +57167,9 @@
       </c>
       <c r="U668" s="5" t="n">
         <v>452</v>
+      </c>
+      <c r="V668" s="5" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="669">
@@ -55675,6 +57252,9 @@
       <c r="U669" s="5" t="n">
         <v>453</v>
       </c>
+      <c r="V669" s="5" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -55758,6 +57338,9 @@
       <c r="U670" s="5" t="n">
         <v>454</v>
       </c>
+      <c r="V670" s="5" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -55841,6 +57424,9 @@
       <c r="U671" s="5" t="n">
         <v>455</v>
       </c>
+      <c r="V671" s="5" t="n">
+        <v>251</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -55922,6 +57508,7 @@
         </is>
       </c>
       <c r="U672" s="5" t="n"/>
+      <c r="V672" s="5" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -56005,6 +57592,9 @@
       <c r="U673" s="5" t="n">
         <v>457</v>
       </c>
+      <c r="V673" s="5" t="n">
+        <v>253</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="2" t="inlineStr">
@@ -56088,6 +57678,9 @@
       <c r="U674" s="5" t="n">
         <v>456</v>
       </c>
+      <c r="V674" s="5" t="n">
+        <v>252</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
@@ -56170,6 +57763,9 @@
       </c>
       <c r="U675" s="5" t="n">
         <v>458</v>
+      </c>
+      <c r="V675" s="5" t="n">
+        <v>254</v>
       </c>
     </row>
     <row r="676">
@@ -56250,6 +57846,7 @@
         </is>
       </c>
       <c r="U676" s="5" t="n"/>
+      <c r="V676" s="5" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -56333,6 +57930,9 @@
       <c r="U677" s="5" t="n">
         <v>459</v>
       </c>
+      <c r="V677" s="5" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -56416,6 +58016,9 @@
       <c r="U678" s="5" t="n">
         <v>460</v>
       </c>
+      <c r="V678" s="5" t="n">
+        <v>256</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -56499,6 +58102,9 @@
       <c r="U679" s="5" t="n">
         <v>461</v>
       </c>
+      <c r="V679" s="5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -56582,6 +58188,9 @@
       <c r="U680" s="5" t="n">
         <v>462</v>
       </c>
+      <c r="V680" s="5" t="n">
+        <v>257</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -56664,6 +58273,9 @@
       </c>
       <c r="U681" s="5" t="n">
         <v>463</v>
+      </c>
+      <c r="V681" s="5" t="n">
+        <v>258</v>
       </c>
     </row>
     <row r="682">
@@ -56746,6 +58358,9 @@
       <c r="U682" s="5" t="n">
         <v>464</v>
       </c>
+      <c r="V682" s="5" t="n">
+        <v>259</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -56829,6 +58444,9 @@
       <c r="U683" s="5" t="n">
         <v>465</v>
       </c>
+      <c r="V683" s="5" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -56912,6 +58530,9 @@
       <c r="U684" s="5" t="n">
         <v>466</v>
       </c>
+      <c r="V684" s="5" t="n">
+        <v>261</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
@@ -56995,6 +58616,9 @@
       <c r="U685" s="5" t="n">
         <v>467</v>
       </c>
+      <c r="V685" s="5" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -57076,6 +58700,7 @@
         </is>
       </c>
       <c r="U686" s="5" t="n"/>
+      <c r="V686" s="5" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -57159,6 +58784,9 @@
       <c r="U687" s="5" t="n">
         <v>468</v>
       </c>
+      <c r="V687" s="5" t="n">
+        <v>263</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -57240,6 +58868,7 @@
         </is>
       </c>
       <c r="U688" s="5" t="n"/>
+      <c r="V688" s="5" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -57323,6 +58952,9 @@
       <c r="U689" s="5" t="n">
         <v>469</v>
       </c>
+      <c r="V689" s="5" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -57406,6 +59038,9 @@
       <c r="U690" s="5" t="n">
         <v>470</v>
       </c>
+      <c r="V690" s="5" t="n">
+        <v>265</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -57489,6 +59124,9 @@
       <c r="U691" s="5" t="n">
         <v>471</v>
       </c>
+      <c r="V691" s="5" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
@@ -57572,6 +59210,9 @@
       <c r="U692" s="5" t="n">
         <v>472</v>
       </c>
+      <c r="V692" s="5" t="n">
+        <v>266</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -57655,6 +59296,9 @@
       <c r="U693" s="5" t="n">
         <v>473</v>
       </c>
+      <c r="V693" s="5" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -57736,6 +59380,7 @@
         </is>
       </c>
       <c r="U694" s="5" t="n"/>
+      <c r="V694" s="5" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -57819,6 +59464,9 @@
       <c r="U695" s="5" t="n">
         <v>474</v>
       </c>
+      <c r="V695" s="5" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -57902,6 +59550,9 @@
       <c r="U696" s="5" t="n">
         <v>477</v>
       </c>
+      <c r="V696" s="5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -57984,6 +59635,9 @@
       </c>
       <c r="U697" s="5" t="n">
         <v>475</v>
+      </c>
+      <c r="V697" s="5" t="n">
+        <v>267</v>
       </c>
     </row>
     <row r="698">
@@ -58066,6 +59720,9 @@
       <c r="U698" s="5" t="n">
         <v>476</v>
       </c>
+      <c r="V698" s="5" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -58147,6 +59804,7 @@
         </is>
       </c>
       <c r="U699" s="5" t="n"/>
+      <c r="V699" s="5" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -58229,6 +59887,9 @@
       </c>
       <c r="U700" s="5" t="n">
         <v>478</v>
+      </c>
+      <c r="V700" s="5" t="n">
+        <v>268</v>
       </c>
     </row>
     <row r="701">
@@ -58311,6 +59972,9 @@
       <c r="U701" s="5" t="n">
         <v>479</v>
       </c>
+      <c r="V701" s="5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -58394,6 +60058,9 @@
       <c r="U702" s="5" t="n">
         <v>480</v>
       </c>
+      <c r="V702" s="5" t="n">
+        <v>269</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -58477,6 +60144,9 @@
       <c r="U703" s="5" t="n">
         <v>481</v>
       </c>
+      <c r="V703" s="5" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -58560,6 +60230,9 @@
       <c r="U704" s="5" t="n">
         <v>482</v>
       </c>
+      <c r="V704" s="5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -58643,6 +60316,9 @@
       <c r="U705" s="5" t="n">
         <v>483</v>
       </c>
+      <c r="V705" s="5" t="n">
+        <v>271</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -58724,6 +60400,7 @@
         </is>
       </c>
       <c r="U706" s="5" t="n"/>
+      <c r="V706" s="5" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -58805,6 +60482,7 @@
         </is>
       </c>
       <c r="U707" s="5" t="n"/>
+      <c r="V707" s="5" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -58888,6 +60566,9 @@
       <c r="U708" s="5" t="n">
         <v>484</v>
       </c>
+      <c r="V708" s="5" t="n">
+        <v>272</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -58971,6 +60652,9 @@
       <c r="U709" s="5" t="n">
         <v>485</v>
       </c>
+      <c r="V709" s="5" t="n">
+        <v>273</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -59053,6 +60737,9 @@
       </c>
       <c r="U710" s="5" t="n">
         <v>486</v>
+      </c>
+      <c r="V710" s="5" t="n">
+        <v>274</v>
       </c>
     </row>
     <row r="711">
@@ -59135,6 +60822,9 @@
       <c r="U711" s="5" t="n">
         <v>487</v>
       </c>
+      <c r="V711" s="5" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -59218,6 +60908,9 @@
       <c r="U712" s="5" t="n">
         <v>488</v>
       </c>
+      <c r="V712" s="5" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -59299,6 +60992,7 @@
         </is>
       </c>
       <c r="U713" s="5" t="n"/>
+      <c r="V713" s="5" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -59380,6 +61074,7 @@
         </is>
       </c>
       <c r="U714" s="5" t="n"/>
+      <c r="V714" s="5" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -59463,6 +61158,9 @@
       <c r="U715" s="5" t="n">
         <v>489</v>
       </c>
+      <c r="V715" s="5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -59546,6 +61244,9 @@
       <c r="U716" s="5" t="n">
         <v>490</v>
       </c>
+      <c r="V716" s="5" t="n">
+        <v>275</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
@@ -59629,6 +61330,9 @@
       <c r="U717" s="5" t="n">
         <v>491</v>
       </c>
+      <c r="V717" s="5" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="2" t="inlineStr">
@@ -59712,6 +61416,9 @@
       <c r="U718" s="5" t="n">
         <v>492</v>
       </c>
+      <c r="V718" s="5" t="n">
+        <v>276</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -59793,6 +61500,7 @@
         </is>
       </c>
       <c r="U719" s="5" t="n"/>
+      <c r="V719" s="5" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="inlineStr">
@@ -59875,6 +61583,9 @@
       </c>
       <c r="U720" s="5" t="n">
         <v>493</v>
+      </c>
+      <c r="V720" s="5" t="n">
+        <v>277</v>
       </c>
     </row>
     <row r="721">
@@ -59955,6 +61666,7 @@
         </is>
       </c>
       <c r="U721" s="5" t="n"/>
+      <c r="V721" s="5" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -60034,6 +61746,9 @@
       <c r="U722" s="5" t="n">
         <v>494</v>
       </c>
+      <c r="V722" s="5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
@@ -60117,6 +61832,9 @@
       <c r="U723" s="5" t="n">
         <v>495</v>
       </c>
+      <c r="V723" s="5" t="n">
+        <v>278</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -60199,6 +61917,9 @@
       </c>
       <c r="U724" s="5" t="n">
         <v>496</v>
+      </c>
+      <c r="V724" s="5" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="725">
@@ -60279,6 +62000,7 @@
         </is>
       </c>
       <c r="U725" s="5" t="n"/>
+      <c r="V725" s="5" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="inlineStr">
@@ -60360,6 +62082,9 @@
       <c r="U726" s="5" t="n">
         <v>497</v>
       </c>
+      <c r="V726" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="inlineStr">
@@ -60441,6 +62166,7 @@
         </is>
       </c>
       <c r="U727" s="5" t="n"/>
+      <c r="V727" s="5" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -60520,6 +62246,7 @@
         </is>
       </c>
       <c r="U728" s="5" t="n"/>
+      <c r="V728" s="5" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="inlineStr">
@@ -60601,6 +62328,9 @@
       <c r="U729" s="5" t="n">
         <v>498</v>
       </c>
+      <c r="V729" s="5" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="inlineStr">
@@ -60684,6 +62414,9 @@
       <c r="U730" s="5" t="n">
         <v>499</v>
       </c>
+      <c r="V730" s="5" t="n">
+        <v>279</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -60765,6 +62498,7 @@
         </is>
       </c>
       <c r="U731" s="5" t="n"/>
+      <c r="V731" s="5" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -60848,6 +62582,9 @@
       <c r="U732" s="5" t="n">
         <v>500</v>
       </c>
+      <c r="V732" s="5" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -60931,6 +62668,9 @@
       <c r="U733" s="5" t="n">
         <v>501</v>
       </c>
+      <c r="V733" s="5" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="inlineStr">
@@ -61014,6 +62754,9 @@
       <c r="U734" s="5" t="n">
         <v>502</v>
       </c>
+      <c r="V734" s="5" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="inlineStr">
@@ -61097,6 +62840,9 @@
       <c r="U735" s="5" t="n">
         <v>503</v>
       </c>
+      <c r="V735" s="5" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
@@ -61178,6 +62924,7 @@
         </is>
       </c>
       <c r="U736" s="5" t="n"/>
+      <c r="V736" s="5" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="inlineStr">
@@ -61259,6 +63006,7 @@
         </is>
       </c>
       <c r="U737" s="5" t="n"/>
+      <c r="V737" s="5" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="inlineStr">
@@ -61342,6 +63090,9 @@
       <c r="U738" s="5" t="n">
         <v>504</v>
       </c>
+      <c r="V738" s="5" t="n">
+        <v>283</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -61423,6 +63174,7 @@
         </is>
       </c>
       <c r="U739" s="5" t="n"/>
+      <c r="V739" s="5" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
@@ -61505,6 +63257,9 @@
       </c>
       <c r="U740" s="5" t="n">
         <v>505</v>
+      </c>
+      <c r="V740" s="5" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="741">
@@ -61587,6 +63342,9 @@
       <c r="U741" s="5" t="n">
         <v>506</v>
       </c>
+      <c r="V741" s="5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -61670,6 +63428,9 @@
       <c r="U742" s="5" t="n">
         <v>507</v>
       </c>
+      <c r="V742" s="5" t="n">
+        <v>285</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="inlineStr">
@@ -61753,6 +63514,9 @@
       <c r="U743" s="5" t="n">
         <v>508</v>
       </c>
+      <c r="V743" s="5" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -61836,6 +63600,9 @@
       <c r="U744" s="5" t="n">
         <v>509</v>
       </c>
+      <c r="V744" s="5" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -61919,6 +63686,9 @@
       <c r="U745" s="5" t="n">
         <v>510</v>
       </c>
+      <c r="V745" s="5" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -62000,6 +63770,7 @@
         </is>
       </c>
       <c r="U746" s="5" t="n"/>
+      <c r="V746" s="5" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -62081,6 +63852,9 @@
       <c r="U747" s="5" t="n">
         <v>511</v>
       </c>
+      <c r="V747" s="5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -62164,6 +63938,9 @@
       <c r="U748" s="5" t="n">
         <v>512</v>
       </c>
+      <c r="V748" s="5" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -62246,6 +64023,9 @@
       </c>
       <c r="U749" s="5" t="n">
         <v>513</v>
+      </c>
+      <c r="V749" s="5" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="750">
@@ -62328,6 +64108,9 @@
       <c r="U750" s="5" t="n">
         <v>514</v>
       </c>
+      <c r="V750" s="5" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -62411,6 +64194,9 @@
       <c r="U751" s="5" t="n">
         <v>515</v>
       </c>
+      <c r="V751" s="5" t="n">
+        <v>291</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">
@@ -62494,6 +64280,9 @@
       <c r="U752" s="5" t="n">
         <v>516</v>
       </c>
+      <c r="V752" s="5" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">
@@ -62577,6 +64366,9 @@
       <c r="U753" s="5" t="n">
         <v>517</v>
       </c>
+      <c r="V753" s="5" t="n">
+        <v>293</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -62660,6 +64452,9 @@
       <c r="U754" s="5" t="n">
         <v>518</v>
       </c>
+      <c r="V754" s="5" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="inlineStr">
@@ -62743,6 +64538,9 @@
       <c r="U755" s="5" t="n">
         <v>519</v>
       </c>
+      <c r="V755" s="5" t="n">
+        <v>295</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="inlineStr">
@@ -62824,6 +64622,7 @@
         </is>
       </c>
       <c r="U756" s="5" t="n"/>
+      <c r="V756" s="5" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="inlineStr">
@@ -62907,6 +64706,9 @@
       <c r="U757" s="5" t="n">
         <v>520</v>
       </c>
+      <c r="V757" s="5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -62990,6 +64792,9 @@
       <c r="U758" s="5" t="n">
         <v>521</v>
       </c>
+      <c r="V758" s="5" t="n">
+        <v>296</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -63072,6 +64877,9 @@
       </c>
       <c r="U759" s="5" t="n">
         <v>522</v>
+      </c>
+      <c r="V759" s="5" t="n">
+        <v>297</v>
       </c>
     </row>
     <row r="760">
@@ -63152,6 +64960,7 @@
         </is>
       </c>
       <c r="U760" s="5" t="n"/>
+      <c r="V760" s="5" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -63235,6 +65044,9 @@
       <c r="U761" s="5" t="n">
         <v>523</v>
       </c>
+      <c r="V761" s="5" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -63316,6 +65128,7 @@
         </is>
       </c>
       <c r="U762" s="5" t="n"/>
+      <c r="V762" s="5" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -63399,6 +65212,9 @@
       <c r="U763" s="5" t="n">
         <v>524</v>
       </c>
+      <c r="V763" s="5" t="n">
+        <v>299</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="inlineStr">
@@ -63482,6 +65298,9 @@
       <c r="U764" s="5" t="n">
         <v>525</v>
       </c>
+      <c r="V764" s="5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" s="2" t="inlineStr">
@@ -63565,6 +65384,9 @@
       <c r="U765" s="5" t="n">
         <v>527</v>
       </c>
+      <c r="V765" s="5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -63647,6 +65469,9 @@
       </c>
       <c r="U766" s="5" t="n">
         <v>526</v>
+      </c>
+      <c r="V766" s="5" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="767">
@@ -63729,6 +65554,9 @@
       <c r="U767" s="5" t="n">
         <v>528</v>
       </c>
+      <c r="V767" s="5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -63812,6 +65640,9 @@
       <c r="U768" s="5" t="n">
         <v>529</v>
       </c>
+      <c r="V768" s="5" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -63894,6 +65725,9 @@
       </c>
       <c r="U769" s="5" t="n">
         <v>530</v>
+      </c>
+      <c r="V769" s="5" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="770">
@@ -63976,6 +65810,9 @@
       <c r="U770" s="5" t="n">
         <v>531</v>
       </c>
+      <c r="V770" s="5" t="n">
+        <v>302</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -64057,6 +65894,7 @@
         </is>
       </c>
       <c r="U771" s="5" t="n"/>
+      <c r="V771" s="5" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="inlineStr">
@@ -64140,6 +65978,9 @@
       <c r="U772" s="5" t="n">
         <v>532</v>
       </c>
+      <c r="V772" s="5" t="n">
+        <v>303</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="inlineStr">
@@ -64223,6 +66064,9 @@
       <c r="U773" s="5" t="n">
         <v>533</v>
       </c>
+      <c r="V773" s="5" t="n">
+        <v>304</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="inlineStr">
@@ -64304,6 +66148,7 @@
         </is>
       </c>
       <c r="U774" s="5" t="n"/>
+      <c r="V774" s="5" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -64386,6 +66231,9 @@
       </c>
       <c r="U775" s="5" t="n">
         <v>534</v>
+      </c>
+      <c r="V775" s="5" t="n">
+        <v>305</v>
       </c>
     </row>
     <row r="776">
@@ -64468,6 +66316,9 @@
       <c r="U776" s="5" t="n">
         <v>535</v>
       </c>
+      <c r="V776" s="5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -64551,6 +66402,9 @@
       <c r="U777" s="5" t="n">
         <v>536</v>
       </c>
+      <c r="V777" s="5" t="n">
+        <v>306</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="2" t="inlineStr">
@@ -64632,6 +66486,7 @@
         </is>
       </c>
       <c r="U778" s="5" t="n"/>
+      <c r="V778" s="5" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="inlineStr">
@@ -64715,6 +66570,9 @@
       <c r="U779" s="5" t="n">
         <v>537</v>
       </c>
+      <c r="V779" s="5" t="n">
+        <v>307</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -64798,6 +66656,9 @@
       <c r="U780" s="5" t="n">
         <v>538</v>
       </c>
+      <c r="V780" s="5" t="n">
+        <v>308</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="inlineStr">
@@ -64881,6 +66742,9 @@
       <c r="U781" s="5" t="n">
         <v>540</v>
       </c>
+      <c r="V781" s="5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="2" t="inlineStr">
@@ -64964,6 +66828,9 @@
       <c r="U782" s="5" t="n">
         <v>539</v>
       </c>
+      <c r="V782" s="5" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" s="2" t="inlineStr">
@@ -65047,6 +66914,9 @@
       <c r="U783" s="5" t="n">
         <v>541</v>
       </c>
+      <c r="V783" s="5" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784" s="2" t="inlineStr">
@@ -65129,6 +66999,9 @@
       </c>
       <c r="U784" s="5" t="n">
         <v>542</v>
+      </c>
+      <c r="V784" s="5" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="785">
@@ -65211,6 +67084,9 @@
       <c r="U785" s="5" t="n">
         <v>543</v>
       </c>
+      <c r="V785" s="5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -65294,6 +67170,9 @@
       <c r="U786" s="5" t="n">
         <v>544</v>
       </c>
+      <c r="V786" s="5" t="n">
+        <v>312</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="2" t="inlineStr">
@@ -65375,6 +67254,7 @@
         </is>
       </c>
       <c r="U787" s="5" t="n"/>
+      <c r="V787" s="5" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -65458,6 +67338,9 @@
       <c r="U788" s="5" t="n">
         <v>545</v>
       </c>
+      <c r="V788" s="5" t="n">
+        <v>313</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -65541,6 +67424,9 @@
       <c r="U789" s="5" t="n">
         <v>547</v>
       </c>
+      <c r="V789" s="5" t="n">
+        <v>315</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="2" t="inlineStr">
@@ -65624,6 +67510,9 @@
       <c r="U790" s="5" t="n">
         <v>546</v>
       </c>
+      <c r="V790" s="5" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="inlineStr">
@@ -65707,6 +67596,9 @@
       <c r="U791" s="5" t="n">
         <v>548</v>
       </c>
+      <c r="V791" s="5" t="n">
+        <v>316</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="2" t="inlineStr">
@@ -65789,6 +67681,9 @@
       </c>
       <c r="U792" s="5" t="n">
         <v>549</v>
+      </c>
+      <c r="V792" s="5" t="n">
+        <v>317</v>
       </c>
     </row>
     <row r="793">
@@ -65871,6 +67766,9 @@
       <c r="U793" s="5" t="n">
         <v>550</v>
       </c>
+      <c r="V793" s="5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="2" t="inlineStr">
@@ -65953,6 +67851,9 @@
       </c>
       <c r="U794" s="5" t="n">
         <v>551</v>
+      </c>
+      <c r="V794" s="5" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="795">
@@ -66035,6 +67936,9 @@
       <c r="U795" s="5" t="n">
         <v>552</v>
       </c>
+      <c r="V795" s="5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="inlineStr">
@@ -66117,6 +68021,9 @@
       </c>
       <c r="U796" s="5" t="n">
         <v>553</v>
+      </c>
+      <c r="V796" s="5" t="n">
+        <v>318</v>
       </c>
     </row>
     <row r="797">
@@ -66199,6 +68106,9 @@
       <c r="U797" s="5" t="n">
         <v>554</v>
       </c>
+      <c r="V797" s="5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="inlineStr">
@@ -66281,6 +68191,9 @@
       </c>
       <c r="U798" s="5" t="n">
         <v>555</v>
+      </c>
+      <c r="V798" s="5" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="799">
@@ -66361,6 +68274,7 @@
         </is>
       </c>
       <c r="U799" s="5" t="n"/>
+      <c r="V799" s="5" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="inlineStr">
@@ -66444,6 +68358,9 @@
       <c r="U800" s="5" t="n">
         <v>556</v>
       </c>
+      <c r="V800" s="5" t="n">
+        <v>319</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -66527,6 +68444,9 @@
       <c r="U801" s="5" t="n">
         <v>557</v>
       </c>
+      <c r="V801" s="5" t="n">
+        <v>320</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -66610,6 +68530,9 @@
       <c r="U802" s="5" t="n">
         <v>558</v>
       </c>
+      <c r="V802" s="5" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -66693,6 +68616,9 @@
       <c r="U803" s="5" t="n">
         <v>559</v>
       </c>
+      <c r="V803" s="5" t="n">
+        <v>322</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -66776,6 +68702,9 @@
       <c r="U804" s="5" t="n">
         <v>560</v>
       </c>
+      <c r="V804" s="5" t="n">
+        <v>323</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="inlineStr">
@@ -66859,6 +68788,9 @@
       <c r="U805" s="5" t="n">
         <v>561</v>
       </c>
+      <c r="V805" s="5" t="n">
+        <v>324</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="inlineStr">
@@ -66942,6 +68874,9 @@
       <c r="U806" s="5" t="n">
         <v>562</v>
       </c>
+      <c r="V806" s="5" t="n">
+        <v>325</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="inlineStr">
@@ -67025,6 +68960,9 @@
       <c r="U807" s="5" t="n">
         <v>563</v>
       </c>
+      <c r="V807" s="5" t="n">
+        <v>326</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808" s="2" t="inlineStr">
@@ -67108,6 +69046,9 @@
       <c r="U808" s="5" t="n">
         <v>564</v>
       </c>
+      <c r="V808" s="5" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="2" t="inlineStr">
@@ -67190,6 +69131,9 @@
       </c>
       <c r="U809" s="5" t="n">
         <v>565</v>
+      </c>
+      <c r="V809" s="5" t="n">
+        <v>328</v>
       </c>
     </row>
     <row r="810">
@@ -67272,6 +69216,9 @@
       <c r="U810" s="5" t="n">
         <v>566</v>
       </c>
+      <c r="V810" s="5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="inlineStr">
@@ -67355,6 +69302,9 @@
       <c r="U811" s="5" t="n">
         <v>567</v>
       </c>
+      <c r="V811" s="5" t="n">
+        <v>329</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="inlineStr">
@@ -67437,6 +69387,9 @@
       </c>
       <c r="U812" s="5" t="n">
         <v>568</v>
+      </c>
+      <c r="V812" s="5" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="813">
@@ -67519,6 +69472,9 @@
       <c r="U813" s="5" t="n">
         <v>569</v>
       </c>
+      <c r="V813" s="5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="inlineStr">
@@ -67600,6 +69556,7 @@
         </is>
       </c>
       <c r="U814" s="5" t="n"/>
+      <c r="V814" s="5" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="inlineStr">
@@ -67683,6 +69640,9 @@
       <c r="U815" s="5" t="n">
         <v>570</v>
       </c>
+      <c r="V815" s="5" t="n">
+        <v>331</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="inlineStr">
@@ -67765,6 +69725,9 @@
       </c>
       <c r="U816" s="5" t="n">
         <v>571</v>
+      </c>
+      <c r="V816" s="5" t="n">
+        <v>332</v>
       </c>
     </row>
     <row r="817">
@@ -67845,6 +69808,9 @@
       <c r="U817" s="5" t="n">
         <v>572</v>
       </c>
+      <c r="V817" s="5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="inlineStr">
@@ -67928,6 +69894,9 @@
       <c r="U818" s="5" t="n">
         <v>573</v>
       </c>
+      <c r="V818" s="5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -68009,6 +69978,7 @@
         </is>
       </c>
       <c r="U819" s="5" t="n"/>
+      <c r="V819" s="5" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -68091,6 +70061,9 @@
       </c>
       <c r="U820" s="5" t="n">
         <v>574</v>
+      </c>
+      <c r="V820" s="5" t="n">
+        <v>333</v>
       </c>
     </row>
     <row r="821">
@@ -68171,6 +70144,7 @@
         </is>
       </c>
       <c r="U821" s="5" t="n"/>
+      <c r="V821" s="5" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="inlineStr">
@@ -68252,6 +70226,7 @@
         </is>
       </c>
       <c r="U822" s="5" t="n"/>
+      <c r="V822" s="5" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -68335,6 +70310,9 @@
       <c r="U823" s="5" t="n">
         <v>575</v>
       </c>
+      <c r="V823" s="5" t="n">
+        <v>334</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="inlineStr">
@@ -68416,6 +70394,7 @@
         </is>
       </c>
       <c r="U824" s="5" t="n"/>
+      <c r="V824" s="5" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">
@@ -68499,6 +70478,9 @@
       <c r="U825" s="5" t="n">
         <v>576</v>
       </c>
+      <c r="V825" s="5" t="n">
+        <v>335</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -68582,6 +70564,9 @@
       <c r="U826" s="5" t="n">
         <v>577</v>
       </c>
+      <c r="V826" s="5" t="n">
+        <v>336</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="inlineStr">
@@ -68665,6 +70650,9 @@
       <c r="U827" s="5" t="n">
         <v>578</v>
       </c>
+      <c r="V827" s="5" t="n">
+        <v>337</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="inlineStr">
@@ -68748,6 +70736,9 @@
       <c r="U828" s="5" t="n">
         <v>579</v>
       </c>
+      <c r="V828" s="5" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="inlineStr">
@@ -68831,6 +70822,9 @@
       <c r="U829" s="5" t="n">
         <v>580</v>
       </c>
+      <c r="V829" s="5" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="2" t="inlineStr">
@@ -68914,6 +70908,9 @@
       <c r="U830" s="5" t="n">
         <v>581</v>
       </c>
+      <c r="V830" s="5" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -68997,6 +70994,9 @@
       <c r="U831" s="5" t="n">
         <v>582</v>
       </c>
+      <c r="V831" s="5" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -69080,6 +71080,9 @@
       <c r="U832" s="5" t="n">
         <v>583</v>
       </c>
+      <c r="V832" s="5" t="n">
+        <v>342</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="inlineStr">
@@ -69163,6 +71166,9 @@
       <c r="U833" s="5" t="n">
         <v>584</v>
       </c>
+      <c r="V833" s="5" t="n">
+        <v>343</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="inlineStr">
@@ -69246,6 +71252,9 @@
       <c r="U834" s="5" t="n">
         <v>585</v>
       </c>
+      <c r="V834" s="5" t="n">
+        <v>344</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -69327,6 +71336,7 @@
         </is>
       </c>
       <c r="U835" s="5" t="n"/>
+      <c r="V835" s="5" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -69410,6 +71420,9 @@
       <c r="U836" s="5" t="n">
         <v>586</v>
       </c>
+      <c r="V836" s="5" t="n">
+        <v>345</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -69493,6 +71506,9 @@
       <c r="U837" s="5" t="n">
         <v>587</v>
       </c>
+      <c r="V837" s="5" t="n">
+        <v>346</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="inlineStr">
@@ -69576,6 +71592,9 @@
       <c r="U838" s="5" t="n">
         <v>588</v>
       </c>
+      <c r="V838" s="5" t="n">
+        <v>347</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="inlineStr">
@@ -69659,6 +71678,9 @@
       <c r="U839" s="5" t="n">
         <v>589</v>
       </c>
+      <c r="V839" s="5" t="n">
+        <v>348</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="2" t="inlineStr">
@@ -69742,6 +71764,9 @@
       <c r="U840" s="5" t="n">
         <v>590</v>
       </c>
+      <c r="V840" s="5" t="n">
+        <v>349</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="inlineStr">
@@ -69825,6 +71850,9 @@
       <c r="U841" s="5" t="n">
         <v>591</v>
       </c>
+      <c r="V841" s="5" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="inlineStr">
@@ -69906,6 +71934,7 @@
         </is>
       </c>
       <c r="U842" s="5" t="n"/>
+      <c r="V842" s="5" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -69989,6 +72018,9 @@
       <c r="U843" s="5" t="n">
         <v>592</v>
       </c>
+      <c r="V843" s="5" t="n">
+        <v>351</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="inlineStr">
@@ -70072,6 +72104,9 @@
       <c r="U844" s="5" t="n">
         <v>593</v>
       </c>
+      <c r="V844" s="5" t="n">
+        <v>352</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -70155,6 +72190,9 @@
       <c r="U845" s="5" t="n">
         <v>594</v>
       </c>
+      <c r="V845" s="5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -70237,6 +72275,9 @@
       </c>
       <c r="U846" s="5" t="n">
         <v>595</v>
+      </c>
+      <c r="V846" s="5" t="n">
+        <v>353</v>
       </c>
     </row>
     <row r="847">
@@ -70319,6 +72360,9 @@
       <c r="U847" s="5" t="n">
         <v>596</v>
       </c>
+      <c r="V847" s="5" t="n">
+        <v>354</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -70402,6 +72446,9 @@
       <c r="U848" s="5" t="n">
         <v>597</v>
       </c>
+      <c r="V848" s="5" t="n">
+        <v>355</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -70485,6 +72532,9 @@
       <c r="U849" s="5" t="n">
         <v>598</v>
       </c>
+      <c r="V849" s="5" t="n">
+        <v>356</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
@@ -70568,6 +72618,9 @@
       <c r="U850" s="5" t="n">
         <v>599</v>
       </c>
+      <c r="V850" s="5" t="n">
+        <v>357</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="inlineStr">
@@ -70649,6 +72702,7 @@
         </is>
       </c>
       <c r="U851" s="5" t="n"/>
+      <c r="V851" s="5" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -70730,6 +72784,9 @@
       <c r="U852" s="5" t="n">
         <v>600</v>
       </c>
+      <c r="V852" s="5" t="n">
+        <v>358</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -70813,6 +72870,9 @@
       <c r="U853" s="5" t="n">
         <v>601</v>
       </c>
+      <c r="V853" s="5" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
@@ -70896,6 +72956,9 @@
       <c r="U854" s="5" t="n">
         <v>602</v>
       </c>
+      <c r="V854" s="5" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -70979,6 +73042,9 @@
       <c r="U855" s="5" t="n">
         <v>603</v>
       </c>
+      <c r="V855" s="5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -71062,6 +73128,9 @@
       <c r="U856" s="5" t="n">
         <v>604</v>
       </c>
+      <c r="V856" s="5" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="inlineStr">
@@ -71145,6 +73214,9 @@
       <c r="U857" s="5" t="n">
         <v>605</v>
       </c>
+      <c r="V857" s="5" t="n">
+        <v>362</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="inlineStr">
@@ -71226,6 +73298,7 @@
         </is>
       </c>
       <c r="U858" s="5" t="n"/>
+      <c r="V858" s="5" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -71309,6 +73382,9 @@
       <c r="U859" s="5" t="n">
         <v>606</v>
       </c>
+      <c r="V859" s="5" t="n">
+        <v>363</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="inlineStr">
@@ -71392,6 +73468,9 @@
       <c r="U860" s="5" t="n">
         <v>607</v>
       </c>
+      <c r="V860" s="5" t="n">
+        <v>364</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="inlineStr">
@@ -71473,6 +73552,7 @@
         </is>
       </c>
       <c r="U861" s="5" t="n"/>
+      <c r="V861" s="5" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -71552,6 +73632,7 @@
         </is>
       </c>
       <c r="U862" s="5" t="n"/>
+      <c r="V862" s="5" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
@@ -71635,6 +73716,9 @@
       <c r="U863" s="5" t="n">
         <v>608</v>
       </c>
+      <c r="V863" s="5" t="n">
+        <v>365</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
@@ -71718,6 +73802,9 @@
       <c r="U864" s="5" t="n">
         <v>609</v>
       </c>
+      <c r="V864" s="5" t="n">
+        <v>366</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -71801,6 +73888,9 @@
       <c r="U865" s="5" t="n">
         <v>610</v>
       </c>
+      <c r="V865" s="5" t="n">
+        <v>367</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866" s="2" t="inlineStr">
@@ -71884,6 +73974,9 @@
       <c r="U866" s="5" t="n">
         <v>611</v>
       </c>
+      <c r="V866" s="5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="inlineStr">
@@ -71967,6 +74060,9 @@
       <c r="U867" s="5" t="n">
         <v>612</v>
       </c>
+      <c r="V867" s="5" t="n">
+        <v>368</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
@@ -72050,6 +74146,9 @@
       <c r="U868" s="5" t="n">
         <v>613</v>
       </c>
+      <c r="V868" s="5" t="n">
+        <v>369</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -72133,6 +74232,9 @@
       <c r="U869" s="5" t="n">
         <v>614</v>
       </c>
+      <c r="V869" s="5" t="n">
+        <v>370</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -72214,6 +74316,7 @@
         </is>
       </c>
       <c r="U870" s="5" t="n"/>
+      <c r="V870" s="5" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="inlineStr">
@@ -72295,6 +74398,9 @@
       <c r="U871" s="5" t="n">
         <v>616</v>
       </c>
+      <c r="V871" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="inlineStr">
@@ -72377,6 +74483,9 @@
       </c>
       <c r="U872" s="5" t="n">
         <v>615</v>
+      </c>
+      <c r="V872" s="5" t="n">
+        <v>371</v>
       </c>
     </row>
     <row r="873">
@@ -72459,6 +74568,9 @@
       <c r="U873" s="5" t="n">
         <v>617</v>
       </c>
+      <c r="V873" s="5" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -72542,6 +74654,9 @@
       <c r="U874" s="5" t="n">
         <v>618</v>
       </c>
+      <c r="V874" s="5" t="n">
+        <v>373</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
@@ -72625,6 +74740,9 @@
       <c r="U875" s="5" t="n">
         <v>619</v>
       </c>
+      <c r="V875" s="5" t="n">
+        <v>374</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="inlineStr">
@@ -72708,6 +74826,9 @@
       <c r="U876" s="5" t="n">
         <v>620</v>
       </c>
+      <c r="V876" s="5" t="n">
+        <v>375</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="inlineStr">
@@ -72791,6 +74912,9 @@
       <c r="U877" s="5" t="n">
         <v>621</v>
       </c>
+      <c r="V877" s="5" t="n">
+        <v>376</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="inlineStr">
@@ -72873,6 +74997,9 @@
       </c>
       <c r="U878" s="5" t="n">
         <v>622</v>
+      </c>
+      <c r="V878" s="5" t="n">
+        <v>377</v>
       </c>
     </row>
     <row r="879">
@@ -72955,6 +75082,9 @@
       <c r="U879" s="5" t="n">
         <v>623</v>
       </c>
+      <c r="V879" s="5" t="n">
+        <v>378</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
@@ -73036,6 +75166,9 @@
       <c r="U880" s="5" t="n">
         <v>624</v>
       </c>
+      <c r="V880" s="5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="inlineStr">
@@ -73119,6 +75252,9 @@
       <c r="U881" s="5" t="n">
         <v>625</v>
       </c>
+      <c r="V881" s="5" t="n">
+        <v>379</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="inlineStr">
@@ -73200,6 +75336,7 @@
         </is>
       </c>
       <c r="U882" s="5" t="n"/>
+      <c r="V882" s="5" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
@@ -73281,6 +75418,9 @@
       <c r="U883" s="5" t="n">
         <v>626</v>
       </c>
+      <c r="V883" s="5" t="n">
+        <v>380</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="inlineStr">
@@ -73364,6 +75504,9 @@
       <c r="U884" s="5" t="n">
         <v>627</v>
       </c>
+      <c r="V884" s="5" t="n">
+        <v>381</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
@@ -73445,6 +75588,7 @@
         </is>
       </c>
       <c r="U885" s="5" t="n"/>
+      <c r="V885" s="5" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="inlineStr">
@@ -73528,6 +75672,9 @@
       <c r="U886" s="5" t="n">
         <v>628</v>
       </c>
+      <c r="V886" s="5" t="n">
+        <v>382</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
@@ -73611,6 +75758,9 @@
       <c r="U887" s="5" t="n">
         <v>629</v>
       </c>
+      <c r="V887" s="5" t="n">
+        <v>383</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -73694,6 +75844,9 @@
       <c r="U888" s="5" t="n">
         <v>630</v>
       </c>
+      <c r="V888" s="5" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -73777,6 +75930,9 @@
       <c r="U889" s="5" t="n">
         <v>631</v>
       </c>
+      <c r="V889" s="5" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
@@ -73858,6 +76014,7 @@
         </is>
       </c>
       <c r="U890" s="5" t="n"/>
+      <c r="V890" s="5" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="inlineStr">
@@ -73939,6 +76096,9 @@
       <c r="U891" s="5" t="n">
         <v>632</v>
       </c>
+      <c r="V891" s="5" t="n">
+        <v>386</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="inlineStr">
@@ -74020,6 +76180,7 @@
         </is>
       </c>
       <c r="U892" s="5" t="n"/>
+      <c r="V892" s="5" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="inlineStr">
@@ -74102,6 +76263,9 @@
       </c>
       <c r="U893" s="5" t="n">
         <v>633</v>
+      </c>
+      <c r="V893" s="5" t="n">
+        <v>387</v>
       </c>
     </row>
     <row r="894">
@@ -74182,6 +76346,7 @@
         </is>
       </c>
       <c r="U894" s="5" t="n"/>
+      <c r="V894" s="5" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
@@ -74263,6 +76428,7 @@
         </is>
       </c>
       <c r="U895" s="5" t="n"/>
+      <c r="V895" s="5" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="inlineStr">
@@ -74345,6 +76511,9 @@
       </c>
       <c r="U896" s="5" t="n">
         <v>634</v>
+      </c>
+      <c r="V896" s="5" t="n">
+        <v>388</v>
       </c>
     </row>
     <row r="897">
@@ -74425,6 +76594,7 @@
         </is>
       </c>
       <c r="U897" s="5" t="n"/>
+      <c r="V897" s="5" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
@@ -74506,6 +76676,7 @@
         </is>
       </c>
       <c r="U898" s="5" t="n"/>
+      <c r="V898" s="5" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
@@ -74585,6 +76756,7 @@
         </is>
       </c>
       <c r="U899" s="5" t="n"/>
+      <c r="V899" s="5" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
@@ -74668,6 +76840,9 @@
       <c r="U900" s="5" t="n">
         <v>635</v>
       </c>
+      <c r="V900" s="5" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -74751,6 +76926,9 @@
       <c r="U901" s="5" t="n">
         <v>636</v>
       </c>
+      <c r="V901" s="5" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" s="2" t="inlineStr">
@@ -74834,6 +77012,9 @@
       <c r="U902" s="5" t="n">
         <v>637</v>
       </c>
+      <c r="V902" s="5" t="n">
+        <v>391</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="inlineStr">
@@ -74915,6 +77096,7 @@
         </is>
       </c>
       <c r="U903" s="5" t="n"/>
+      <c r="V903" s="5" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -74997,6 +77179,9 @@
       </c>
       <c r="U904" s="5" t="n">
         <v>638</v>
+      </c>
+      <c r="V904" s="5" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="905">
@@ -75079,6 +77264,9 @@
       <c r="U905" s="5" t="n">
         <v>639</v>
       </c>
+      <c r="V905" s="5" t="n">
+        <v>393</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
@@ -75160,6 +77348,9 @@
       <c r="U906" s="5" t="n">
         <v>640</v>
       </c>
+      <c r="V906" s="5" t="n">
+        <v>394</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
@@ -75243,6 +77434,9 @@
       <c r="U907" s="5" t="n">
         <v>641</v>
       </c>
+      <c r="V907" s="5" t="n">
+        <v>395</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
@@ -75326,6 +77520,9 @@
       <c r="U908" s="5" t="n">
         <v>642</v>
       </c>
+      <c r="V908" s="5" t="n">
+        <v>396</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
@@ -75409,6 +77606,9 @@
       <c r="U909" s="5" t="n">
         <v>643</v>
       </c>
+      <c r="V909" s="5" t="n">
+        <v>397</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
@@ -75492,6 +77692,9 @@
       <c r="U910" s="5" t="n">
         <v>644</v>
       </c>
+      <c r="V910" s="5" t="n">
+        <v>398</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -75573,6 +77776,7 @@
         </is>
       </c>
       <c r="U911" s="5" t="n"/>
+      <c r="V911" s="5" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -75653,6 +77857,9 @@
       </c>
       <c r="U912" s="5" t="n">
         <v>645</v>
+      </c>
+      <c r="V912" s="5" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="913">
@@ -75733,6 +77940,9 @@
       <c r="U913" s="5" t="n">
         <v>646</v>
       </c>
+      <c r="V913" s="5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -75814,6 +78024,9 @@
       <c r="U914" s="5" t="n">
         <v>647</v>
       </c>
+      <c r="V914" s="5" t="n">
+        <v>399</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
@@ -75897,6 +78110,9 @@
       <c r="U915" s="5" t="n">
         <v>648</v>
       </c>
+      <c r="V915" s="5" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
@@ -75978,6 +78194,7 @@
         </is>
       </c>
       <c r="U916" s="5" t="n"/>
+      <c r="V916" s="5" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="inlineStr">
@@ -76059,6 +78276,7 @@
         </is>
       </c>
       <c r="U917" s="5" t="n"/>
+      <c r="V917" s="5" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
@@ -76141,6 +78359,9 @@
       </c>
       <c r="U918" s="5" t="n">
         <v>649</v>
+      </c>
+      <c r="V918" s="5" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="919">
@@ -76221,6 +78442,7 @@
         </is>
       </c>
       <c r="U919" s="5" t="n"/>
+      <c r="V919" s="5" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
@@ -76303,6 +78525,9 @@
       </c>
       <c r="U920" s="5" t="n">
         <v>650</v>
+      </c>
+      <c r="V920" s="5" t="n">
+        <v>402</v>
       </c>
     </row>
     <row r="921">
@@ -76385,6 +78610,9 @@
       <c r="U921" s="5" t="n">
         <v>651</v>
       </c>
+      <c r="V921" s="5" t="n">
+        <v>403</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -76468,6 +78696,9 @@
       <c r="U922" s="5" t="n">
         <v>652</v>
       </c>
+      <c r="V922" s="5" t="n">
+        <v>404</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -76550,6 +78781,9 @@
       </c>
       <c r="U923" s="5" t="n">
         <v>653</v>
+      </c>
+      <c r="V923" s="5" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="924">
@@ -76630,6 +78864,7 @@
         </is>
       </c>
       <c r="U924" s="5" t="n"/>
+      <c r="V924" s="5" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
@@ -76711,6 +78946,7 @@
         </is>
       </c>
       <c r="U925" s="5" t="n"/>
+      <c r="V925" s="5" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -76792,6 +79028,7 @@
         </is>
       </c>
       <c r="U926" s="5" t="n"/>
+      <c r="V926" s="5" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
@@ -76875,6 +79112,9 @@
       <c r="U927" s="5" t="n">
         <v>654</v>
       </c>
+      <c r="V927" s="5" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="inlineStr">
@@ -76958,6 +79198,9 @@
       <c r="U928" s="5" t="n">
         <v>655</v>
       </c>
+      <c r="V928" s="5" t="n">
+        <v>407</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="2" t="inlineStr">
@@ -77039,6 +79282,7 @@
         </is>
       </c>
       <c r="U929" s="5" t="n"/>
+      <c r="V929" s="5" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="inlineStr">
@@ -77122,6 +79366,9 @@
       <c r="U930" s="5" t="n">
         <v>656</v>
       </c>
+      <c r="V930" s="5" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
@@ -77204,6 +79451,9 @@
       </c>
       <c r="U931" s="5" t="n">
         <v>657</v>
+      </c>
+      <c r="V931" s="5" t="n">
+        <v>409</v>
       </c>
     </row>
     <row r="932">
@@ -77286,6 +79536,9 @@
       <c r="U932" s="5" t="n">
         <v>658</v>
       </c>
+      <c r="V932" s="5" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
@@ -77367,6 +79620,7 @@
         </is>
       </c>
       <c r="U933" s="5" t="n"/>
+      <c r="V933" s="5" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -77448,6 +79702,7 @@
         </is>
       </c>
       <c r="U934" s="5" t="n"/>
+      <c r="V934" s="5" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
@@ -77529,6 +79784,7 @@
         </is>
       </c>
       <c r="U935" s="5" t="n"/>
+      <c r="V935" s="5" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="inlineStr">
@@ -77612,6 +79868,9 @@
       <c r="U936" s="5" t="n">
         <v>659</v>
       </c>
+      <c r="V936" s="5" t="n">
+        <v>410</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
@@ -77695,6 +79954,9 @@
       <c r="U937" s="5" t="n">
         <v>660</v>
       </c>
+      <c r="V937" s="5" t="n">
+        <v>411</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -77778,6 +80040,9 @@
       <c r="U938" s="5" t="n">
         <v>661</v>
       </c>
+      <c r="V938" s="5" t="n">
+        <v>412</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -77861,6 +80126,9 @@
       <c r="U939" s="5" t="n">
         <v>662</v>
       </c>
+      <c r="V939" s="5" t="n">
+        <v>413</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
@@ -77944,6 +80212,9 @@
       <c r="U940" s="5" t="n">
         <v>663</v>
       </c>
+      <c r="V940" s="5" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -78027,6 +80298,9 @@
       <c r="U941" s="5" t="n">
         <v>664</v>
       </c>
+      <c r="V941" s="5" t="n">
+        <v>415</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" s="2" t="inlineStr">
@@ -78108,6 +80382,7 @@
         </is>
       </c>
       <c r="U942" s="5" t="n"/>
+      <c r="V942" s="5" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="inlineStr">
@@ -78190,6 +80465,9 @@
       </c>
       <c r="U943" s="5" t="n">
         <v>665</v>
+      </c>
+      <c r="V943" s="5" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="944">
@@ -78272,6 +80550,9 @@
       <c r="U944" s="5" t="n">
         <v>666</v>
       </c>
+      <c r="V944" s="5" t="n">
+        <v>417</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
@@ -78353,6 +80634,9 @@
       <c r="U945" s="5" t="n">
         <v>667</v>
       </c>
+      <c r="V945" s="5" t="n">
+        <v>418</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
@@ -78434,6 +80718,7 @@
         </is>
       </c>
       <c r="U946" s="5" t="n"/>
+      <c r="V946" s="5" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
@@ -78515,9 +80800,10 @@
         </is>
       </c>
       <c r="U947" s="5" t="n"/>
+      <c r="V947" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U947"/>
+  <autoFilter ref="A1:V947"/>
   <conditionalFormatting sqref="E2:E947">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -78691,6 +80977,11 @@
   <conditionalFormatting sqref="U2:U947">
     <cfRule type="expression" priority="22" dxfId="2">
       <formula>NOT(ISBLANK(U2))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V947">
+    <cfRule type="expression" priority="23" dxfId="2">
+      <formula>NOT(ISBLANK(V2))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -79651,7 +81942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C28"/>
+  <dimension ref="B2:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -79924,6 +82215,18 @@
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Dense rank (1, 2, 3, …) by score descending over eligible rows only — blank for ineligible or unscored rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>eco_priority</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>The same rank restarted within each ecosystem, so npm rank 1 and PyPI rank 1 are both present. Same rows and same order as priority — only the grouping differs.</t>
         </is>
       </c>
     </row>
@@ -80091,10 +82394,10 @@
         <v>295086</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>30293</v>
+        <v>30315</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>3767613</v>
+        <v>3767635</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
@@ -80102,16 +82405,16 @@
         </is>
       </c>
       <c r="J7" s="20" t="n">
-        <v>8488</v>
+        <v>8508</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>22448</v>
+        <v>22452</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>30936</v>
+        <v>30960</v>
       </c>
       <c r="M7" s="21" t="n">
-        <v>30293</v>
+        <v>30315</v>
       </c>
     </row>
     <row r="8">
@@ -80141,13 +82444,13 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="K8" s="24" t="n">
         <v>1631</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="M8" s="25" t="n">
         <v>1334</v>
@@ -80182,7 +82485,7 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>6258</v>
+        <v>6259</v>
       </c>
       <c r="D10" s="20" t="n">
         <v>2927</v>
@@ -80191,10 +82494,10 @@
         <v>6403</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>17071</v>
+        <v>17074</v>
       </c>
     </row>
     <row r="11">
@@ -80204,7 +82507,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>2299</v>
@@ -80213,10 +82516,10 @@
         <v>3559</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>11567</v>
+        <v>11570</v>
       </c>
     </row>
     <row r="14">
@@ -80317,13 +82620,13 @@
         <v>921</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>6927</v>
+        <v>6929</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>10619</v>
+        <v>10620</v>
       </c>
       <c r="G21" s="32" t="n">
         <v>0.9179999999999999</v>
@@ -80342,10 +82645,10 @@
         <v>226</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G22" s="32" t="n">
         <v>0.073</v>
@@ -80361,13 +82664,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E23" s="20" t="n">
         <v>64</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G23" s="32" t="n">
         <v>0.009000000000000001</v>
@@ -80386,10 +82689,10 @@
         <v>3016</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>7498</v>
+        <v>7500</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>11460</v>
+        <v>11462</v>
       </c>
       <c r="G24" s="35" t="n">
         <v>0.991</v>
@@ -80408,10 +82711,10 @@
         <v>22</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G25" s="32" t="n">
         <v>0.009000000000000001</v>
@@ -80430,10 +82733,10 @@
         <v>1396</v>
       </c>
       <c r="E26" s="34" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="F26" s="34" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="G26" s="35" t="n">
         <v>0.3720000000000001</v>
@@ -80496,10 +82799,10 @@
         <v>535</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="G29" s="32" t="n">
         <v>0.127</v>
@@ -80518,10 +82821,10 @@
         <v>3038</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>7583</v>
+        <v>7586</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>11567</v>
+        <v>11570</v>
       </c>
       <c r="G30" s="36" t="n">
         <v>1</v>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -82516,10 +82516,10 @@
         <v>3559</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>11570</v>
+        <v>11567</v>
       </c>
     </row>
     <row r="14">
@@ -82645,10 +82645,10 @@
         <v>226</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="G22" s="32" t="n">
         <v>0.073</v>
@@ -82689,10 +82689,10 @@
         <v>3016</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>7500</v>
+        <v>7497</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>11462</v>
+        <v>11459</v>
       </c>
       <c r="G24" s="35" t="n">
         <v>0.991</v>
@@ -82799,10 +82799,10 @@
         <v>535</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="G29" s="32" t="n">
         <v>0.127</v>
@@ -82821,10 +82821,10 @@
         <v>3038</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>7586</v>
+        <v>7583</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>11570</v>
+        <v>11567</v>
       </c>
       <c r="G30" s="36" t="n">
         <v>1</v>

--- a/data/preview/preview.xlsx
+++ b/data/preview/preview.xlsx
@@ -82577,10 +82577,10 @@
         <v>6403</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>17075</v>
+        <v>17076</v>
       </c>
     </row>
     <row r="11">
@@ -82599,10 +82599,10 @@
         <v>3559</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>11568</v>
+        <v>11569</v>
       </c>
     </row>
     <row r="14">
@@ -82703,13 +82703,13 @@
         <v>922</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="E21" s="20" t="n">
         <v>6929</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>10621</v>
+        <v>10622</v>
       </c>
       <c r="G21" s="32" t="n">
         <v>0.9179999999999999</v>
@@ -82769,13 +82769,13 @@
         <v>947</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>7497</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>11460</v>
+        <v>11461</v>
       </c>
       <c r="G24" s="35" t="n">
         <v>0.991</v>
@@ -82879,13 +82879,13 @@
         <v>86</v>
       </c>
       <c r="D29" s="20" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E29" s="20" t="n">
         <v>844</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="G29" s="32" t="n">
         <v>0.127</v>
@@ -82901,13 +82901,13 @@
         <v>947</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="E30" s="27" t="n">
         <v>7583</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>11568</v>
+        <v>11569</v>
       </c>
       <c r="G30" s="36" t="n">
         <v>1</v>
